--- a/research/traditional_assets/database/data/slovenia/slovenia_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_retail_automotive.xlsx
@@ -647,10 +647,10 @@
         <v>0.1915333550984873</v>
       </c>
       <c r="X2">
-        <v>0.1036980901936136</v>
+        <v>0.1036784890718817</v>
       </c>
       <c r="Y2">
-        <v>0.08783526490487373</v>
+        <v>0.08785486602660564</v>
       </c>
       <c r="Z2">
         <v>5.450823492852702</v>
@@ -659,10 +659,10 @@
         <v>0.1505512646461269</v>
       </c>
       <c r="AB2">
-        <v>0.08930507047336521</v>
+        <v>0.08929165038149207</v>
       </c>
       <c r="AC2">
-        <v>0.06124619417276168</v>
+        <v>0.06125961426463482</v>
       </c>
       <c r="AD2">
         <v>617.5</v>
@@ -781,10 +781,10 @@
         <v>0.1915333550984873</v>
       </c>
       <c r="X3">
-        <v>0.1036980901936136</v>
+        <v>0.1036784890718817</v>
       </c>
       <c r="Y3">
-        <v>0.08783526490487373</v>
+        <v>0.08785486602660564</v>
       </c>
       <c r="Z3">
         <v>5.450823492852702</v>
@@ -793,10 +793,10 @@
         <v>0.1505512646461269</v>
       </c>
       <c r="AB3">
-        <v>0.08930507047336521</v>
+        <v>0.08929165038149207</v>
       </c>
       <c r="AC3">
-        <v>0.06124619417276168</v>
+        <v>0.06125961426463482</v>
       </c>
       <c r="AD3">
         <v>617.5</v>
@@ -1133,7 +1133,7 @@
         <v>11.0357142857143</v>
       </c>
       <c r="F2">
-        <v>13.3653956882537</v>
+        <v>13.6663540422406</v>
       </c>
       <c r="G2">
         <v>1.88032886723508</v>
@@ -1151,13 +1151,13 @@
         <v>1340.7</v>
       </c>
       <c r="L2">
-        <v>1732.18795260205</v>
+        <v>1734.80739304254</v>
       </c>
       <c r="M2">
         <v>1880.8</v>
       </c>
       <c r="N2">
-        <v>1909.35395260205</v>
+        <v>1911.97339304254</v>
       </c>
       <c r="O2">
         <v>617.5</v>
@@ -1166,16 +1166,16 @@
         <v>254.566</v>
       </c>
       <c r="Q2">
-        <v>0.08930507047336519</v>
+        <v>0.0892916503814921</v>
       </c>
       <c r="R2">
-        <v>0.0876656271106698</v>
+        <v>0.0875042843146757</v>
       </c>
       <c r="S2">
         <v>0.0580553189933052</v>
       </c>
       <c r="T2">
-        <v>0.0514943189933052</v>
+        <v>0.0503603189933052</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.103698090193614</v>
+        <v>0.103678489071882</v>
       </c>
       <c r="X2">
-        <v>0.093070535220161</v>
+        <v>0.0930545320063748</v>
       </c>
       <c r="Y2">
         <v>0.975914475240016</v>
@@ -1230,7 +1230,7 @@
         <v>1340.7</v>
       </c>
       <c r="AK2">
-        <v>0.05932701242019611</v>
+        <v>0.05930692754367341</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08796688776944536</v>
+        <v>0.08795261237111252</v>
       </c>
       <c r="C2">
-        <v>1981.442098131395</v>
+        <v>1981.457427205323</v>
       </c>
       <c r="D2">
-        <v>1904.042098131395</v>
+        <v>1904.057427205323</v>
       </c>
       <c r="E2">
         <v>-617.5</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08796688776944536</v>
+        <v>0.08795261237111252</v>
       </c>
       <c r="T2">
         <v>0.7107536019307608</v>
       </c>
       <c r="U2">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V2">
         <v>0.19</v>
       </c>
       <c r="W2">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08794371387261649</v>
+        <v>0.08791812559754046</v>
       </c>
       <c r="C3">
-        <v>1962.267652795008</v>
+        <v>1962.482019783637</v>
       </c>
       <c r="D3">
-        <v>1904.449652795008</v>
+        <v>1904.664019783637</v>
       </c>
       <c r="E3">
         <v>-597.918</v>
@@ -1533,37 +1533,37 @@
         <v>216.3</v>
       </c>
       <c r="M3">
-        <v>1.244891054971485</v>
+        <v>1.217476254971485</v>
       </c>
       <c r="N3">
-        <v>215.0551089450285</v>
+        <v>215.0825237450285</v>
       </c>
       <c r="O3">
-        <v>40.86047069955541</v>
+        <v>40.86567951155542</v>
       </c>
       <c r="P3">
-        <v>174.1946382454731</v>
+        <v>174.2168442334731</v>
       </c>
       <c r="Q3">
-        <v>286.2946382454731</v>
+        <v>286.3168442334731</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08831188957846811</v>
+        <v>0.08829749738142163</v>
       </c>
       <c r="T3">
         <v>0.7165688586738307</v>
       </c>
       <c r="U3">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V3">
         <v>0.19</v>
       </c>
       <c r="W3">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>173.7501439472986</v>
+        <v>177.6626025491282</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08792053997578758</v>
+        <v>0.08788363882396841</v>
       </c>
       <c r="C4">
-        <v>1943.093381967752</v>
+        <v>1943.506998980348</v>
       </c>
       <c r="D4">
-        <v>1904.857381967752</v>
+        <v>1905.270998980348</v>
       </c>
       <c r="E4">
         <v>-578.336</v>
@@ -1615,37 +1615,37 @@
         <v>216.3</v>
       </c>
       <c r="M4">
-        <v>2.489782109942971</v>
+        <v>2.434952509942971</v>
       </c>
       <c r="N4">
-        <v>213.810217890057</v>
+        <v>213.865047490057</v>
       </c>
       <c r="O4">
-        <v>40.62394139911083</v>
+        <v>40.63435902311083</v>
       </c>
       <c r="P4">
-        <v>173.1862764909462</v>
+        <v>173.2306884669462</v>
       </c>
       <c r="Q4">
-        <v>285.2862764909462</v>
+        <v>285.3306884669462</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08866393224073621</v>
+        <v>0.08864942086132888</v>
       </c>
       <c r="T4">
         <v>0.7225027941259428</v>
       </c>
       <c r="U4">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V4">
         <v>0.19</v>
       </c>
       <c r="W4">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.8750719736493</v>
+        <v>88.83130127456407</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08789736607895869</v>
+        <v>0.08784915205039634</v>
       </c>
       <c r="C5">
-        <v>1923.919285761733</v>
+        <v>1924.532365165199</v>
       </c>
       <c r="D5">
-        <v>1905.265285761733</v>
+        <v>1905.878365165199</v>
       </c>
       <c r="E5">
         <v>-558.754</v>
@@ -1697,37 +1697,37 @@
         <v>216.3</v>
       </c>
       <c r="M5">
-        <v>3.734673164914456</v>
+        <v>3.652428764914456</v>
       </c>
       <c r="N5">
-        <v>212.5653268350855</v>
+        <v>212.6475712350855</v>
       </c>
       <c r="O5">
-        <v>40.38741209866625</v>
+        <v>40.40303853466625</v>
       </c>
       <c r="P5">
-        <v>172.1779147364193</v>
+        <v>172.2445327004193</v>
       </c>
       <c r="Q5">
-        <v>284.2779147364192</v>
+        <v>284.3445327004193</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08902323351459746</v>
+        <v>0.08900860049546101</v>
       </c>
       <c r="T5">
         <v>0.7285590787626345</v>
       </c>
       <c r="U5">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V5">
         <v>0.19</v>
       </c>
       <c r="W5">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.91671464909953</v>
+        <v>59.22086751637605</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08787419218212979</v>
+        <v>0.08781466527682429</v>
       </c>
       <c r="C6">
-        <v>1904.745364289155</v>
+        <v>1905.558118708401</v>
       </c>
       <c r="D6">
-        <v>1905.673364289155</v>
+        <v>1906.4861187084</v>
       </c>
       <c r="E6">
         <v>-539.172</v>
@@ -1779,37 +1779,37 @@
         <v>216.3</v>
       </c>
       <c r="M6">
-        <v>4.979564219885941</v>
+        <v>4.869905019885941</v>
       </c>
       <c r="N6">
-        <v>211.3204357801141</v>
+        <v>211.430094980114</v>
       </c>
       <c r="O6">
-        <v>40.15088279822167</v>
+        <v>40.17171804622167</v>
       </c>
       <c r="P6">
-        <v>171.1695529818924</v>
+        <v>171.2583769338924</v>
       </c>
       <c r="Q6">
-        <v>283.2695529818924</v>
+        <v>283.3583769338924</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08939002023166415</v>
+        <v>0.08937526303863758</v>
       </c>
       <c r="T6">
         <v>0.7347415359959238</v>
       </c>
       <c r="U6">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V6">
         <v>0.19</v>
       </c>
       <c r="W6">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.43753598682465</v>
+        <v>44.41565063728203</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0878510182853009</v>
+        <v>0.08778017850325222</v>
       </c>
       <c r="C7">
-        <v>1885.571617662317</v>
+        <v>1886.584259980639</v>
       </c>
       <c r="D7">
-        <v>1906.081617662317</v>
+        <v>1907.094259980639</v>
       </c>
       <c r="E7">
         <v>-519.59</v>
@@ -1861,37 +1861,37 @@
         <v>216.3</v>
       </c>
       <c r="M7">
-        <v>6.224455274857427</v>
+        <v>6.087381274857427</v>
       </c>
       <c r="N7">
-        <v>210.0755447251425</v>
+        <v>210.2126187251426</v>
       </c>
       <c r="O7">
-        <v>39.91435349777709</v>
+        <v>39.94039755777709</v>
       </c>
       <c r="P7">
-        <v>170.1611912273655</v>
+        <v>170.2722211673655</v>
       </c>
       <c r="Q7">
-        <v>282.2611912273654</v>
+        <v>282.3722211673655</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0897645287743533</v>
+        <v>0.08974964479324943</v>
       </c>
       <c r="T7">
         <v>0.7410541502235984</v>
       </c>
       <c r="U7">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V7">
         <v>0.19</v>
       </c>
       <c r="W7">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.75002878945971</v>
+        <v>35.53252050982562</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08782784438847199</v>
+        <v>0.08774569172968015</v>
       </c>
       <c r="C8">
-        <v>1866.398045993616</v>
+        <v>1867.610789353073</v>
       </c>
       <c r="D8">
-        <v>1906.490045993616</v>
+        <v>1907.702789353073</v>
       </c>
       <c r="E8">
         <v>-500.008</v>
@@ -1943,37 +1943,37 @@
         <v>216.3</v>
       </c>
       <c r="M8">
-        <v>7.469346329828912</v>
+        <v>7.304857529828912</v>
       </c>
       <c r="N8">
-        <v>208.8306536701711</v>
+        <v>208.9951424701711</v>
       </c>
       <c r="O8">
-        <v>39.67782419733251</v>
+        <v>39.7090770693325</v>
       </c>
       <c r="P8">
-        <v>169.1528294728386</v>
+        <v>169.2860654008386</v>
       </c>
       <c r="Q8">
-        <v>281.2528294728386</v>
+        <v>281.3860654008386</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09014700558390817</v>
+        <v>0.09013199211710834</v>
       </c>
       <c r="T8">
         <v>0.7475010753922873</v>
       </c>
       <c r="U8">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V8">
         <v>0.19</v>
       </c>
       <c r="W8">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.95835732454977</v>
+        <v>29.61043375818802</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08780467049164312</v>
+        <v>0.0877112049561081</v>
       </c>
       <c r="C9">
-        <v>1847.224649395543</v>
+        <v>1848.637707197332</v>
       </c>
       <c r="D9">
-        <v>1906.898649395543</v>
+        <v>1908.311707197332</v>
       </c>
       <c r="E9">
         <v>-480.426</v>
@@ -2025,37 +2025,37 @@
         <v>216.3</v>
       </c>
       <c r="M9">
-        <v>8.714237384800397</v>
+        <v>8.522333784800397</v>
       </c>
       <c r="N9">
-        <v>207.5857626151996</v>
+        <v>207.7776662151996</v>
       </c>
       <c r="O9">
-        <v>39.44129489688792</v>
+        <v>39.47775658088792</v>
       </c>
       <c r="P9">
-        <v>168.1444677183117</v>
+        <v>168.2999096343117</v>
       </c>
       <c r="Q9">
-        <v>280.2444677183116</v>
+        <v>280.3999096343117</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09053770770119543</v>
+        <v>0.090522561964061</v>
       </c>
       <c r="T9">
         <v>0.7540866441129911</v>
       </c>
       <c r="U9">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V9">
         <v>0.19</v>
       </c>
       <c r="W9">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.82144913532838</v>
+        <v>25.38037179273259</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08778149659481423</v>
+        <v>0.08767671818253604</v>
       </c>
       <c r="C10">
-        <v>1828.051427980689</v>
+        <v>1829.665013885525</v>
       </c>
       <c r="D10">
-        <v>1907.307427980689</v>
+        <v>1908.921013885525</v>
       </c>
       <c r="E10">
         <v>-460.844</v>
@@ -2107,37 +2107,37 @@
         <v>216.3</v>
       </c>
       <c r="M10">
-        <v>9.959128439771883</v>
+        <v>9.739810039771882</v>
       </c>
       <c r="N10">
-        <v>206.3408715602281</v>
+        <v>206.5601899602281</v>
       </c>
       <c r="O10">
-        <v>39.20476559644334</v>
+        <v>39.24643609244334</v>
       </c>
       <c r="P10">
-        <v>167.1361059637848</v>
+        <v>167.3137538677848</v>
       </c>
       <c r="Q10">
-        <v>279.2361059637848</v>
+        <v>279.4137538677847</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09093690334277152</v>
+        <v>0.09092162245986046</v>
       </c>
       <c r="T10">
         <v>0.7608153773711014</v>
       </c>
       <c r="U10">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.71876799341232</v>
+        <v>22.20782531864102</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08775832269798534</v>
+        <v>0.08764223140896397</v>
       </c>
       <c r="C11">
-        <v>1808.878381861737</v>
+        <v>1810.692709790234</v>
       </c>
       <c r="D11">
-        <v>1907.716381861737</v>
+        <v>1909.530709790234</v>
       </c>
       <c r="E11">
         <v>-441.262</v>
@@ -2189,37 +2189,37 @@
         <v>216.3</v>
       </c>
       <c r="M11">
-        <v>11.20401949474337</v>
+        <v>10.95728629474337</v>
       </c>
       <c r="N11">
-        <v>205.0959805052566</v>
+        <v>205.3427137052566</v>
       </c>
       <c r="O11">
-        <v>38.96823629599876</v>
+        <v>39.01511560399876</v>
       </c>
       <c r="P11">
-        <v>166.1277442092579</v>
+        <v>166.3275981012578</v>
       </c>
       <c r="Q11">
-        <v>278.2277442092578</v>
+        <v>278.4275981012578</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0913448725149317</v>
+        <v>0.09132945351600713</v>
       </c>
       <c r="T11">
         <v>0.7676919948766425</v>
       </c>
       <c r="U11">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V11">
         <v>0.19</v>
       </c>
       <c r="W11">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.30557154969985</v>
+        <v>19.74028917212535</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08773514880115645</v>
+        <v>0.08760774463539192</v>
       </c>
       <c r="C12">
-        <v>1789.70551115147</v>
+        <v>1791.720795284516</v>
       </c>
       <c r="D12">
-        <v>1908.12551115147</v>
+        <v>1910.140795284515</v>
       </c>
       <c r="E12">
         <v>-421.6799999999999</v>
@@ -2271,37 +2271,37 @@
         <v>216.3</v>
       </c>
       <c r="M12">
-        <v>12.44891054971485</v>
+        <v>12.17476254971485</v>
       </c>
       <c r="N12">
-        <v>203.8510894502851</v>
+        <v>204.1252374502851</v>
       </c>
       <c r="O12">
-        <v>38.73170699555417</v>
+        <v>38.78379511555418</v>
       </c>
       <c r="P12">
-        <v>165.119382454731</v>
+        <v>165.341442334731</v>
       </c>
       <c r="Q12">
-        <v>277.219382454731</v>
+        <v>277.4414423347309</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09176190766869546</v>
+        <v>0.09174634748451266</v>
       </c>
       <c r="T12">
         <v>0.7747214261045293</v>
       </c>
       <c r="U12">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.37501439472986</v>
+        <v>17.76626025491281</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08771197490432754</v>
+        <v>0.08757325786181985</v>
       </c>
       <c r="C13">
-        <v>1770.532815962767</v>
+        <v>1772.749270741906</v>
       </c>
       <c r="D13">
-        <v>1908.534815962767</v>
+        <v>1910.751270741906</v>
       </c>
       <c r="E13">
         <v>-402.098</v>
@@ -2353,37 +2353,37 @@
         <v>216.3</v>
       </c>
       <c r="M13">
-        <v>13.69380160468634</v>
+        <v>13.39223880468634</v>
       </c>
       <c r="N13">
-        <v>202.6061983953136</v>
+        <v>202.9077611953136</v>
       </c>
       <c r="O13">
-        <v>38.49517769510959</v>
+        <v>38.55247462710959</v>
       </c>
       <c r="P13">
-        <v>164.1110207002041</v>
+        <v>164.3552865682041</v>
       </c>
       <c r="Q13">
-        <v>276.211020700204</v>
+        <v>276.4552865682041</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09218831439894827</v>
+        <v>0.09217260985680481</v>
       </c>
       <c r="T13">
         <v>0.7819088220791099</v>
       </c>
       <c r="U13">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.7954676315726</v>
+        <v>16.15114568628437</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08768880100749864</v>
+        <v>0.0875387710882478</v>
       </c>
       <c r="C14">
-        <v>1751.360296408604</v>
+        <v>1753.778136536418</v>
       </c>
       <c r="D14">
-        <v>1908.944296408604</v>
+        <v>1911.362136536418</v>
       </c>
       <c r="E14">
         <v>-382.516</v>
@@ -2435,37 +2435,37 @@
         <v>216.3</v>
       </c>
       <c r="M14">
-        <v>14.93869265965782</v>
+        <v>14.60971505965782</v>
       </c>
       <c r="N14">
-        <v>201.3613073403422</v>
+        <v>201.6902849403422</v>
       </c>
       <c r="O14">
-        <v>38.25864839466501</v>
+        <v>38.32115413866502</v>
       </c>
       <c r="P14">
-        <v>163.1026589456771</v>
+        <v>163.3691308016772</v>
       </c>
       <c r="Q14">
-        <v>275.2026589456772</v>
+        <v>275.4691308016771</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09262441219125228</v>
+        <v>0.09260856001028542</v>
       </c>
       <c r="T14">
         <v>0.7892595679622039</v>
       </c>
       <c r="U14">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V14">
         <v>0.19</v>
       </c>
       <c r="W14">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.47917866227488</v>
+        <v>14.80521687909401</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08766562711066976</v>
+        <v>0.08750428431467573</v>
       </c>
       <c r="C15">
-        <v>1732.187952602052</v>
+        <v>1734.807393042542</v>
       </c>
       <c r="D15">
-        <v>1909.353952602052</v>
+        <v>1911.973393042542</v>
       </c>
       <c r="E15">
         <v>-362.934</v>
@@ -2517,37 +2517,37 @@
         <v>216.3</v>
       </c>
       <c r="M15">
-        <v>16.18358371462931</v>
+        <v>15.82719131462931</v>
       </c>
       <c r="N15">
-        <v>200.1164162853707</v>
+        <v>200.4728086853707</v>
       </c>
       <c r="O15">
-        <v>38.02211909422043</v>
+        <v>38.08983365022043</v>
       </c>
       <c r="P15">
-        <v>162.0942971911502</v>
+        <v>162.3829750351503</v>
       </c>
       <c r="Q15">
-        <v>274.1942971911502</v>
+        <v>274.4829750351503</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09307053522016101</v>
+        <v>0.09305453200637477</v>
       </c>
       <c r="T15">
         <v>0.796779296509277</v>
       </c>
       <c r="U15">
-        <v>0.06357323332506819</v>
+        <v>0.06217323332506819</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.05149431899330523</v>
+        <v>0.05036031899330524</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.36539568825374</v>
+        <v>13.66635404224063</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08776719321384086</v>
+        <v>0.08763989754110366</v>
       </c>
       <c r="C16">
-        <v>1710.811821575111</v>
+        <v>1712.823984597249</v>
       </c>
       <c r="D16">
-        <v>1907.55982157511</v>
+        <v>1909.571984597249</v>
       </c>
       <c r="E16">
         <v>-343.352</v>
@@ -2599,37 +2599,37 @@
         <v>216.3</v>
       </c>
       <c r="M16">
-        <v>17.7300375696008</v>
+        <v>17.4558895696008</v>
       </c>
       <c r="N16">
-        <v>198.5699624303992</v>
+        <v>198.8441104303992</v>
       </c>
       <c r="O16">
-        <v>37.72829286177585</v>
+        <v>37.78038098177584</v>
       </c>
       <c r="P16">
-        <v>160.8416695686233</v>
+        <v>161.0637294486233</v>
       </c>
       <c r="Q16">
-        <v>272.9416695686233</v>
+        <v>273.1637294486234</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09352703320323039</v>
+        <v>0.09351087544423364</v>
       </c>
       <c r="T16">
         <v>0.8044739024644216</v>
       </c>
       <c r="U16">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.05238531899330524</v>
+        <v>0.05157531899330524</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.19963573968163</v>
+        <v>12.39123329335697</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08775292931701197</v>
+        <v>0.0876175607675316</v>
       </c>
       <c r="C17">
-        <v>1691.481584973816</v>
+        <v>1693.637104102941</v>
       </c>
       <c r="D17">
-        <v>1907.811584973816</v>
+        <v>1909.967104102941</v>
       </c>
       <c r="E17">
         <v>-323.77</v>
@@ -2681,37 +2681,37 @@
         <v>216.3</v>
       </c>
       <c r="M17">
-        <v>18.99646882457228</v>
+        <v>18.70273882457228</v>
       </c>
       <c r="N17">
-        <v>197.3035311754277</v>
+        <v>197.5972611754277</v>
       </c>
       <c r="O17">
-        <v>37.48767092333127</v>
+        <v>37.54347962333127</v>
       </c>
       <c r="P17">
-        <v>159.8158602520965</v>
+        <v>160.0537815520964</v>
       </c>
       <c r="Q17">
-        <v>271.9158602520964</v>
+        <v>272.1537815520965</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09399427231531315</v>
+        <v>0.09397795637474803</v>
       </c>
       <c r="T17">
         <v>0.8123495579714519</v>
       </c>
       <c r="U17">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.05238531899330524</v>
+        <v>0.05157531899330524</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.38632669036953</v>
+        <v>11.56515107379984</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08773866542018306</v>
+        <v>0.08759522399395955</v>
       </c>
       <c r="C18">
-        <v>1672.151414837725</v>
+        <v>1674.450387154952</v>
       </c>
       <c r="D18">
-        <v>1908.063414837725</v>
+        <v>1910.362387154952</v>
       </c>
       <c r="E18">
         <v>-304.188</v>
@@ -2763,37 +2763,37 @@
         <v>216.3</v>
       </c>
       <c r="M18">
-        <v>20.26290007954377</v>
+        <v>19.94958807954377</v>
       </c>
       <c r="N18">
-        <v>196.0370999204562</v>
+        <v>196.3504119204562</v>
       </c>
       <c r="O18">
-        <v>37.24704898488668</v>
+        <v>37.30657826488668</v>
       </c>
       <c r="P18">
-        <v>158.7900509355696</v>
+        <v>159.0438336555695</v>
       </c>
       <c r="Q18">
-        <v>270.8900509355695</v>
+        <v>271.1438336555696</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09447263616815979</v>
+        <v>0.09445615827979846</v>
       </c>
       <c r="T18">
         <v>0.8204127290857924</v>
       </c>
       <c r="U18">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.05238531899330524</v>
+        <v>0.05157531899330524</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.67468127222143</v>
+        <v>10.84232913168735</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08772440152335419</v>
+        <v>0.08757288722038749</v>
       </c>
       <c r="C19">
-        <v>1652.82131119316</v>
+        <v>1655.263833854844</v>
       </c>
       <c r="D19">
-        <v>1908.31531119316</v>
+        <v>1910.757833854844</v>
       </c>
       <c r="E19">
         <v>-284.606</v>
@@ -2845,37 +2845,37 @@
         <v>216.3</v>
       </c>
       <c r="M19">
-        <v>21.52933133451525</v>
+        <v>21.19643733451525</v>
       </c>
       <c r="N19">
-        <v>194.7706686654847</v>
+        <v>195.1035626654847</v>
       </c>
       <c r="O19">
-        <v>37.0064270464421</v>
+        <v>37.0696769064421</v>
       </c>
       <c r="P19">
-        <v>157.7642416190426</v>
+        <v>158.0338857590426</v>
       </c>
       <c r="Q19">
-        <v>269.8642416190426</v>
+        <v>270.1338857590426</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09496252686083409</v>
+        <v>0.09494588312232</v>
       </c>
       <c r="T19">
         <v>0.8286701934799967</v>
       </c>
       <c r="U19">
-        <v>0.06467323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.05238531899330524</v>
+        <v>0.05157531899330524</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.0467588444437</v>
+        <v>10.2045450651175</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08803089762652529</v>
+        <v>0.08779841044681543</v>
       </c>
       <c r="C20">
-        <v>1627.841275441261</v>
+        <v>1631.696708761607</v>
       </c>
       <c r="D20">
-        <v>1902.917275441261</v>
+        <v>1906.772708761607</v>
       </c>
       <c r="E20">
         <v>-265.024</v>
@@ -2927,37 +2927,37 @@
         <v>216.3</v>
       </c>
       <c r="M20">
-        <v>23.57120978948673</v>
+        <v>23.04249578948673</v>
       </c>
       <c r="N20">
-        <v>192.7287902105132</v>
+        <v>193.2575042105132</v>
       </c>
       <c r="O20">
-        <v>36.61847013999751</v>
+        <v>36.71892579999751</v>
       </c>
       <c r="P20">
-        <v>156.1103200705157</v>
+        <v>156.5385784105157</v>
       </c>
       <c r="Q20">
-        <v>268.2103200705158</v>
+        <v>268.6385784105157</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09546436610698822</v>
+        <v>0.0954475524731957</v>
       </c>
       <c r="T20">
         <v>0.8371290594447911</v>
       </c>
       <c r="U20">
-        <v>0.06687323332506818</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.05416731899330524</v>
+        <v>0.05295231899330523</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.176448809024407</v>
+        <v>9.387003993668431</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08803445372969639</v>
+        <v>0.08778984367324336</v>
       </c>
       <c r="C21">
-        <v>1608.196824257818</v>
+        <v>1612.265784824177</v>
       </c>
       <c r="D21">
-        <v>1902.854824257818</v>
+        <v>1906.923784824177</v>
       </c>
       <c r="E21">
         <v>-245.442</v>
@@ -3009,37 +3009,37 @@
         <v>216.3</v>
       </c>
       <c r="M21">
-        <v>24.88072144445822</v>
+        <v>24.32263444445822</v>
       </c>
       <c r="N21">
-        <v>191.4192785555418</v>
+        <v>191.9773655555418</v>
       </c>
       <c r="O21">
-        <v>36.36966292555294</v>
+        <v>36.47569945555294</v>
       </c>
       <c r="P21">
-        <v>155.0496156299888</v>
+        <v>155.5016660999888</v>
       </c>
       <c r="Q21">
-        <v>267.1496156299888</v>
+        <v>267.6016660999888</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09597859644563998</v>
+        <v>0.0959616087216239</v>
       </c>
       <c r="T21">
         <v>0.8457967862976052</v>
       </c>
       <c r="U21">
-        <v>0.06687323332506818</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V21">
         <v>0.19</v>
       </c>
       <c r="W21">
-        <v>0.05416731899330524</v>
+        <v>0.05295231899330523</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.693477819075756</v>
+        <v>8.89295115189641</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.0880380098328675</v>
+        <v>0.08778127689967131</v>
       </c>
       <c r="C22">
-        <v>1588.552377173369</v>
+        <v>1592.834884828546</v>
       </c>
       <c r="D22">
-        <v>1902.792377173369</v>
+        <v>1907.074884828546</v>
       </c>
       <c r="E22">
         <v>-225.86</v>
@@ -3091,37 +3091,37 @@
         <v>216.3</v>
       </c>
       <c r="M22">
-        <v>26.19023309942971</v>
+        <v>25.6027730994297</v>
       </c>
       <c r="N22">
-        <v>190.1097669005703</v>
+        <v>190.6972269005703</v>
       </c>
       <c r="O22">
-        <v>36.12085571110835</v>
+        <v>36.23247311110836</v>
       </c>
       <c r="P22">
-        <v>153.9889111894619</v>
+        <v>154.4647537894619</v>
       </c>
       <c r="Q22">
-        <v>266.0889111894619</v>
+        <v>266.5647537894619</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09650568254275807</v>
+        <v>0.09648851637626282</v>
       </c>
       <c r="T22">
         <v>0.8546812063217399</v>
       </c>
       <c r="U22">
-        <v>0.06687323332506818</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.05416731899330524</v>
+        <v>0.05295231899330523</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.258803928121964</v>
+        <v>8.448303594301589</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08804156593603861</v>
+        <v>0.08777271012609923</v>
       </c>
       <c r="C23">
-        <v>1568.907934187509</v>
+        <v>1573.404008780408</v>
       </c>
       <c r="D23">
-        <v>1902.729934187508</v>
+        <v>1907.226008780408</v>
       </c>
       <c r="E23">
         <v>-206.278</v>
@@ -3173,37 +3173,37 @@
         <v>216.3</v>
       </c>
       <c r="M23">
-        <v>27.49974475440119</v>
+        <v>26.88291175440119</v>
       </c>
       <c r="N23">
-        <v>188.8002552455988</v>
+        <v>189.4170882455988</v>
       </c>
       <c r="O23">
-        <v>35.87204849666377</v>
+        <v>35.98924676666377</v>
       </c>
       <c r="P23">
-        <v>152.928206748935</v>
+        <v>153.427841478935</v>
       </c>
       <c r="Q23">
-        <v>265.028206748935</v>
+        <v>265.527841478935</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0970461125917019</v>
+        <v>0.09702876346519637</v>
       </c>
       <c r="T23">
         <v>0.8637905483718018</v>
       </c>
       <c r="U23">
-        <v>0.06687323332506818</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V23">
         <v>0.19</v>
       </c>
       <c r="W23">
-        <v>0.05416731899330524</v>
+        <v>0.05295231899330523</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.86552755059235</v>
+        <v>8.04600342314437</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08831242203920969</v>
+        <v>0.08776414335252718</v>
       </c>
       <c r="C24">
-        <v>1544.581881432441</v>
+        <v>1553.973156685454</v>
       </c>
       <c r="D24">
-        <v>1897.985881432441</v>
+        <v>1907.377156685454</v>
       </c>
       <c r="E24">
         <v>-186.696</v>
@@ -3255,45 +3255,45 @@
         <v>216.3</v>
       </c>
       <c r="M24">
-        <v>29.45546240937268</v>
+        <v>28.16305040937268</v>
       </c>
       <c r="N24">
-        <v>186.8445375906273</v>
+        <v>188.1369495906273</v>
       </c>
       <c r="O24">
-        <v>35.50046214221919</v>
+        <v>35.74602042221919</v>
       </c>
       <c r="P24">
-        <v>151.3440754484081</v>
+        <v>152.3909291684081</v>
       </c>
       <c r="Q24">
-        <v>263.4440754484081</v>
+        <v>264.4909291684081</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09760039982138788</v>
+        <v>0.09758286304358976</v>
       </c>
       <c r="T24">
         <v>0.8731334632949422</v>
       </c>
       <c r="U24">
-        <v>0.06837323332506819</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.05538231899330524</v>
+        <v>0.05295231899330523</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.343289913220771</v>
+        <v>7.680275994819625</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08832812814238081</v>
+        <v>0.08790461657895511</v>
       </c>
       <c r="C25">
-        <v>1524.725514118321</v>
+        <v>1531.915737123129</v>
       </c>
       <c r="D25">
-        <v>1897.711514118321</v>
+        <v>1904.901737123129</v>
       </c>
       <c r="E25">
         <v>-167.114</v>
@@ -3337,37 +3337,37 @@
         <v>216.3</v>
       </c>
       <c r="M25">
-        <v>30.79434706434416</v>
+        <v>29.80349786434417</v>
       </c>
       <c r="N25">
-        <v>185.5056529356558</v>
+        <v>186.4965021356558</v>
       </c>
       <c r="O25">
-        <v>35.24607405777461</v>
+        <v>35.4343354057746</v>
       </c>
       <c r="P25">
-        <v>150.2595788778812</v>
+        <v>151.0621667298812</v>
       </c>
       <c r="Q25">
-        <v>262.3595788778812</v>
+        <v>263.1621667298812</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09816908412197481</v>
+        <v>0.09815135481882456</v>
       </c>
       <c r="T25">
         <v>0.8827190513329695</v>
       </c>
       <c r="U25">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.05538231899330524</v>
+        <v>0.05360031899330524</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.024016438732913</v>
+        <v>7.257537386535207</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08834383424555192</v>
+        <v>0.08790252980538305</v>
       </c>
       <c r="C26">
-        <v>1504.869226116215</v>
+        <v>1512.370463235856</v>
       </c>
       <c r="D26">
-        <v>1897.437226116215</v>
+        <v>1904.938463235856</v>
       </c>
       <c r="E26">
         <v>-147.532</v>
@@ -3419,37 +3419,37 @@
         <v>216.3</v>
       </c>
       <c r="M26">
-        <v>32.13323171931565</v>
+        <v>31.09930211931565</v>
       </c>
       <c r="N26">
-        <v>184.1667682806843</v>
+        <v>185.2006978806843</v>
       </c>
       <c r="O26">
-        <v>34.99168597333002</v>
+        <v>35.18813259733002</v>
       </c>
       <c r="P26">
-        <v>149.1750823073543</v>
+        <v>150.0125652833543</v>
       </c>
       <c r="Q26">
-        <v>261.2750823073543</v>
+        <v>262.1125652833543</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09875273379889297</v>
+        <v>0.09873480690393394</v>
       </c>
       <c r="T26">
         <v>0.892556891687787</v>
       </c>
       <c r="U26">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V26">
         <v>0.19</v>
       </c>
       <c r="W26">
-        <v>0.05538231899330524</v>
+        <v>0.05360031899330524</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.731349087119041</v>
+        <v>6.955139995429574</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08835954034872302</v>
+        <v>0.08790044303181101</v>
       </c>
       <c r="C27">
-        <v>1485.013017391741</v>
+        <v>1492.825190764753</v>
       </c>
       <c r="D27">
-        <v>1897.163017391741</v>
+        <v>1904.975190764753</v>
       </c>
       <c r="E27">
         <v>-127.95</v>
@@ -3501,37 +3501,37 @@
         <v>216.3</v>
       </c>
       <c r="M27">
-        <v>33.47211637428713</v>
+        <v>32.39510637428713</v>
       </c>
       <c r="N27">
-        <v>182.8278836257128</v>
+        <v>183.9048936257128</v>
       </c>
       <c r="O27">
-        <v>34.73729788888544</v>
+        <v>34.94192978888544</v>
       </c>
       <c r="P27">
-        <v>148.0905857368274</v>
+        <v>148.9629638368274</v>
       </c>
       <c r="Q27">
-        <v>260.1905857368274</v>
+        <v>261.0629638368274</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09935194746719561</v>
+        <v>0.09933381771131292</v>
       </c>
       <c r="T27">
         <v>0.9026570744520662</v>
       </c>
       <c r="U27">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.05538231899330524</v>
+        <v>0.05360031899330524</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.462095123634279</v>
+        <v>6.676934395612391</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08837524645189412</v>
+        <v>0.08789835625823893</v>
       </c>
       <c r="C28">
-        <v>1465.15688791053</v>
+        <v>1473.279919709904</v>
       </c>
       <c r="D28">
-        <v>1896.88888791053</v>
+        <v>1905.011919709904</v>
       </c>
       <c r="E28">
         <v>-108.368</v>
@@ -3583,37 +3583,37 @@
         <v>216.3</v>
       </c>
       <c r="M28">
-        <v>34.81100102925862</v>
+        <v>33.69091062925862</v>
       </c>
       <c r="N28">
-        <v>181.4889989707414</v>
+        <v>182.6090893707414</v>
       </c>
       <c r="O28">
-        <v>34.48290980444086</v>
+        <v>34.69572698044086</v>
       </c>
       <c r="P28">
-        <v>147.0060891663005</v>
+        <v>147.9133623903005</v>
       </c>
       <c r="Q28">
-        <v>259.1060891663005</v>
+        <v>260.0133623903005</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09996735609950644</v>
+        <v>0.09994901799997238</v>
       </c>
       <c r="T28">
         <v>0.9130302351288936</v>
       </c>
       <c r="U28">
-        <v>0.06837323332506819</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V28">
         <v>0.19</v>
       </c>
       <c r="W28">
-        <v>0.05538231899330524</v>
+        <v>0.05360031899330524</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.213553003494499</v>
+        <v>6.420129226550377</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08869713255506524</v>
+        <v>0.08789626948466686</v>
       </c>
       <c r="C29">
-        <v>1439.974184372777</v>
+        <v>1453.73465007139</v>
       </c>
       <c r="D29">
-        <v>1891.288184372777</v>
+        <v>1905.04865007139</v>
       </c>
       <c r="E29">
         <v>-88.78599999999994</v>
@@ -3665,45 +3665,45 @@
         <v>216.3</v>
       </c>
       <c r="M29">
-        <v>36.8900852842301</v>
+        <v>34.98671488423011</v>
       </c>
       <c r="N29">
-        <v>179.4099147157699</v>
+        <v>181.3132851157699</v>
       </c>
       <c r="O29">
-        <v>34.08788379599628</v>
+        <v>34.44952417199627</v>
       </c>
       <c r="P29">
-        <v>145.3220309197736</v>
+        <v>146.8637609437736</v>
       </c>
       <c r="Q29">
-        <v>257.4220309197736</v>
+        <v>258.9637609437736</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1005996252422915</v>
+        <v>0.1005810730910609</v>
       </c>
       <c r="T29">
         <v>0.9236875919886476</v>
       </c>
       <c r="U29">
-        <v>0.06977323332506818</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V29">
         <v>0.19</v>
       </c>
       <c r="W29">
-        <v>0.05651631899330523</v>
+        <v>0.05360031899330524</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.863364053876682</v>
+        <v>6.182346662604065</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08872417865823633</v>
+        <v>0.08812098271109479</v>
       </c>
       <c r="C30">
-        <v>1419.923097644694</v>
+        <v>1430.20547752167</v>
       </c>
       <c r="D30">
-        <v>1890.819097644694</v>
+        <v>1901.10147752167</v>
       </c>
       <c r="E30">
         <v>-69.20399999999995</v>
@@ -3747,37 +3747,37 @@
         <v>216.3</v>
       </c>
       <c r="M30">
-        <v>38.25638473920159</v>
+        <v>36.83081513920159</v>
       </c>
       <c r="N30">
-        <v>178.0436152607984</v>
+        <v>179.4691848607984</v>
       </c>
       <c r="O30">
-        <v>33.82828689955169</v>
+        <v>34.0991451235517</v>
       </c>
       <c r="P30">
-        <v>144.2153283612467</v>
+        <v>145.3700397372467</v>
       </c>
       <c r="Q30">
-        <v>256.3153283612467</v>
+        <v>257.4700397372467</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1012494574168206</v>
+        <v>0.101230685268013</v>
       </c>
       <c r="T30">
         <v>0.9346409865389503</v>
       </c>
       <c r="U30">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.653958194809658</v>
+        <v>5.872799697277862</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08875122476140744</v>
+        <v>0.08812699593752274</v>
       </c>
       <c r="C31">
-        <v>1399.872243549372</v>
+        <v>1410.5180776253</v>
       </c>
       <c r="D31">
-        <v>1890.350243549372</v>
+        <v>1900.9960776253</v>
       </c>
       <c r="E31">
         <v>-49.62200000000007</v>
@@ -3829,37 +3829,37 @@
         <v>216.3</v>
       </c>
       <c r="M31">
-        <v>39.62268419417307</v>
+        <v>38.14620139417307</v>
       </c>
       <c r="N31">
-        <v>176.6773158058269</v>
+        <v>178.1537986058269</v>
       </c>
       <c r="O31">
-        <v>33.56869000310711</v>
+        <v>33.84922173510711</v>
       </c>
       <c r="P31">
-        <v>143.1086258027198</v>
+        <v>144.3045768707198</v>
       </c>
       <c r="Q31">
-        <v>255.2086258027198</v>
+        <v>256.4045768707198</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1019175947230267</v>
+        <v>0.1018985963795271</v>
       </c>
       <c r="T31">
         <v>0.9459029274146138</v>
       </c>
       <c r="U31">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V31">
         <v>0.19</v>
       </c>
       <c r="W31">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.458994119126568</v>
+        <v>5.670289362888971</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08877827086457854</v>
+        <v>0.08813300916395068</v>
       </c>
       <c r="C32">
-        <v>1379.821621913801</v>
+        <v>1390.830689415336</v>
       </c>
       <c r="D32">
-        <v>1889.8816219138</v>
+        <v>1900.890689415336</v>
       </c>
       <c r="E32">
         <v>-30.03999999999996</v>
@@ -3911,37 +3911,37 @@
         <v>216.3</v>
       </c>
       <c r="M32">
-        <v>40.98898364914456</v>
+        <v>39.46158764914456</v>
       </c>
       <c r="N32">
-        <v>175.3110163508554</v>
+        <v>176.8384123508554</v>
       </c>
       <c r="O32">
-        <v>33.30909310666253</v>
+        <v>33.59929834666254</v>
       </c>
       <c r="P32">
-        <v>142.0019232441929</v>
+        <v>143.2391140041929</v>
       </c>
       <c r="Q32">
-        <v>254.1019232441929</v>
+        <v>255.3391140041929</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1026048216665528</v>
+        <v>0.1025855906656559</v>
       </c>
       <c r="T32">
         <v>0.957486638029582</v>
       </c>
       <c r="U32">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.277027648489015</v>
+        <v>5.481279717459338</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08880531696774965</v>
+        <v>0.08813902239037862</v>
       </c>
       <c r="C33">
-        <v>1359.771232565141</v>
+        <v>1371.143312889835</v>
       </c>
       <c r="D33">
-        <v>1889.41323256514</v>
+        <v>1900.785312889835</v>
       </c>
       <c r="E33">
         <v>-10.45799999999997</v>
@@ -3993,37 +3993,37 @@
         <v>216.3</v>
       </c>
       <c r="M33">
-        <v>42.35528310411604</v>
+        <v>40.77697390411605</v>
       </c>
       <c r="N33">
-        <v>173.9447168958839</v>
+        <v>175.5230260958839</v>
       </c>
       <c r="O33">
-        <v>33.04949621021795</v>
+        <v>33.34937495821795</v>
       </c>
       <c r="P33">
-        <v>140.895220685666</v>
+        <v>142.173651137666</v>
       </c>
       <c r="Q33">
-        <v>252.995220685666</v>
+        <v>254.273651137666</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1033119682316305</v>
+        <v>0.1032924978296435</v>
       </c>
       <c r="T33">
         <v>0.9694061083725203</v>
       </c>
       <c r="U33">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V33">
         <v>0.19</v>
       </c>
       <c r="W33">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.10680095015066</v>
+        <v>5.304464242702585</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08883236307092077</v>
+        <v>0.08814503561680656</v>
       </c>
       <c r="C34">
-        <v>1339.721075330724</v>
+        <v>1351.455948046854</v>
       </c>
       <c r="D34">
-        <v>1888.945075330724</v>
+        <v>1900.679948046854</v>
       </c>
       <c r="E34">
         <v>9.124000000000024</v>
@@ -4075,37 +4075,37 @@
         <v>216.3</v>
       </c>
       <c r="M34">
-        <v>43.72158255908753</v>
+        <v>42.09236015908753</v>
       </c>
       <c r="N34">
-        <v>172.5784174409125</v>
+        <v>174.2076398409125</v>
       </c>
       <c r="O34">
-        <v>32.78989931377337</v>
+        <v>33.09945156977337</v>
       </c>
       <c r="P34">
-        <v>139.7885181271391</v>
+        <v>141.1081882711391</v>
       </c>
       <c r="Q34">
-        <v>251.8885181271391</v>
+        <v>253.2081882711391</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1040399132250928</v>
+        <v>0.1040201963808072</v>
       </c>
       <c r="T34">
         <v>0.9816761513726038</v>
       </c>
       <c r="U34">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.947213420458452</v>
+        <v>5.138699735118129</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08885940917409187</v>
+        <v>0.08815104884323449</v>
       </c>
       <c r="C35">
-        <v>1319.671150038057</v>
+        <v>1331.768594884451</v>
       </c>
       <c r="D35">
-        <v>1888.477150038056</v>
+        <v>1900.574594884451</v>
       </c>
       <c r="E35">
         <v>28.70600000000002</v>
@@ -4157,37 +4157,37 @@
         <v>216.3</v>
       </c>
       <c r="M35">
-        <v>45.08788201405901</v>
+        <v>43.40774641405902</v>
       </c>
       <c r="N35">
-        <v>171.212117985941</v>
+        <v>172.892253585941</v>
       </c>
       <c r="O35">
-        <v>32.53030241732878</v>
+        <v>32.84952818132879</v>
       </c>
       <c r="P35">
-        <v>138.6818155686122</v>
+        <v>140.0427254046122</v>
       </c>
       <c r="Q35">
-        <v>250.7818155686122</v>
+        <v>252.1427254046122</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1047895879198525</v>
+        <v>0.1047696172767817</v>
       </c>
       <c r="T35">
         <v>0.9943124643129883</v>
       </c>
       <c r="U35">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V35">
         <v>0.19</v>
       </c>
       <c r="W35">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.797297862262742</v>
+        <v>4.982981561326671</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08888645527726297</v>
+        <v>0.08815706206966244</v>
       </c>
       <c r="C36">
-        <v>1299.62145651481</v>
+        <v>1312.081253400682</v>
       </c>
       <c r="D36">
-        <v>1888.00945651481</v>
+        <v>1900.469253400682</v>
       </c>
       <c r="E36">
         <v>48.28800000000001</v>
@@ -4239,37 +4239,37 @@
         <v>216.3</v>
       </c>
       <c r="M36">
-        <v>46.45418146903049</v>
+        <v>44.72313266903051</v>
       </c>
       <c r="N36">
-        <v>169.8458185309695</v>
+        <v>171.5768673309695</v>
       </c>
       <c r="O36">
-        <v>32.27070552088421</v>
+        <v>32.5996047928842</v>
       </c>
       <c r="P36">
-        <v>137.5751130100853</v>
+        <v>138.9772625380853</v>
       </c>
       <c r="Q36">
-        <v>249.6751130100853</v>
+        <v>251.0772625380853</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1055619800296048</v>
+        <v>0.1055417478968768</v>
       </c>
       <c r="T36">
         <v>1.007331695827324</v>
       </c>
       <c r="U36">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.656200866313837</v>
+        <v>4.83642328011118</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08891350138043408</v>
+        <v>0.08816307529609037</v>
       </c>
       <c r="C37">
-        <v>1279.57199458883</v>
+        <v>1292.393923593607</v>
       </c>
       <c r="D37">
-        <v>1887.54199458883</v>
+        <v>1900.363923593607</v>
       </c>
       <c r="E37">
         <v>67.87000000000012</v>
@@ -4321,37 +4321,37 @@
         <v>216.3</v>
       </c>
       <c r="M37">
-        <v>47.82048092400199</v>
+        <v>46.038518924002</v>
       </c>
       <c r="N37">
-        <v>168.479519075998</v>
+        <v>170.261481075998</v>
       </c>
       <c r="O37">
-        <v>32.01110862443961</v>
+        <v>32.34968140443961</v>
       </c>
       <c r="P37">
-        <v>136.4684104515584</v>
+        <v>137.9117996715584</v>
       </c>
       <c r="Q37">
-        <v>248.5684104515584</v>
+        <v>250.0117996715584</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1063581380504265</v>
+        <v>0.1063376363822054</v>
       </c>
       <c r="T37">
         <v>1.020751519080562</v>
       </c>
       <c r="U37">
-        <v>0.06977323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.05651631899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.523166555847727</v>
+        <v>4.698239757822288</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08969870748360519</v>
+        <v>0.08816908852251831</v>
       </c>
       <c r="C38">
-        <v>1246.518771373694</v>
+        <v>1272.706605461283</v>
       </c>
       <c r="D38">
-        <v>1874.070771373694</v>
+        <v>1900.258605461283</v>
       </c>
       <c r="E38">
         <v>87.452</v>
@@ -4403,45 +4403,45 @@
         <v>216.3</v>
       </c>
       <c r="M38">
-        <v>51.01965557897346</v>
+        <v>47.35390517897347</v>
       </c>
       <c r="N38">
-        <v>165.2803444210265</v>
+        <v>168.9460948210265</v>
       </c>
       <c r="O38">
-        <v>31.40326543999504</v>
+        <v>32.09975801599504</v>
       </c>
       <c r="P38">
-        <v>133.8770789810315</v>
+        <v>136.8463368050315</v>
       </c>
       <c r="Q38">
-        <v>245.9770789810315</v>
+        <v>248.9463368050315</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1071791760093989</v>
+        <v>0.1071583963827007</v>
       </c>
       <c r="T38">
         <v>1.034590711810464</v>
       </c>
       <c r="U38">
-        <v>0.07237323332506818</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V38">
         <v>0.19</v>
       </c>
       <c r="W38">
-        <v>0.05862231899330523</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.239542536017097</v>
+        <v>4.567733097882781</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08974681358677629</v>
+        <v>0.08892435174894624</v>
       </c>
       <c r="C39">
-        <v>1226.117697532177</v>
+        <v>1239.988781754145</v>
       </c>
       <c r="D39">
-        <v>1873.251697532177</v>
+        <v>1887.122781754145</v>
       </c>
       <c r="E39">
         <v>107.034</v>
@@ -4485,37 +4485,37 @@
         <v>216.3</v>
       </c>
       <c r="M39">
-        <v>52.43686823394494</v>
+        <v>50.48062643394495</v>
       </c>
       <c r="N39">
-        <v>163.863131766055</v>
+        <v>165.819373566055</v>
       </c>
       <c r="O39">
-        <v>31.13399503555046</v>
+        <v>31.50568097755046</v>
       </c>
       <c r="P39">
-        <v>132.7291367305046</v>
+        <v>134.3136925885046</v>
       </c>
       <c r="Q39">
-        <v>244.8291367305046</v>
+        <v>246.4136925885046</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1080262786654815</v>
+        <v>0.1080052122562275</v>
       </c>
       <c r="T39">
         <v>1.048869243992108</v>
       </c>
       <c r="U39">
-        <v>0.07237323332506818</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V39">
         <v>0.19</v>
       </c>
       <c r="W39">
-        <v>0.05862231899330523</v>
+        <v>0.05643531899330523</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.124960305313932</v>
+        <v>4.284812120606972</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08979491968994739</v>
+        <v>0.08895061497537418</v>
       </c>
       <c r="C40">
-        <v>1205.717339340126</v>
+        <v>1219.953268361074</v>
       </c>
       <c r="D40">
-        <v>1872.433339340126</v>
+        <v>1886.669268361074</v>
       </c>
       <c r="E40">
         <v>126.616</v>
@@ -4567,37 +4567,37 @@
         <v>216.3</v>
       </c>
       <c r="M40">
-        <v>53.85408088891643</v>
+        <v>51.84496768891643</v>
       </c>
       <c r="N40">
-        <v>162.4459191110836</v>
+        <v>164.4550323110836</v>
       </c>
       <c r="O40">
-        <v>30.86472463110588</v>
+        <v>31.24645613910588</v>
       </c>
       <c r="P40">
-        <v>131.5811944799777</v>
+        <v>133.2085761719777</v>
       </c>
       <c r="Q40">
-        <v>243.6811944799777</v>
+        <v>245.3085761719777</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1089007072136958</v>
+        <v>0.1088793447708358</v>
       </c>
       <c r="T40">
         <v>1.063608373986064</v>
       </c>
       <c r="U40">
-        <v>0.07237323332506818</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V40">
         <v>0.19</v>
       </c>
       <c r="W40">
-        <v>0.05862231899330523</v>
+        <v>0.05643531899330523</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.016408718331987</v>
+        <v>4.172053906906788</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09069595579311851</v>
+        <v>0.08897687820180211</v>
       </c>
       <c r="C41">
-        <v>1170.93838713157</v>
+        <v>1199.91797289233</v>
       </c>
       <c r="D41">
-        <v>1857.23638713157</v>
+        <v>1886.21597289233</v>
       </c>
       <c r="E41">
         <v>146.1980000000001</v>
@@ -4649,45 +4649,45 @@
         <v>216.3</v>
       </c>
       <c r="M41">
-        <v>57.33327814388793</v>
+        <v>53.20930894388793</v>
       </c>
       <c r="N41">
-        <v>158.9667218561121</v>
+        <v>163.0906910561121</v>
       </c>
       <c r="O41">
-        <v>30.20367715266129</v>
+        <v>30.98723130066129</v>
       </c>
       <c r="P41">
-        <v>128.7630447034508</v>
+        <v>132.1034597554508</v>
       </c>
       <c r="Q41">
-        <v>240.8630447034508</v>
+        <v>244.2034597554508</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1098038055503762</v>
+        <v>0.1097821373678903</v>
       </c>
       <c r="T41">
         <v>1.078830754143757</v>
       </c>
       <c r="U41">
-        <v>0.07507323332506818</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V41">
         <v>0.19</v>
       </c>
       <c r="W41">
-        <v>0.06080931899330523</v>
+        <v>0.05643531899330523</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.772678050209464</v>
+        <v>4.065078165704049</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09076593189628961</v>
+        <v>0.09013714142823007</v>
       </c>
       <c r="C42">
-        <v>1150.186480450684</v>
+        <v>1160.525264601042</v>
       </c>
       <c r="D42">
-        <v>1856.066480450684</v>
+        <v>1866.405264601042</v>
       </c>
       <c r="E42">
         <v>165.7800000000001</v>
@@ -4731,37 +4731,37 @@
         <v>216.3</v>
       </c>
       <c r="M42">
-        <v>58.80336219885941</v>
+        <v>57.31513019885941</v>
       </c>
       <c r="N42">
-        <v>157.4966378011406</v>
+        <v>158.9848698011406</v>
       </c>
       <c r="O42">
-        <v>29.92436118221671</v>
+        <v>30.20712526221671</v>
       </c>
       <c r="P42">
-        <v>127.5722766189239</v>
+        <v>128.7777445389239</v>
       </c>
       <c r="Q42">
-        <v>239.6722766189239</v>
+        <v>240.8777445389238</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1107370071649459</v>
+        <v>0.1107150230515133</v>
       </c>
       <c r="T42">
         <v>1.094560546973372</v>
       </c>
       <c r="U42">
-        <v>0.07507323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V42">
         <v>0.19</v>
       </c>
       <c r="W42">
-        <v>0.06080931899330523</v>
+        <v>0.05927031899330523</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.678361098954227</v>
+        <v>3.773872610068753</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09083590799946072</v>
+        <v>0.09019175465465799</v>
       </c>
       <c r="C43">
-        <v>1129.436046732568</v>
+        <v>1140.021030463104</v>
       </c>
       <c r="D43">
-        <v>1854.898046732568</v>
+        <v>1865.483030463104</v>
       </c>
       <c r="E43">
         <v>185.3620000000001</v>
@@ -4813,37 +4813,37 @@
         <v>216.3</v>
       </c>
       <c r="M43">
-        <v>60.2734462538309</v>
+        <v>58.7480084538309</v>
       </c>
       <c r="N43">
-        <v>156.0265537461691</v>
+        <v>157.5519915461691</v>
       </c>
       <c r="O43">
-        <v>29.64504521177213</v>
+        <v>29.93487839377213</v>
       </c>
       <c r="P43">
-        <v>126.381508534397</v>
+        <v>127.617113152397</v>
       </c>
       <c r="Q43">
-        <v>238.481508534397</v>
+        <v>239.717113152397</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1117018427325518</v>
+        <v>0.1116795319786489</v>
       </c>
       <c r="T43">
         <v>1.110823553119245</v>
       </c>
       <c r="U43">
-        <v>0.07507323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.06080931899330523</v>
+        <v>0.05927031899330523</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.58864497458949</v>
+        <v>3.681826936652442</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09090588410263184</v>
+        <v>0.09024636788108595</v>
       </c>
       <c r="C44">
-        <v>1108.687083197188</v>
+        <v>1119.51770726961</v>
       </c>
       <c r="D44">
-        <v>1853.731083197188</v>
+        <v>1864.56170726961</v>
       </c>
       <c r="E44">
         <v>204.944</v>
@@ -4895,37 +4895,37 @@
         <v>216.3</v>
       </c>
       <c r="M44">
-        <v>61.74353030880238</v>
+        <v>60.18088670880238</v>
       </c>
       <c r="N44">
-        <v>154.5564696911976</v>
+        <v>156.1191132911976</v>
       </c>
       <c r="O44">
-        <v>29.36572924132755</v>
+        <v>29.66263152532754</v>
       </c>
       <c r="P44">
-        <v>125.1907404498701</v>
+        <v>126.4564817658701</v>
       </c>
       <c r="Q44">
-        <v>237.29074044987</v>
+        <v>238.55648176587</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1126999484921442</v>
+        <v>0.1126772998343064</v>
       </c>
       <c r="T44">
         <v>1.127647352580493</v>
       </c>
       <c r="U44">
-        <v>0.07507323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V44">
         <v>0.19</v>
       </c>
       <c r="W44">
-        <v>0.06080931899330523</v>
+        <v>0.05927031899330523</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.503201046623074</v>
+        <v>3.59416439054167</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09261287020580294</v>
+        <v>0.09030098110751389</v>
       </c>
       <c r="C45">
-        <v>1061.086265427648</v>
+        <v>1099.015293671537</v>
       </c>
       <c r="D45">
-        <v>1825.712265427648</v>
+        <v>1863.641293671537</v>
       </c>
       <c r="E45">
         <v>224.526</v>
@@ -4977,45 +4977,45 @@
         <v>216.3</v>
       </c>
       <c r="M45">
-        <v>67.17113656377387</v>
+        <v>61.61376496377386</v>
       </c>
       <c r="N45">
-        <v>149.1288634362261</v>
+        <v>154.6862350362261</v>
       </c>
       <c r="O45">
-        <v>28.33448405288296</v>
+        <v>29.39038465688296</v>
       </c>
       <c r="P45">
-        <v>120.7943793833432</v>
+        <v>125.2958503793432</v>
       </c>
       <c r="Q45">
-        <v>232.8943793833432</v>
+        <v>237.3958503793432</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1137330755064591</v>
+        <v>0.1137100770884081</v>
       </c>
       <c r="T45">
         <v>1.145061460794768</v>
       </c>
       <c r="U45">
-        <v>0.07977323332506819</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V45">
         <v>0.19</v>
       </c>
       <c r="W45">
-        <v>0.06461631899330524</v>
+        <v>0.05927031899330523</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.220133096819638</v>
+        <v>3.51057917215698</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09272091630897406</v>
+        <v>0.09135351433394183</v>
       </c>
       <c r="C46">
-        <v>1039.759250151357</v>
+        <v>1061.870467524373</v>
       </c>
       <c r="D46">
-        <v>1823.967250151357</v>
+        <v>1846.078467524374</v>
       </c>
       <c r="E46">
         <v>244.1080000000001</v>
@@ -5059,37 +5059,37 @@
         <v>216.3</v>
       </c>
       <c r="M46">
-        <v>68.73325601874537</v>
+        <v>65.45914561874535</v>
       </c>
       <c r="N46">
-        <v>147.5667439812546</v>
+        <v>150.8408543812546</v>
       </c>
       <c r="O46">
-        <v>28.03768135643838</v>
+        <v>28.65976233243838</v>
       </c>
       <c r="P46">
-        <v>119.5290626248162</v>
+        <v>122.1810920488163</v>
       </c>
       <c r="Q46">
-        <v>231.6290626248162</v>
+        <v>234.2810920488162</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1148030999141424</v>
+        <v>0.114779739244442</v>
       </c>
       <c r="T46">
         <v>1.163097501445266</v>
       </c>
       <c r="U46">
-        <v>0.07977323332506819</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.06461631899330524</v>
+        <v>0.06153831899330523</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.1469482537101</v>
+        <v>3.304351102591519</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09282896241214514</v>
+        <v>0.09143080756036975</v>
       </c>
       <c r="C47">
-        <v>1018.435567460015</v>
+        <v>1041.011771792957</v>
       </c>
       <c r="D47">
-        <v>1822.225567460015</v>
+        <v>1844.801771792957</v>
       </c>
       <c r="E47">
         <v>263.6900000000001</v>
@@ -5141,37 +5141,37 @@
         <v>216.3</v>
       </c>
       <c r="M47">
-        <v>70.29537547371685</v>
+        <v>66.94685347371683</v>
       </c>
       <c r="N47">
-        <v>146.0046245262831</v>
+        <v>149.3531465262832</v>
       </c>
       <c r="O47">
-        <v>27.74087865999379</v>
+        <v>28.3770978399938</v>
       </c>
       <c r="P47">
-        <v>118.2637458662893</v>
+        <v>120.9760486862894</v>
       </c>
       <c r="Q47">
-        <v>230.3637458662893</v>
+        <v>233.0760486862894</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1159120343002869</v>
+        <v>0.1158882982061498</v>
       </c>
       <c r="T47">
         <v>1.181789398119419</v>
       </c>
       <c r="U47">
-        <v>0.07977323332506819</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V47">
         <v>0.19</v>
       </c>
       <c r="W47">
-        <v>0.06461631899330524</v>
+        <v>0.06153831899330523</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.077016070294321</v>
+        <v>3.230921078089485</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09293700851531625</v>
+        <v>0.09150810078679769</v>
       </c>
       <c r="C48">
-        <v>997.1152078160027</v>
+        <v>1020.154840694594</v>
       </c>
       <c r="D48">
-        <v>1820.487207816003</v>
+        <v>1843.526840694594</v>
       </c>
       <c r="E48">
         <v>283.272</v>
@@ -5223,37 +5223,37 @@
         <v>216.3</v>
       </c>
       <c r="M48">
-        <v>71.85749492868833</v>
+        <v>68.43456132868832</v>
       </c>
       <c r="N48">
-        <v>144.4425050713116</v>
+        <v>147.8654386713117</v>
       </c>
       <c r="O48">
-        <v>27.44407596354921</v>
+        <v>28.09443334754922</v>
       </c>
       <c r="P48">
-        <v>116.9984291077624</v>
+        <v>119.7710053237625</v>
       </c>
       <c r="Q48">
-        <v>229.0984291077624</v>
+        <v>231.8710053237625</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1170620403303627</v>
+        <v>0.1170379149071802</v>
       </c>
       <c r="T48">
         <v>1.201173587262986</v>
       </c>
       <c r="U48">
-        <v>0.07977323332506819</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V48">
         <v>0.19</v>
       </c>
       <c r="W48">
-        <v>0.06461631899330524</v>
+        <v>0.06153831899330523</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.01012441659227</v>
+        <v>3.160683663348409</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09658556461848736</v>
+        <v>0.09158539401322563</v>
       </c>
       <c r="C49">
-        <v>920.7176658405492</v>
+        <v>999.2996705732287</v>
       </c>
       <c r="D49">
-        <v>1763.671665840549</v>
+        <v>1842.253670573229</v>
       </c>
       <c r="E49">
         <v>302.854</v>
@@ -5305,45 +5305,45 @@
         <v>216.3</v>
       </c>
       <c r="M49">
-        <v>81.97890658365981</v>
+        <v>69.92226918365981</v>
       </c>
       <c r="N49">
-        <v>134.3210934163402</v>
+        <v>146.3777308163402</v>
       </c>
       <c r="O49">
-        <v>25.52100774910463</v>
+        <v>27.81176885510463</v>
       </c>
       <c r="P49">
-        <v>108.8000856672355</v>
+        <v>118.5659619612355</v>
       </c>
       <c r="Q49">
-        <v>220.9000856672355</v>
+        <v>230.6659619612356</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1182554428144036</v>
+        <v>0.1182309133705135</v>
       </c>
       <c r="T49">
         <v>1.221289255242158</v>
       </c>
       <c r="U49">
-        <v>0.08907323332506818</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V49">
         <v>0.19</v>
       </c>
       <c r="W49">
-        <v>0.07214931899330523</v>
+        <v>0.06153831899330523</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.638483593084581</v>
+        <v>3.093435074766528</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09676894072165847</v>
+        <v>0.09166268723965358</v>
       </c>
       <c r="C50">
-        <v>898.3735729022484</v>
+        <v>978.4462577829003</v>
       </c>
       <c r="D50">
-        <v>1760.909572902248</v>
+        <v>1840.9822577829</v>
       </c>
       <c r="E50">
         <v>322.436</v>
@@ -5387,45 +5387,45 @@
         <v>216.3</v>
       </c>
       <c r="M50">
-        <v>83.72313863863128</v>
+        <v>71.40997703863128</v>
       </c>
       <c r="N50">
-        <v>132.5768613613687</v>
+        <v>144.8900229613687</v>
       </c>
       <c r="O50">
-        <v>25.18960365866005</v>
+        <v>27.52910436266005</v>
       </c>
       <c r="P50">
-        <v>107.3872577027086</v>
+        <v>117.3609185987086</v>
       </c>
       <c r="Q50">
-        <v>219.4872577027086</v>
+        <v>229.4609185987086</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1194947453939845</v>
+        <v>0.119469796390129</v>
       </c>
       <c r="T50">
         <v>1.242178602758991</v>
       </c>
       <c r="U50">
-        <v>0.08907323332506818</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V50">
         <v>0.19</v>
       </c>
       <c r="W50">
-        <v>0.07214931899330523</v>
+        <v>0.06153831899330523</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.58351518489532</v>
+        <v>3.028988510708893</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09695231682482958</v>
+        <v>0.09483580046608152</v>
       </c>
       <c r="C51">
-        <v>876.0381178846869</v>
+        <v>908.1421351536778</v>
       </c>
       <c r="D51">
-        <v>1758.156117884687</v>
+        <v>1790.260135153678</v>
       </c>
       <c r="E51">
         <v>342.018</v>
@@ -5469,37 +5469,37 @@
         <v>216.3</v>
       </c>
       <c r="M51">
-        <v>85.46737069360277</v>
+        <v>80.38192529360279</v>
       </c>
       <c r="N51">
-        <v>130.8326293063972</v>
+        <v>135.9180747063972</v>
       </c>
       <c r="O51">
-        <v>24.85819956821547</v>
+        <v>25.82443419421547</v>
       </c>
       <c r="P51">
-        <v>105.9744297381818</v>
+        <v>110.0936405121817</v>
       </c>
       <c r="Q51">
-        <v>218.0744297381817</v>
+        <v>222.1936405121817</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1207826480747255</v>
+        <v>0.1207572630575725</v>
       </c>
       <c r="T51">
         <v>1.263887140374524</v>
       </c>
       <c r="U51">
-        <v>0.08907323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.07214931899330523</v>
+        <v>0.06785631899330524</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.530790385203578</v>
+        <v>2.690903448877882</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09903919292800067</v>
+        <v>0.09497627369250945</v>
       </c>
       <c r="C52">
-        <v>825.7169550223529</v>
+        <v>886.3792009866889</v>
       </c>
       <c r="D52">
-        <v>1727.416955022353</v>
+        <v>1788.079200986689</v>
       </c>
       <c r="E52">
         <v>361.6</v>
@@ -5551,45 +5551,45 @@
         <v>216.3</v>
       </c>
       <c r="M52">
-        <v>91.81337274857425</v>
+        <v>82.02237274857427</v>
       </c>
       <c r="N52">
-        <v>124.4866272514257</v>
+        <v>134.2776272514257</v>
       </c>
       <c r="O52">
-        <v>23.65245917777089</v>
+        <v>25.51274917777089</v>
       </c>
       <c r="P52">
-        <v>100.8341680736548</v>
+        <v>108.7648780736548</v>
       </c>
       <c r="Q52">
-        <v>212.9341680736548</v>
+        <v>220.8648780736548</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1221220668626961</v>
+        <v>0.1220962283917137</v>
       </c>
       <c r="T52">
         <v>1.286464019494677</v>
       </c>
       <c r="U52">
-        <v>0.09377323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V52">
         <v>0.19</v>
       </c>
       <c r="W52">
-        <v>0.07595631899330522</v>
+        <v>0.06785631899330524</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.35586596510647</v>
+        <v>2.637085379900324</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09926063903117177</v>
+        <v>0.0951167469189374</v>
       </c>
       <c r="C53">
-        <v>802.9360733982121</v>
+        <v>864.621574077966</v>
       </c>
       <c r="D53">
-        <v>1724.218073398212</v>
+        <v>1785.903574077966</v>
       </c>
       <c r="E53">
         <v>381.182</v>
@@ -5633,45 +5633,45 @@
         <v>216.3</v>
       </c>
       <c r="M53">
-        <v>93.64964020354574</v>
+        <v>83.66282020354576</v>
       </c>
       <c r="N53">
-        <v>122.6503597964542</v>
+        <v>132.6371797964542</v>
       </c>
       <c r="O53">
-        <v>23.30356836132631</v>
+        <v>25.2010641613263</v>
       </c>
       <c r="P53">
-        <v>99.34679143512793</v>
+        <v>107.4361156351279</v>
       </c>
       <c r="Q53">
-        <v>211.4467914351279</v>
+        <v>219.5361156351279</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1235161558052778</v>
+        <v>0.1234898453721464</v>
       </c>
       <c r="T53">
         <v>1.309962403885041</v>
       </c>
       <c r="U53">
-        <v>0.09377323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V53">
         <v>0.19</v>
       </c>
       <c r="W53">
-        <v>0.07595631899330522</v>
+        <v>0.06785631899330524</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.309672514810265</v>
+        <v>2.58537782343169</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09948208513434288</v>
+        <v>0.09525722014536533</v>
       </c>
       <c r="C54">
-        <v>780.1670174414766</v>
+        <v>842.8692350783969</v>
       </c>
       <c r="D54">
-        <v>1721.031017441476</v>
+        <v>1783.733235078397</v>
       </c>
       <c r="E54">
         <v>400.764</v>
@@ -5715,45 +5715,45 @@
         <v>216.3</v>
       </c>
       <c r="M54">
-        <v>95.48590765851722</v>
+        <v>85.30326765851724</v>
       </c>
       <c r="N54">
-        <v>120.8140923414828</v>
+        <v>130.9967323414828</v>
       </c>
       <c r="O54">
-        <v>22.95467754488173</v>
+        <v>24.88937914488172</v>
       </c>
       <c r="P54">
-        <v>97.85941479660104</v>
+        <v>106.107353196601</v>
       </c>
       <c r="Q54">
-        <v>209.959414796601</v>
+        <v>218.207353196601</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1249683317871337</v>
+        <v>0.1249415297267638</v>
       </c>
       <c r="T54">
         <v>1.334439887625003</v>
       </c>
       <c r="U54">
-        <v>0.09377323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V54">
         <v>0.19</v>
       </c>
       <c r="W54">
-        <v>0.07595631899330522</v>
+        <v>0.06785631899330524</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.265255735679299</v>
+        <v>2.535659019134927</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09970353123751399</v>
+        <v>0.09707196337179327</v>
       </c>
       <c r="C55">
-        <v>757.4097216972109</v>
+        <v>795.7160281864219</v>
       </c>
       <c r="D55">
-        <v>1717.855721697211</v>
+        <v>1756.162028186422</v>
       </c>
       <c r="E55">
         <v>420.346</v>
@@ -5797,37 +5797,37 @@
         <v>216.3</v>
       </c>
       <c r="M55">
-        <v>97.32217511348871</v>
+        <v>90.99131451348872</v>
       </c>
       <c r="N55">
-        <v>118.9778248865113</v>
+        <v>125.3086854865113</v>
       </c>
       <c r="O55">
-        <v>22.60578672843714</v>
+        <v>23.80865024243714</v>
       </c>
       <c r="P55">
-        <v>96.37203815807413</v>
+        <v>101.5000352440741</v>
       </c>
       <c r="Q55">
-        <v>208.4720381580741</v>
+        <v>213.6000352440741</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1264823024916218</v>
+        <v>0.1264549878837053</v>
       </c>
       <c r="T55">
         <v>1.35995896641773</v>
       </c>
       <c r="U55">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.07595631899330522</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.222515061421198</v>
+        <v>2.377149963779623</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09992497734068509</v>
+        <v>0.09724402659822121</v>
       </c>
       <c r="C56">
-        <v>734.6641211926462</v>
+        <v>773.5640625158671</v>
       </c>
       <c r="D56">
-        <v>1714.692121192646</v>
+        <v>1753.592062515867</v>
       </c>
       <c r="E56">
         <v>439.9280000000001</v>
@@ -5879,37 +5879,37 @@
         <v>216.3</v>
       </c>
       <c r="M56">
-        <v>99.1584425684602</v>
+        <v>92.70813176846021</v>
       </c>
       <c r="N56">
-        <v>117.1415574315398</v>
+        <v>123.5918682315398</v>
       </c>
       <c r="O56">
-        <v>22.25689591199256</v>
+        <v>23.48245496399256</v>
       </c>
       <c r="P56">
-        <v>94.88466151954722</v>
+        <v>100.1094132675472</v>
       </c>
       <c r="Q56">
-        <v>206.9846615195472</v>
+        <v>212.2094132675472</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1280620980093484</v>
+        <v>0.1280342485692095</v>
       </c>
       <c r="T56">
         <v>1.386587570375358</v>
       </c>
       <c r="U56">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.07595631899330522</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.181357375098584</v>
+        <v>2.333128668154075</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1001464234438562</v>
+        <v>0.09741608982464917</v>
       </c>
       <c r="C57">
-        <v>711.9301514327494</v>
+        <v>751.419607624181</v>
       </c>
       <c r="D57">
-        <v>1711.54015143275</v>
+        <v>1751.029607624181</v>
       </c>
       <c r="E57">
         <v>459.5100000000002</v>
@@ -5961,37 +5961,37 @@
         <v>216.3</v>
       </c>
       <c r="M57">
-        <v>100.9947100234317</v>
+        <v>94.42494902343171</v>
       </c>
       <c r="N57">
-        <v>115.3052899765683</v>
+        <v>121.8750509765683</v>
       </c>
       <c r="O57">
-        <v>21.90800509554797</v>
+        <v>23.15625968554797</v>
       </c>
       <c r="P57">
-        <v>93.39728488102031</v>
+        <v>98.7187912910203</v>
       </c>
       <c r="Q57">
-        <v>205.4972848810203</v>
+        <v>210.8187912910203</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1297121066611963</v>
+        <v>0.1296836986185139</v>
       </c>
       <c r="T57">
         <v>1.414399667842214</v>
       </c>
       <c r="U57">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V57">
         <v>0.19</v>
       </c>
       <c r="W57">
-        <v>0.07595631899330522</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.141696331914972</v>
+        <v>2.290708146914909</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1003678695470273</v>
+        <v>0.09758815305107708</v>
       </c>
       <c r="C58">
-        <v>689.2077483958399</v>
+        <v>729.2826306337929</v>
       </c>
       <c r="D58">
-        <v>1708.39974839584</v>
+        <v>1748.474630633793</v>
       </c>
       <c r="E58">
         <v>479.0920000000001</v>
@@ -6043,37 +6043,37 @@
         <v>216.3</v>
       </c>
       <c r="M58">
-        <v>102.8309774784032</v>
+        <v>96.14176627840318</v>
       </c>
       <c r="N58">
-        <v>113.4690225215968</v>
+        <v>120.1582337215968</v>
       </c>
       <c r="O58">
-        <v>21.55911427910339</v>
+        <v>22.83006440710339</v>
       </c>
       <c r="P58">
-        <v>91.90990824249342</v>
+        <v>97.32816931449341</v>
       </c>
       <c r="Q58">
-        <v>204.0099082424934</v>
+        <v>209.4281693144934</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.13143711570631</v>
+        <v>0.1314081236700594</v>
       </c>
       <c r="T58">
         <v>1.443475951557563</v>
       </c>
       <c r="U58">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V58">
         <v>0.19</v>
       </c>
       <c r="W58">
-        <v>0.07595631899330522</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.103451754559348</v>
+        <v>2.249802644291429</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1005893156501984</v>
+        <v>0.09776021627750503</v>
       </c>
       <c r="C59">
-        <v>666.4968485292534</v>
+        <v>707.1530988587408</v>
       </c>
       <c r="D59">
-        <v>1705.270848529253</v>
+        <v>1745.927098858741</v>
       </c>
       <c r="E59">
         <v>498.6740000000002</v>
@@ -6125,37 +6125,37 @@
         <v>216.3</v>
       </c>
       <c r="M59">
-        <v>104.6672449333747</v>
+        <v>97.85858353337467</v>
       </c>
       <c r="N59">
-        <v>111.6327550666253</v>
+        <v>118.4414164666253</v>
       </c>
       <c r="O59">
-        <v>21.21022346265881</v>
+        <v>22.50386912865881</v>
       </c>
       <c r="P59">
-        <v>90.42253160396652</v>
+        <v>95.93754733796651</v>
       </c>
       <c r="Q59">
-        <v>202.5225316039665</v>
+        <v>208.0375473379665</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1332423577302661</v>
+        <v>0.1332127545379559</v>
       </c>
       <c r="T59">
         <v>1.473904620561999</v>
       </c>
       <c r="U59">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V59">
         <v>0.19</v>
       </c>
       <c r="W59">
-        <v>0.07595631899330522</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.066549092198658</v>
+        <v>2.210332422461755</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1008107617533695</v>
+        <v>0.09793227950393296</v>
       </c>
       <c r="C60">
-        <v>643.7973887450582</v>
+        <v>685.0309798032813</v>
       </c>
       <c r="D60">
-        <v>1702.153388745058</v>
+        <v>1743.386979803281</v>
       </c>
       <c r="E60">
         <v>518.2559999999999</v>
@@ -6207,37 +6207,37 @@
         <v>216.3</v>
       </c>
       <c r="M60">
-        <v>106.5035123883461</v>
+        <v>99.57540078834613</v>
       </c>
       <c r="N60">
-        <v>109.7964876116539</v>
+        <v>116.7245992116539</v>
       </c>
       <c r="O60">
-        <v>20.86133264621423</v>
+        <v>22.17767385021423</v>
       </c>
       <c r="P60">
-        <v>88.93515496543962</v>
+        <v>94.54692536143962</v>
       </c>
       <c r="Q60">
-        <v>201.0351549654396</v>
+        <v>206.6469253614396</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.135133563660125</v>
+        <v>0.1351033202090855</v>
       </c>
       <c r="T60">
         <v>1.50578227380474</v>
       </c>
       <c r="U60">
-        <v>0.09377323332506818</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V60">
         <v>0.19</v>
       </c>
       <c r="W60">
-        <v>0.07595631899330522</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.030918935436612</v>
+        <v>2.172223242764138</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1088219778565406</v>
+        <v>0.09810434273036089</v>
       </c>
       <c r="C61">
-        <v>518.6250984966789</v>
+        <v>662.9162411605048</v>
       </c>
       <c r="D61">
-        <v>1596.563098496679</v>
+        <v>1740.854241160505</v>
       </c>
       <c r="E61">
         <v>537.838</v>
@@ -6289,45 +6289,45 @@
         <v>216.3</v>
       </c>
       <c r="M61">
-        <v>127.1717892433176</v>
+        <v>101.2922180433176</v>
       </c>
       <c r="N61">
-        <v>89.12821075668236</v>
+        <v>115.0077819566824</v>
       </c>
       <c r="O61">
-        <v>16.93436004376965</v>
+        <v>21.85147857176965</v>
       </c>
       <c r="P61">
-        <v>72.19385071291271</v>
+        <v>93.15630338491272</v>
       </c>
       <c r="Q61">
-        <v>184.2938507129127</v>
+        <v>205.2563033849127</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1371170235377818</v>
+        <v>0.13708610859588</v>
       </c>
       <c r="T61">
         <v>1.539214934522738</v>
       </c>
       <c r="U61">
-        <v>0.1100732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V61">
         <v>0.19</v>
       </c>
       <c r="W61">
-        <v>0.08915931899330523</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.700848916941425</v>
+        <v>2.135405899666441</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1091754539597117</v>
+        <v>0.09827640595678883</v>
       </c>
       <c r="C62">
-        <v>494.6851116481196</v>
+        <v>640.8088508109688</v>
       </c>
       <c r="D62">
-        <v>1592.20511164812</v>
+        <v>1738.328850810969</v>
       </c>
       <c r="E62">
         <v>557.4200000000001</v>
@@ -6371,45 +6371,45 @@
         <v>216.3</v>
       </c>
       <c r="M62">
-        <v>129.3272432982891</v>
+        <v>103.0090352982891</v>
       </c>
       <c r="N62">
-        <v>86.97275670171086</v>
+        <v>113.2909647017109</v>
       </c>
       <c r="O62">
-        <v>16.52482377332506</v>
+        <v>21.52528329332506</v>
       </c>
       <c r="P62">
-        <v>70.4479329283858</v>
+        <v>91.7656814083858</v>
       </c>
       <c r="Q62">
-        <v>182.5479329283858</v>
+        <v>203.8656814083858</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1391996564093215</v>
+        <v>0.1391680364020142</v>
       </c>
       <c r="T62">
         <v>1.574319228276635</v>
       </c>
       <c r="U62">
-        <v>0.1100732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V62">
         <v>0.19</v>
       </c>
       <c r="W62">
-        <v>0.08915931899330523</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.672501434992401</v>
+        <v>2.099815801338667</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1095289300628828</v>
+        <v>0.09844846918321679</v>
       </c>
       <c r="C63">
-        <v>470.7688512024993</v>
+        <v>618.7087768213373</v>
       </c>
       <c r="D63">
-        <v>1587.870851202499</v>
+        <v>1735.810776821337</v>
       </c>
       <c r="E63">
         <v>577.002</v>
@@ -6453,45 +6453,45 @@
         <v>216.3</v>
       </c>
       <c r="M63">
-        <v>131.4826973532606</v>
+        <v>104.7258525532606</v>
       </c>
       <c r="N63">
-        <v>84.81730264673939</v>
+        <v>111.5741474467394</v>
       </c>
       <c r="O63">
-        <v>16.11528750288048</v>
+        <v>21.19908801488048</v>
       </c>
       <c r="P63">
-        <v>68.70201514385892</v>
+        <v>90.3750594318589</v>
       </c>
       <c r="Q63">
-        <v>180.8020151438589</v>
+        <v>202.4750594318589</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1413890909665811</v>
+        <v>0.1413567297366682</v>
       </c>
       <c r="T63">
         <v>1.61122374222304</v>
       </c>
       <c r="U63">
-        <v>0.1100732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V63">
         <v>0.19</v>
       </c>
       <c r="W63">
-        <v>0.08915931899330523</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.645083378681051</v>
+        <v>2.065392591480656</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.109882406166054</v>
+        <v>0.09862053240964472</v>
       </c>
       <c r="C64">
-        <v>446.8761239236001</v>
+        <v>596.6159874430377</v>
       </c>
       <c r="D64">
-        <v>1583.5601239236</v>
+        <v>1733.299987443038</v>
       </c>
       <c r="E64">
         <v>596.5840000000001</v>
@@ -6535,45 +6535,45 @@
         <v>216.3</v>
       </c>
       <c r="M64">
-        <v>133.6381514082321</v>
+        <v>106.4426698082321</v>
       </c>
       <c r="N64">
-        <v>82.66184859176789</v>
+        <v>109.8573301917679</v>
       </c>
       <c r="O64">
-        <v>15.7057512324359</v>
+        <v>20.8728927364359</v>
       </c>
       <c r="P64">
-        <v>66.95609735933199</v>
+        <v>88.984437455332</v>
       </c>
       <c r="Q64">
-        <v>179.056097359332</v>
+        <v>201.084437455332</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1436937589215913</v>
+        <v>0.1436606174573565</v>
       </c>
       <c r="T64">
         <v>1.650070599008729</v>
       </c>
       <c r="U64">
-        <v>0.1100732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V64">
         <v>0.19</v>
       </c>
       <c r="W64">
-        <v>0.08915931899330523</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.618549775799098</v>
+        <v>2.032079807747097</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1102358822692251</v>
+        <v>0.1060388556360727</v>
       </c>
       <c r="C65">
-        <v>423.0067386679029</v>
+        <v>475.2858490377828</v>
       </c>
       <c r="D65">
-        <v>1579.272738667903</v>
+        <v>1631.551849037783</v>
       </c>
       <c r="E65">
         <v>616.1659999999999</v>
@@ -6617,37 +6617,37 @@
         <v>216.3</v>
       </c>
       <c r="M65">
-        <v>135.7936054632036</v>
+        <v>125.6775442632036</v>
       </c>
       <c r="N65">
-        <v>80.50639453679642</v>
+        <v>90.62245573679641</v>
       </c>
       <c r="O65">
-        <v>15.29621496199132</v>
+        <v>17.21826658999132</v>
       </c>
       <c r="P65">
-        <v>65.2101795748051</v>
+        <v>73.40418914680509</v>
       </c>
       <c r="Q65">
-        <v>177.3101795748051</v>
+        <v>185.5041891468051</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1461230035228183</v>
+        <v>0.1460890396494334</v>
       </c>
       <c r="T65">
         <v>1.691017285890942</v>
       </c>
       <c r="U65">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.08915931899330523</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.592858509516573</v>
+        <v>1.721071184737728</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1105893583723962</v>
+        <v>0.1063259388625006</v>
       </c>
       <c r="C66">
-        <v>399.160506356332</v>
+        <v>452.0058209307269</v>
       </c>
       <c r="D66">
-        <v>1575.008506356332</v>
+        <v>1627.853820930727</v>
       </c>
       <c r="E66">
         <v>635.748</v>
@@ -6699,37 +6699,37 @@
         <v>216.3</v>
       </c>
       <c r="M66">
-        <v>137.9490595181751</v>
+        <v>127.6724259181751</v>
       </c>
       <c r="N66">
-        <v>78.35094048182492</v>
+        <v>88.62757408182492</v>
       </c>
       <c r="O66">
-        <v>14.88667869154673</v>
+        <v>16.83923907554674</v>
       </c>
       <c r="P66">
-        <v>63.46426179027819</v>
+        <v>71.78833500627817</v>
       </c>
       <c r="Q66">
-        <v>175.5642617902782</v>
+        <v>183.8883350062782</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1486872061574467</v>
+        <v>0.1486523741855146</v>
       </c>
       <c r="T66">
         <v>1.734238788711057</v>
       </c>
       <c r="U66">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V66">
         <v>0.19</v>
       </c>
       <c r="W66">
-        <v>0.08915931899330523</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.567970095305376</v>
+        <v>1.694179447476201</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1109428344755673</v>
+        <v>0.1066130220889285</v>
       </c>
       <c r="C67">
-        <v>375.3372399464613</v>
+        <v>428.7425186000455</v>
       </c>
       <c r="D67">
-        <v>1570.767239946461</v>
+        <v>1624.172518600046</v>
       </c>
       <c r="E67">
         <v>655.3300000000002</v>
@@ -6781,37 +6781,37 @@
         <v>216.3</v>
       </c>
       <c r="M67">
-        <v>140.1045135731466</v>
+        <v>129.6673075731466</v>
       </c>
       <c r="N67">
-        <v>76.19548642685342</v>
+        <v>86.63269242685342</v>
       </c>
       <c r="O67">
-        <v>14.47714242110215</v>
+        <v>16.46021156110215</v>
       </c>
       <c r="P67">
-        <v>61.71834400575127</v>
+        <v>70.17248086575127</v>
       </c>
       <c r="Q67">
-        <v>173.8183440057513</v>
+        <v>182.2724808657513</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.151397934656911</v>
+        <v>0.1513621849808004</v>
       </c>
       <c r="T67">
         <v>1.77993009169232</v>
       </c>
       <c r="U67">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V67">
         <v>0.19</v>
       </c>
       <c r="W67">
-        <v>0.08915931899330523</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.543847478454524</v>
+        <v>1.668115148284259</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1112963105787384</v>
+        <v>0.1069001053153565</v>
       </c>
       <c r="C68">
-        <v>351.5367544051651</v>
+        <v>405.495828828489</v>
       </c>
       <c r="D68">
-        <v>1566.548754405165</v>
+        <v>1620.507828828489</v>
       </c>
       <c r="E68">
         <v>674.912</v>
@@ -6863,37 +6863,37 @@
         <v>216.3</v>
       </c>
       <c r="M68">
-        <v>142.259967628118</v>
+        <v>131.662189228118</v>
       </c>
       <c r="N68">
-        <v>74.04003237188195</v>
+        <v>84.63781077188196</v>
       </c>
       <c r="O68">
-        <v>14.06760615065757</v>
+        <v>16.08118404665757</v>
       </c>
       <c r="P68">
-        <v>59.97242622122438</v>
+        <v>68.55662672522439</v>
       </c>
       <c r="Q68">
-        <v>172.0724262212244</v>
+        <v>180.6566267252244</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1542681177739909</v>
+        <v>0.154231396411103</v>
       </c>
       <c r="T68">
         <v>1.828309118378363</v>
       </c>
       <c r="U68">
-        <v>0.1100732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V68">
         <v>0.19</v>
       </c>
       <c r="W68">
-        <v>0.08915931899330523</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.520455849993092</v>
+        <v>1.642840676340558</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1488175353596471</v>
+        <v>0.1071871885417844</v>
       </c>
       <c r="C69">
-        <v>-15.56264526996802</v>
+        <v>382.2656394183357</v>
       </c>
       <c r="D69">
-        <v>1219.031354730032</v>
+        <v>1616.859639418336</v>
       </c>
       <c r="E69">
         <v>694.4940000000001</v>
@@ -6945,45 +6945,45 @@
         <v>216.3</v>
       </c>
       <c r="M69">
-        <v>230.2198292830896</v>
+        <v>133.6570708830895</v>
       </c>
       <c r="N69">
-        <v>-13.91982928308957</v>
+        <v>82.64292911691047</v>
       </c>
       <c r="O69">
-        <v>-2.644767563787018</v>
+        <v>15.70215653221299</v>
       </c>
       <c r="P69">
-        <v>-11.27506171930255</v>
+        <v>66.94077258469747</v>
       </c>
       <c r="Q69">
-        <v>100.8249382806974</v>
+        <v>179.0407725846975</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.158295757789577</v>
+        <v>0.1572744994432421</v>
       </c>
       <c r="T69">
-        <v>1.896197924021557</v>
+        <v>1.879620207287803</v>
       </c>
       <c r="U69">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V69">
-        <v>0.178511990596019</v>
+        <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.1441491571478906</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.9395367926106266</v>
+        <v>1.618320666245923</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1501142676928978</v>
+        <v>0.1074742717682124</v>
       </c>
       <c r="C70">
-        <v>-44.41943260466337</v>
+        <v>359.0518391799405</v>
       </c>
       <c r="D70">
-        <v>1209.756567395337</v>
+        <v>1613.22783917994</v>
       </c>
       <c r="E70">
         <v>714.076</v>
@@ -7027,45 +7027,45 @@
         <v>216.3</v>
       </c>
       <c r="M70">
-        <v>233.655946138061</v>
+        <v>135.651952538061</v>
       </c>
       <c r="N70">
-        <v>-17.35594613806103</v>
+        <v>80.64804746193897</v>
       </c>
       <c r="O70">
-        <v>-3.297629766231596</v>
+        <v>15.32312901776841</v>
       </c>
       <c r="P70">
-        <v>-14.05831637182943</v>
+        <v>65.32491844417056</v>
       </c>
       <c r="Q70">
-        <v>98.04168362817056</v>
+        <v>177.4249184441705</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1618112502205013</v>
+        <v>0.16050779641489</v>
       </c>
       <c r="T70">
-        <v>1.955454109147231</v>
+        <v>1.934138239254083</v>
       </c>
       <c r="U70">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V70">
-        <v>0.1758868142637247</v>
+        <v>0.19</v>
       </c>
       <c r="W70">
-        <v>0.1446098053269667</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.9257200750722352</v>
+        <v>1.594521832918777</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1514110000261485</v>
+        <v>0.1077613549946403</v>
       </c>
       <c r="C71">
-        <v>-73.13615440169178</v>
+        <v>335.8543179204385</v>
       </c>
       <c r="D71">
-        <v>1200.621845598308</v>
+        <v>1609.612317920438</v>
       </c>
       <c r="E71">
         <v>733.6580000000001</v>
@@ -7109,45 +7109,45 @@
         <v>216.3</v>
       </c>
       <c r="M71">
-        <v>237.0920629930325</v>
+        <v>137.6468341930325</v>
       </c>
       <c r="N71">
-        <v>-20.79206299303254</v>
+        <v>78.65316580696748</v>
       </c>
       <c r="O71">
-        <v>-3.950491968676184</v>
+        <v>14.94410150332382</v>
       </c>
       <c r="P71">
-        <v>-16.84157102435636</v>
+        <v>63.70906430364366</v>
       </c>
       <c r="Q71">
-        <v>95.25842897564362</v>
+        <v>175.8090643036437</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.165553548614711</v>
+        <v>0.1639496931911603</v>
       </c>
       <c r="T71">
-        <v>2.018533273958432</v>
+        <v>1.992173563605284</v>
       </c>
       <c r="U71">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V71">
-        <v>0.173337729999033</v>
+        <v>0.19</v>
       </c>
       <c r="W71">
-        <v>0.1450571013849102</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.9123038421001737</v>
+        <v>1.57141282084749</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1527077323593992</v>
+        <v>0.1080484382210682</v>
       </c>
       <c r="C72">
-        <v>-101.7159597352934</v>
+        <v>312.6729664326015</v>
       </c>
       <c r="D72">
-        <v>1191.624040264707</v>
+        <v>1606.012966432602</v>
       </c>
       <c r="E72">
         <v>753.2400000000002</v>
@@ -7191,45 +7191,45 @@
         <v>216.3</v>
       </c>
       <c r="M72">
-        <v>240.528179848004</v>
+        <v>139.641715848004</v>
       </c>
       <c r="N72">
-        <v>-24.22817984800403</v>
+        <v>76.65828415199599</v>
       </c>
       <c r="O72">
-        <v>-4.603354171120766</v>
+        <v>14.56507398887924</v>
       </c>
       <c r="P72">
-        <v>-19.62482567688327</v>
+        <v>62.09321016311675</v>
       </c>
       <c r="Q72">
-        <v>92.47517432311673</v>
+        <v>174.1932101631168</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1695453335685347</v>
+        <v>0.1676210497525152</v>
       </c>
       <c r="T72">
-        <v>2.085817716423713</v>
+        <v>2.054077909579899</v>
       </c>
       <c r="U72">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V72">
-        <v>0.1708614767133325</v>
+        <v>0.19</v>
       </c>
       <c r="W72">
-        <v>0.1454916175554839</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8992709300701712</v>
+        <v>1.548964066263955</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1540044646926498</v>
+        <v>0.1083355214474962</v>
       </c>
       <c r="C73">
-        <v>-130.161903981636</v>
+        <v>289.5076764838404</v>
       </c>
       <c r="D73">
-        <v>1182.760096018364</v>
+        <v>1602.42967648384</v>
       </c>
       <c r="E73">
         <v>772.8219999999999</v>
@@ -7273,45 +7273,45 @@
         <v>216.3</v>
       </c>
       <c r="M73">
-        <v>243.9642967029754</v>
+        <v>141.6365975029754</v>
       </c>
       <c r="N73">
-        <v>-27.66429670297546</v>
+        <v>74.66340249702455</v>
       </c>
       <c r="O73">
-        <v>-5.256216373565338</v>
+        <v>14.18604647443467</v>
       </c>
       <c r="P73">
-        <v>-22.40808032941013</v>
+        <v>60.47735602258989</v>
       </c>
       <c r="Q73">
-        <v>89.69191967058987</v>
+        <v>172.5773560225899</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1738124140364152</v>
+        <v>0.1715456033181015</v>
       </c>
       <c r="T73">
-        <v>2.15774246526591</v>
+        <v>2.120251520794142</v>
       </c>
       <c r="U73">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V73">
-        <v>0.1684549770413138</v>
+        <v>0.19</v>
       </c>
       <c r="W73">
-        <v>0.1459138938339287</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8866051423227042</v>
+        <v>1.527147670964463</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1553011970259005</v>
+        <v>0.1086226046739241</v>
       </c>
       <c r="C74">
-        <v>-158.476952277972</v>
+        <v>266.3583408053578</v>
       </c>
       <c r="D74">
-        <v>1174.027047722028</v>
+        <v>1598.862340805358</v>
       </c>
       <c r="E74">
         <v>792.404</v>
@@ -7355,45 +7355,45 @@
         <v>216.3</v>
       </c>
       <c r="M74">
-        <v>247.400413557947</v>
+        <v>143.6314791579469</v>
       </c>
       <c r="N74">
-        <v>-31.10041355794698</v>
+        <v>72.66852084205306</v>
       </c>
       <c r="O74">
-        <v>-5.909078576009926</v>
+        <v>13.80701895999008</v>
       </c>
       <c r="P74">
-        <v>-25.19133498193705</v>
+        <v>58.86150188206297</v>
       </c>
       <c r="Q74">
-        <v>86.90866501806295</v>
+        <v>170.961501882063</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1783842859662872</v>
+        <v>0.1757504821383726</v>
       </c>
       <c r="T74">
-        <v>2.234804696168263</v>
+        <v>2.191151818523688</v>
       </c>
       <c r="U74">
-        <v>0.1754732333250682</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V74">
-        <v>0.1661153245824066</v>
+        <v>0.19</v>
       </c>
       <c r="W74">
-        <v>0.1463244402157501</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8742911820126665</v>
+        <v>1.505937286645512</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1565979293591512</v>
+        <v>0.1437875690469573</v>
       </c>
       <c r="C75">
-        <v>-186.6639828296654</v>
+        <v>-95.79907972603633</v>
       </c>
       <c r="D75">
-        <v>1165.422017170335</v>
+        <v>1256.286920273964</v>
       </c>
       <c r="E75">
         <v>811.9860000000001</v>
@@ -7437,37 +7437,37 @@
         <v>216.3</v>
       </c>
       <c r="M75">
-        <v>250.8365304129184</v>
+        <v>226.8211656129184</v>
       </c>
       <c r="N75">
-        <v>-34.53653041291847</v>
+        <v>-10.52116561291845</v>
       </c>
       <c r="O75">
-        <v>-6.561940778454509</v>
+        <v>-1.999021466454506</v>
       </c>
       <c r="P75">
-        <v>-27.97458963446396</v>
+        <v>-8.522144146463946</v>
       </c>
       <c r="Q75">
-        <v>84.12541036553604</v>
+        <v>103.5778558535361</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1832948150761496</v>
+        <v>0.1812712583643203</v>
       </c>
       <c r="T75">
-        <v>2.317575240470791</v>
+        <v>2.284240036959591</v>
       </c>
       <c r="U75">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V75">
-        <v>0.1638397721908668</v>
+        <v>0.1811867948431853</v>
       </c>
       <c r="W75">
-        <v>0.1467237387514942</v>
+        <v>0.1299237387514942</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8623145904782464</v>
+        <v>0.9536147097009749</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1578946616924018</v>
+        <v>0.1449163013802079</v>
       </c>
       <c r="C76">
-        <v>-214.7257900728491</v>
+        <v>-123.9620845155916</v>
       </c>
       <c r="D76">
-        <v>1156.942209927151</v>
+        <v>1247.705915484408</v>
       </c>
       <c r="E76">
         <v>831.568</v>
@@ -7519,37 +7519,37 @@
         <v>216.3</v>
       </c>
       <c r="M76">
-        <v>254.2726472678899</v>
+        <v>229.9283048678899</v>
       </c>
       <c r="N76">
-        <v>-37.97264726788995</v>
+        <v>-13.62830486788994</v>
       </c>
       <c r="O76">
-        <v>-7.214802980899091</v>
+        <v>-2.589377924899088</v>
       </c>
       <c r="P76">
-        <v>-30.75784428699086</v>
+        <v>-11.03892694299085</v>
       </c>
       <c r="Q76">
-        <v>81.34215571300913</v>
+        <v>101.0610730570091</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1885830771944631</v>
+        <v>0.1864816913783327</v>
       </c>
       <c r="T76">
-        <v>2.406712749719668</v>
+        <v>2.372095422996499</v>
       </c>
       <c r="U76">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V76">
-        <v>0.1616257212153146</v>
+        <v>0.1787383246426017</v>
       </c>
       <c r="W76">
-        <v>0.1471122454349209</v>
+        <v>0.1303122454349209</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8506616906069188</v>
+        <v>0.9407280244347456</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1591913940256526</v>
+        <v>0.1460450337134586</v>
       </c>
       <c r="C77">
-        <v>-242.6650877000056</v>
+        <v>-152.0086603219479</v>
       </c>
       <c r="D77">
-        <v>1148.584912299994</v>
+        <v>1239.241339678052</v>
       </c>
       <c r="E77">
         <v>851.1500000000001</v>
@@ -7601,37 +7601,37 @@
         <v>216.3</v>
       </c>
       <c r="M77">
-        <v>257.7087641228615</v>
+        <v>233.0354441228614</v>
       </c>
       <c r="N77">
-        <v>-41.40876412286147</v>
+        <v>-16.73544412286142</v>
       </c>
       <c r="O77">
-        <v>-7.867665183343679</v>
+        <v>-3.17973438334367</v>
       </c>
       <c r="P77">
-        <v>-33.54109893951779</v>
+        <v>-13.55570973951775</v>
       </c>
       <c r="Q77">
-        <v>78.55890106048221</v>
+        <v>98.54429026048224</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1942944002822417</v>
+        <v>0.192108959033466</v>
       </c>
       <c r="T77">
-        <v>2.502981259708455</v>
+        <v>2.466979239916359</v>
       </c>
       <c r="U77">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V77">
-        <v>0.1594707115991104</v>
+        <v>0.1763551469807003</v>
       </c>
       <c r="W77">
-        <v>0.1474903919401229</v>
+        <v>0.1306903919401228</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8393195347321598</v>
+        <v>0.928184984108949</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1604881263589032</v>
+        <v>0.1471737660467093</v>
       </c>
       <c r="C78">
-        <v>-270.4845115553524</v>
+        <v>-179.9411607793313</v>
       </c>
       <c r="D78">
-        <v>1140.347488444648</v>
+        <v>1230.890839220669</v>
       </c>
       <c r="E78">
         <v>870.732</v>
@@ -7683,37 +7683,37 @@
         <v>216.3</v>
       </c>
       <c r="M78">
-        <v>261.1448809778329</v>
+        <v>236.1425833778329</v>
       </c>
       <c r="N78">
-        <v>-44.8448809778329</v>
+        <v>-19.84258337783291</v>
       </c>
       <c r="O78">
-        <v>-8.520527385788251</v>
+        <v>-3.770090841788253</v>
       </c>
       <c r="P78">
-        <v>-36.32435359204465</v>
+        <v>-16.07249253604466</v>
       </c>
       <c r="Q78">
-        <v>75.77564640795535</v>
+        <v>96.02750746395535</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2004816669606684</v>
+        <v>0.1982051656598604</v>
       </c>
       <c r="T78">
-        <v>2.607272145529641</v>
+        <v>2.56977004157954</v>
       </c>
       <c r="U78">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V78">
-        <v>0.15737241276228</v>
+        <v>0.1740346845204279</v>
       </c>
       <c r="W78">
-        <v>0.1478585872215037</v>
+        <v>0.1310585872215037</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8282758566435788</v>
+        <v>0.9159720237917259</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1617848586921539</v>
+        <v>0.14830249837996</v>
       </c>
       <c r="C79">
-        <v>-298.1866224065298</v>
+        <v>-207.7618765076945</v>
       </c>
       <c r="D79">
-        <v>1132.22737759347</v>
+        <v>1222.652123492305</v>
       </c>
       <c r="E79">
         <v>890.3140000000001</v>
@@ -7765,37 +7765,37 @@
         <v>216.3</v>
       </c>
       <c r="M79">
-        <v>264.5809978328044</v>
+        <v>239.2497226328044</v>
       </c>
       <c r="N79">
-        <v>-48.28099783280439</v>
+        <v>-22.9497226328044</v>
       </c>
       <c r="O79">
-        <v>-9.173389588232833</v>
+        <v>-4.360447300232835</v>
       </c>
       <c r="P79">
-        <v>-39.10760824457155</v>
+        <v>-18.58927533257156</v>
       </c>
       <c r="Q79">
-        <v>72.99239175542844</v>
+        <v>93.51072466742843</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2072069568285235</v>
+        <v>0.2048314772102891</v>
       </c>
       <c r="T79">
-        <v>2.72063180403093</v>
+        <v>2.681499173822129</v>
       </c>
       <c r="U79">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V79">
-        <v>0.1553286151939387</v>
+        <v>0.1717744938123704</v>
       </c>
       <c r="W79">
-        <v>0.1482172189890825</v>
+        <v>0.1314172189890825</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8175190273365194</v>
+        <v>0.9040762832230023</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1630815910254046</v>
+        <v>0.1494312307132107</v>
       </c>
       <c r="C80">
-        <v>-325.7739085986989</v>
+        <v>-235.4730372075599</v>
       </c>
       <c r="D80">
-        <v>1124.222091401301</v>
+        <v>1214.52296279244</v>
       </c>
       <c r="E80">
         <v>909.8960000000002</v>
@@ -7847,37 +7847,37 @@
         <v>216.3</v>
       </c>
       <c r="M80">
-        <v>268.0171146877759</v>
+        <v>242.3568618877759</v>
       </c>
       <c r="N80">
-        <v>-51.71711468777593</v>
+        <v>-26.05686188777591</v>
       </c>
       <c r="O80">
-        <v>-9.826251790677427</v>
+        <v>-4.950803758677423</v>
       </c>
       <c r="P80">
-        <v>-41.89086289709851</v>
+        <v>-21.10605812909849</v>
       </c>
       <c r="Q80">
-        <v>70.20913710290148</v>
+        <v>90.99394187090151</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2145436366843655</v>
+        <v>0.2120601807198478</v>
       </c>
       <c r="T80">
-        <v>2.844296886032336</v>
+        <v>2.803385499904953</v>
       </c>
       <c r="U80">
-        <v>0.1754732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V80">
-        <v>0.1533372226914523</v>
+        <v>0.1695722567122118</v>
       </c>
       <c r="W80">
-        <v>0.1485666550703131</v>
+        <v>0.131766655070313</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8070380141655382</v>
+        <v>0.8924855616432201</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.206772628006492</v>
+        <v>0.1505599630464614</v>
       </c>
       <c r="C81">
-        <v>-561.6467731600541</v>
+        <v>-263.076813671845</v>
       </c>
       <c r="D81">
-        <v>907.931226839946</v>
+        <v>1206.501186328155</v>
       </c>
       <c r="E81">
         <v>929.4780000000001</v>
@@ -7929,45 +7929,45 @@
         <v>216.3</v>
       </c>
       <c r="M81">
-        <v>352.2054831427474</v>
+        <v>245.4640011427473</v>
       </c>
       <c r="N81">
-        <v>-135.9054831427474</v>
+        <v>-29.16400114274737</v>
       </c>
       <c r="O81">
-        <v>-25.822041797122</v>
+        <v>-5.541160217122</v>
       </c>
       <c r="P81">
-        <v>-110.0834413456254</v>
+        <v>-23.62284092562537</v>
       </c>
       <c r="Q81">
-        <v>2.01655865437462</v>
+        <v>88.47715907437463</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.228085260563796</v>
+        <v>0.2199773321826976</v>
       </c>
       <c r="T81">
-        <v>3.072550818381381</v>
+        <v>2.936880047519475</v>
       </c>
       <c r="U81">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V81">
-        <v>0.1166847251589878</v>
+        <v>0.167425772450032</v>
       </c>
       <c r="W81">
-        <v>0.2011072446684745</v>
+        <v>0.1321072446684745</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.6141301324157253</v>
+        <v>0.8811882760527997</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2085913603397427</v>
+        <v>0.151688695379712</v>
       </c>
       <c r="C82">
-        <v>-588.4423583607754</v>
+        <v>-290.5753197184899</v>
       </c>
       <c r="D82">
-        <v>900.7176416392248</v>
+        <v>1198.58468028151</v>
       </c>
       <c r="E82">
         <v>949.0600000000002</v>
@@ -8011,45 +8011,45 @@
         <v>216.3</v>
       </c>
       <c r="M82">
-        <v>356.6637803977189</v>
+        <v>248.5711403977189</v>
       </c>
       <c r="N82">
-        <v>-140.3637803977189</v>
+        <v>-32.27114039771888</v>
       </c>
       <c r="O82">
-        <v>-26.66911827556659</v>
+        <v>-6.131516675566587</v>
       </c>
       <c r="P82">
-        <v>-113.6946621221523</v>
+        <v>-26.13962372215229</v>
       </c>
       <c r="Q82">
-        <v>-1.594662122152315</v>
+        <v>85.9603762778477</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2371995235919858</v>
+        <v>0.2286861987918325</v>
       </c>
       <c r="T82">
-        <v>3.226178359300451</v>
+        <v>3.083724049895449</v>
       </c>
       <c r="U82">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V82">
-        <v>0.1152261660945005</v>
+        <v>0.1653329502944065</v>
       </c>
       <c r="W82">
-        <v>0.2014393195266819</v>
+        <v>0.1324393195266819</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.6064535057605288</v>
+        <v>0.8701734226021396</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2104100926729934</v>
+        <v>0.1528174277129627</v>
       </c>
       <c r="C83">
-        <v>-615.1242220809976</v>
+        <v>-317.9706140474857</v>
       </c>
       <c r="D83">
-        <v>893.6177779190025</v>
+        <v>1190.771385952514</v>
       </c>
       <c r="E83">
         <v>968.6420000000001</v>
@@ -8093,45 +8093,45 @@
         <v>216.3</v>
       </c>
       <c r="M83">
-        <v>361.1220776526903</v>
+        <v>251.6782796526903</v>
       </c>
       <c r="N83">
-        <v>-144.8220776526904</v>
+        <v>-35.37827965269034</v>
       </c>
       <c r="O83">
-        <v>-27.51619475401117</v>
+        <v>-6.721873134011164</v>
       </c>
       <c r="P83">
-        <v>-117.3058828986792</v>
+        <v>-28.65640651867917</v>
       </c>
       <c r="Q83">
-        <v>-5.205882898679192</v>
+        <v>83.44359348132082</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2472731827284061</v>
+        <v>0.238311788201929</v>
       </c>
       <c r="T83">
-        <v>3.395977220316265</v>
+        <v>3.24602531567942</v>
       </c>
       <c r="U83">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V83">
-        <v>0.1138036208340746</v>
+        <v>0.1632918027599077</v>
       </c>
       <c r="W83">
-        <v>0.2017631950056744</v>
+        <v>0.1327631950056744</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5989664254424976</v>
+        <v>0.8594305408416194</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2122288250062441</v>
+        <v>0.1539461600462134</v>
       </c>
       <c r="C84">
-        <v>-641.6950325013041</v>
+        <v>-345.264702025748</v>
       </c>
       <c r="D84">
-        <v>886.6289674986961</v>
+        <v>1183.059297974252</v>
       </c>
       <c r="E84">
         <v>988.2240000000002</v>
@@ -8175,45 +8175,45 @@
         <v>216.3</v>
       </c>
       <c r="M84">
-        <v>365.5803749076618</v>
+        <v>254.7854189076618</v>
       </c>
       <c r="N84">
-        <v>-149.2803749076619</v>
+        <v>-38.48541890766185</v>
       </c>
       <c r="O84">
-        <v>-28.36327123245576</v>
+        <v>-7.312229592455752</v>
       </c>
       <c r="P84">
-        <v>-120.9171036752061</v>
+        <v>-31.1731893152061</v>
       </c>
       <c r="Q84">
-        <v>-8.817103675206113</v>
+        <v>80.92681068479389</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2584661373244286</v>
+        <v>0.2490068875464806</v>
       </c>
       <c r="T84">
-        <v>3.584642621444946</v>
+        <v>3.426360055439388</v>
       </c>
       <c r="U84">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V84">
-        <v>0.1124157717995126</v>
+        <v>0.1613004393116161</v>
       </c>
       <c r="W84">
-        <v>0.2020791710827401</v>
+        <v>0.1330791710827401</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5916619568395403</v>
+        <v>0.8489496805874532</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2140475573394948</v>
+        <v>0.1550748923794641</v>
       </c>
       <c r="C85">
-        <v>-668.1573749807286</v>
+        <v>-372.4595374030721</v>
       </c>
       <c r="D85">
-        <v>879.7486250192717</v>
+        <v>1175.446462596928</v>
       </c>
       <c r="E85">
         <v>1007.806</v>
@@ -8257,45 +8257,45 @@
         <v>216.3</v>
       </c>
       <c r="M85">
-        <v>370.0386721626334</v>
+        <v>257.8925581626333</v>
       </c>
       <c r="N85">
-        <v>-153.7386721626334</v>
+        <v>-41.59255816263337</v>
       </c>
       <c r="O85">
-        <v>-29.21034771090034</v>
+        <v>-7.902586050900339</v>
       </c>
       <c r="P85">
-        <v>-124.528324451733</v>
+        <v>-33.68997211173303</v>
       </c>
       <c r="Q85">
-        <v>-12.42832445173303</v>
+        <v>78.41002788826697</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2709759101082186</v>
+        <v>0.2609602338727442</v>
       </c>
       <c r="T85">
-        <v>3.795503952118179</v>
+        <v>3.627910646935823</v>
       </c>
       <c r="U85">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V85">
-        <v>0.1110613649103619</v>
+        <v>0.1593570605247291</v>
       </c>
       <c r="W85">
-        <v>0.2023875332784308</v>
+        <v>0.1333875332784308</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.5845334995282205</v>
+        <v>0.838721371182785</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2158662896727454</v>
+        <v>0.1562036247127148</v>
       </c>
       <c r="C86">
-        <v>-694.513755245533</v>
+        <v>-399.5570239622639</v>
       </c>
       <c r="D86">
-        <v>872.9742447544669</v>
+        <v>1167.930976037736</v>
       </c>
       <c r="E86">
         <v>1027.388</v>
@@ -8339,45 +8339,45 @@
         <v>216.3</v>
       </c>
       <c r="M86">
-        <v>374.4969694176048</v>
+        <v>260.9996974176048</v>
       </c>
       <c r="N86">
-        <v>-158.1969694176048</v>
+        <v>-44.69969741760477</v>
       </c>
       <c r="O86">
-        <v>-30.05742418934491</v>
+        <v>-8.492942509344905</v>
       </c>
       <c r="P86">
-        <v>-128.1395452282599</v>
+        <v>-36.20675490825986</v>
       </c>
       <c r="Q86">
-        <v>-16.03954522825987</v>
+        <v>75.89324509174014</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2850494044899822</v>
+        <v>0.2744077484897905</v>
       </c>
       <c r="T86">
-        <v>4.032722949125563</v>
+        <v>3.854655062369309</v>
       </c>
       <c r="U86">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V86">
-        <v>0.1097392058042862</v>
+        <v>0.1574599526613396</v>
       </c>
       <c r="W86">
-        <v>0.2026885535170813</v>
+        <v>0.1336885535170813</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5775747673909799</v>
+        <v>0.8287365929544188</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2176850220059961</v>
+        <v>0.1573323570459655</v>
       </c>
       <c r="C87">
-        <v>-720.7666024317862</v>
+        <v>-426.5590171063691</v>
       </c>
       <c r="D87">
-        <v>866.3033975682139</v>
+        <v>1160.510982893631</v>
       </c>
       <c r="E87">
         <v>1046.97</v>
@@ -8421,45 +8421,45 @@
         <v>216.3</v>
       </c>
       <c r="M87">
-        <v>378.9552666725763</v>
+        <v>264.1068366725763</v>
       </c>
       <c r="N87">
-        <v>-162.6552666725763</v>
+        <v>-47.80683667257628</v>
       </c>
       <c r="O87">
-        <v>-30.9045006677895</v>
+        <v>-9.083298967789494</v>
       </c>
       <c r="P87">
-        <v>-131.7507660047868</v>
+        <v>-38.72353770478679</v>
       </c>
       <c r="Q87">
-        <v>-19.65076600478679</v>
+        <v>73.3764622952132</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3009993647893143</v>
+        <v>0.2896482650557767</v>
       </c>
       <c r="T87">
-        <v>4.301571145733933</v>
+        <v>4.111632066527265</v>
       </c>
       <c r="U87">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V87">
-        <v>0.1084481563242357</v>
+        <v>0.1556074826300297</v>
       </c>
       <c r="W87">
-        <v>0.202982490926587</v>
+        <v>0.133982490926587</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.5707797701275565</v>
+        <v>0.8189867506843668</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2195037543392468</v>
+        <v>0.1584610893792161</v>
       </c>
       <c r="C88">
-        <v>-746.9182719894928</v>
+        <v>-453.4673253857791</v>
       </c>
       <c r="D88">
-        <v>859.7337280105071</v>
+        <v>1153.184674614221</v>
       </c>
       <c r="E88">
         <v>1066.552</v>
@@ -8503,45 +8503,45 @@
         <v>216.3</v>
       </c>
       <c r="M88">
-        <v>383.4135639275477</v>
+        <v>267.2139759275477</v>
       </c>
       <c r="N88">
-        <v>-167.1135639275477</v>
+        <v>-50.91397592754774</v>
       </c>
       <c r="O88">
-        <v>-31.75157714623407</v>
+        <v>-9.67365542623407</v>
       </c>
       <c r="P88">
-        <v>-135.3619867813137</v>
+        <v>-41.24032050131367</v>
       </c>
       <c r="Q88">
-        <v>-23.26198678131368</v>
+        <v>70.85967949868632</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3192278908456939</v>
+        <v>0.3070659982740464</v>
       </c>
       <c r="T88">
-        <v>4.608826227572072</v>
+        <v>4.405320071279212</v>
       </c>
       <c r="U88">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V88">
-        <v>0.1071871312506981</v>
+        <v>0.1537980932971224</v>
       </c>
       <c r="W88">
-        <v>0.2032695925823833</v>
+        <v>0.1342695925823833</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5641427960563059</v>
+        <v>0.809463648932223</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2213224866724975</v>
+        <v>0.1595898217124668</v>
       </c>
       <c r="C89">
-        <v>-772.9710484555858</v>
+        <v>-480.2837119678591</v>
       </c>
       <c r="D89">
-        <v>853.2629515444142</v>
+        <v>1145.950288032141</v>
       </c>
       <c r="E89">
         <v>1086.134</v>
@@ -8585,45 +8585,45 @@
         <v>216.3</v>
       </c>
       <c r="M89">
-        <v>387.8718611825192</v>
+        <v>270.3211151825192</v>
       </c>
       <c r="N89">
-        <v>-171.5718611825193</v>
+        <v>-54.02111518251925</v>
       </c>
       <c r="O89">
-        <v>-32.59865362467866</v>
+        <v>-10.26401188467866</v>
       </c>
       <c r="P89">
-        <v>-138.9732075578406</v>
+        <v>-43.75710329784059</v>
       </c>
       <c r="Q89">
-        <v>-26.8732075578406</v>
+        <v>68.34289670215941</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3402608055261319</v>
+        <v>0.3271633827566653</v>
       </c>
       <c r="T89">
-        <v>4.963351322000692</v>
+        <v>4.744190845992997</v>
       </c>
       <c r="U89">
-        <v>0.2276732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V89">
-        <v>0.1059550952593108</v>
+        <v>0.1520302991212934</v>
       </c>
       <c r="W89">
-        <v>0.2035500942001153</v>
+        <v>0.1345500942001153</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5576583961016357</v>
+        <v>0.8001594690594388</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2231412190057482</v>
+        <v>0.2096542005583565</v>
       </c>
       <c r="C90">
-        <v>-798.9271481026185</v>
+        <v>-749.3191457636556</v>
       </c>
       <c r="D90">
-        <v>846.8888518973816</v>
+        <v>896.4968542363446</v>
       </c>
       <c r="E90">
         <v>1105.716</v>
@@ -8667,37 +8667,37 @@
         <v>216.3</v>
       </c>
       <c r="M90">
-        <v>392.3301584374908</v>
+        <v>366.4819184374907</v>
       </c>
       <c r="N90">
-        <v>-176.0301584374908</v>
+        <v>-150.1819184374907</v>
       </c>
       <c r="O90">
-        <v>-33.44573010312325</v>
+        <v>-28.53456450312324</v>
       </c>
       <c r="P90">
-        <v>-142.5844283343675</v>
+        <v>-121.6473539343675</v>
       </c>
       <c r="Q90">
-        <v>-30.48442833436752</v>
+        <v>-9.547353934367507</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3647992059866429</v>
+        <v>0.3624073855917122</v>
       </c>
       <c r="T90">
-        <v>5.376963932167418</v>
+        <v>5.338455366087944</v>
       </c>
       <c r="U90">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V90">
-        <v>0.1047510600859095</v>
+        <v>0.1121392296111595</v>
       </c>
       <c r="W90">
-        <v>0.2038242207810807</v>
+        <v>0.1888242207810807</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.551321368873208</v>
+        <v>0.5902064716376816</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2249599513389988</v>
+        <v>0.2113229328916071</v>
       </c>
       <c r="C91">
-        <v>-824.788721469626</v>
+        <v>-775.3590347823681</v>
       </c>
       <c r="D91">
-        <v>840.609278530374</v>
+        <v>890.0389652176319</v>
       </c>
       <c r="E91">
         <v>1125.298</v>
@@ -8749,37 +8749,37 @@
         <v>216.3</v>
       </c>
       <c r="M91">
-        <v>396.7884556924622</v>
+        <v>370.6464856924622</v>
       </c>
       <c r="N91">
-        <v>-180.4884556924622</v>
+        <v>-154.3464856924622</v>
       </c>
       <c r="O91">
-        <v>-34.29280658156782</v>
+        <v>-29.32583228156782</v>
       </c>
       <c r="P91">
-        <v>-146.1956491108944</v>
+        <v>-125.0206534108944</v>
       </c>
       <c r="Q91">
-        <v>-34.09564911089441</v>
+        <v>-12.9206534108944</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3937991338036104</v>
+        <v>0.3911898751909587</v>
       </c>
       <c r="T91">
-        <v>5.865778835091728</v>
+        <v>5.823769490277756</v>
       </c>
       <c r="U91">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V91">
-        <v>0.1035740818826971</v>
+        <v>0.1108792382672139</v>
       </c>
       <c r="W91">
-        <v>0.2040921872141592</v>
+        <v>0.1890921872141592</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5451267467510372</v>
+        <v>0.583574938248494</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2267786836722495</v>
+        <v>0.2129916652248578</v>
       </c>
       <c r="C92">
-        <v>-850.5578557812164</v>
+        <v>-801.3065507759885</v>
       </c>
       <c r="D92">
-        <v>834.4221442187837</v>
+        <v>883.6734492240116</v>
       </c>
       <c r="E92">
         <v>1144.88</v>
@@ -8831,37 +8831,37 @@
         <v>216.3</v>
       </c>
       <c r="M92">
-        <v>401.2467529474337</v>
+        <v>374.8110529474337</v>
       </c>
       <c r="N92">
-        <v>-184.9467529474337</v>
+        <v>-158.5110529474337</v>
       </c>
       <c r="O92">
-        <v>-35.13988306001241</v>
+        <v>-30.1171000600124</v>
       </c>
       <c r="P92">
-        <v>-149.8068698874213</v>
+        <v>-128.3939528874213</v>
       </c>
       <c r="Q92">
-        <v>-37.70686988742133</v>
+        <v>-16.29395288742128</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4285990471839716</v>
+        <v>0.4257288627100547</v>
       </c>
       <c r="T92">
-        <v>6.452356718600902</v>
+        <v>6.406146439305533</v>
       </c>
       <c r="U92">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V92">
-        <v>0.1024232587506671</v>
+        <v>0.1096472467309115</v>
       </c>
       <c r="W92">
-        <v>0.2043541988376137</v>
+        <v>0.1893541988376137</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5390697828982478</v>
+        <v>0.5770907722679552</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2285974160055002</v>
+        <v>0.2146603975581085</v>
       </c>
       <c r="C93">
-        <v>-876.23657726061</v>
+        <v>-827.1636616127531</v>
       </c>
       <c r="D93">
-        <v>828.32542273939</v>
+        <v>877.3983383872469</v>
       </c>
       <c r="E93">
         <v>1164.462</v>
@@ -8913,37 +8913,37 @@
         <v>216.3</v>
       </c>
       <c r="M93">
-        <v>405.7050502024052</v>
+        <v>378.9756202024051</v>
       </c>
       <c r="N93">
-        <v>-189.4050502024052</v>
+        <v>-162.6756202024052</v>
       </c>
       <c r="O93">
-        <v>-35.98695953845699</v>
+        <v>-30.90836783845698</v>
       </c>
       <c r="P93">
-        <v>-153.4180906639482</v>
+        <v>-131.7672523639482</v>
       </c>
       <c r="Q93">
-        <v>-41.3180906639482</v>
+        <v>-19.66725236394819</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4711322746488573</v>
+        <v>0.4679431807889497</v>
       </c>
       <c r="T93">
-        <v>7.169285242889892</v>
+        <v>7.117940488117259</v>
       </c>
       <c r="U93">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V93">
-        <v>0.1012977284347257</v>
+        <v>0.1084423319316707</v>
       </c>
       <c r="W93">
-        <v>0.2046104519638495</v>
+        <v>0.1896104519638495</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5331459391301352</v>
+        <v>0.5707491154298459</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2304161483387509</v>
+        <v>0.2163291298913592</v>
       </c>
       <c r="C94">
-        <v>-901.8268533420139</v>
+        <v>-852.932279658404</v>
       </c>
       <c r="D94">
-        <v>822.3171466579862</v>
+        <v>871.2117203415961</v>
       </c>
       <c r="E94">
         <v>1184.044</v>
@@ -8995,37 +8995,37 @@
         <v>216.3</v>
       </c>
       <c r="M94">
-        <v>410.1633474573767</v>
+        <v>383.1401874573767</v>
       </c>
       <c r="N94">
-        <v>-193.8633474573767</v>
+        <v>-166.8401874573767</v>
       </c>
       <c r="O94">
-        <v>-36.83403601690157</v>
+        <v>-31.69963561690157</v>
       </c>
       <c r="P94">
-        <v>-157.0293114404751</v>
+        <v>-135.1405518404751</v>
       </c>
       <c r="Q94">
-        <v>-44.92931144047515</v>
+        <v>-23.04055184047513</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5242988089799646</v>
+        <v>0.5207110783875686</v>
       </c>
       <c r="T94">
-        <v>8.065445898251131</v>
+        <v>8.00768304913192</v>
       </c>
       <c r="U94">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V94">
-        <v>0.1001966661691309</v>
+        <v>0.1072636109324134</v>
       </c>
       <c r="W94">
-        <v>0.2048611343699497</v>
+        <v>0.1898611343699497</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5273508745743729</v>
+        <v>0.5645453206969128</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2322348806720015</v>
+        <v>0.2179978622246099</v>
       </c>
       <c r="C95">
-        <v>-927.3305947874046</v>
+        <v>-878.6142637192548</v>
       </c>
       <c r="D95">
-        <v>816.3954052125956</v>
+        <v>865.1117362807454</v>
       </c>
       <c r="E95">
         <v>1203.626</v>
@@ -9077,37 +9077,37 @@
         <v>216.3</v>
       </c>
       <c r="M95">
-        <v>414.6216447123482</v>
+        <v>387.3047547123481</v>
       </c>
       <c r="N95">
-        <v>-198.3216447123482</v>
+        <v>-171.0047547123482</v>
       </c>
       <c r="O95">
-        <v>-37.68111249534616</v>
+        <v>-32.49090339534615</v>
       </c>
       <c r="P95">
-        <v>-160.6405322170021</v>
+        <v>-138.513851317002</v>
       </c>
       <c r="Q95">
-        <v>-48.54053221700207</v>
+        <v>-26.41385131700201</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5926557816913881</v>
+        <v>0.5885555181572213</v>
       </c>
       <c r="T95">
-        <v>9.217652455144149</v>
+        <v>9.151637770436482</v>
       </c>
       <c r="U95">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V95">
-        <v>0.09911928266193588</v>
+        <v>0.1061102387718498</v>
       </c>
       <c r="W95">
-        <v>0.2051064257565639</v>
+        <v>0.1901064257565639</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5216804350628205</v>
+        <v>0.5584749409044729</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2340536130052522</v>
+        <v>0.2196665945578605</v>
       </c>
       <c r="C96">
-        <v>-952.749657712504</v>
+        <v>-904.2114209041932</v>
       </c>
       <c r="D96">
-        <v>810.5583422874961</v>
+        <v>859.0965790958069</v>
       </c>
       <c r="E96">
         <v>1223.208</v>
@@ -9159,37 +9159,37 @@
         <v>216.3</v>
       </c>
       <c r="M96">
-        <v>419.0799419673197</v>
+        <v>391.4693219673196</v>
       </c>
       <c r="N96">
-        <v>-202.7799419673197</v>
+        <v>-175.1693219673196</v>
       </c>
       <c r="O96">
-        <v>-38.52818897379074</v>
+        <v>-33.28217117379073</v>
       </c>
       <c r="P96">
-        <v>-164.2517529935289</v>
+        <v>-141.8871507935289</v>
       </c>
       <c r="Q96">
-        <v>-52.15175299352893</v>
+        <v>-29.78715079352892</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6837984119732863</v>
+        <v>0.6790147711834249</v>
       </c>
       <c r="T96">
-        <v>10.75392786433484</v>
+        <v>10.6769107321759</v>
       </c>
       <c r="U96">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V96">
-        <v>0.09806482220808552</v>
+        <v>0.1049814064444897</v>
       </c>
       <c r="W96">
-        <v>0.2053464981775054</v>
+        <v>0.1903464981775054</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.51613064320045</v>
+        <v>0.5525337181288934</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2358723453385029</v>
+        <v>0.2213353268911112</v>
       </c>
       <c r="C97">
-        <v>-978.08584552646</v>
+        <v>-929.7255084095459</v>
       </c>
       <c r="D97">
-        <v>804.8041544735402</v>
+        <v>853.1644915904543</v>
       </c>
       <c r="E97">
         <v>1242.79</v>
@@ -9241,37 +9241,37 @@
         <v>216.3</v>
       </c>
       <c r="M97">
-        <v>423.5382392222912</v>
+        <v>395.6338892222911</v>
       </c>
       <c r="N97">
-        <v>-207.2382392222912</v>
+        <v>-179.3338892222912</v>
       </c>
       <c r="O97">
-        <v>-39.37526545223533</v>
+        <v>-34.07343895223532</v>
       </c>
       <c r="P97">
-        <v>-167.8629737700559</v>
+        <v>-145.2604502700559</v>
       </c>
       <c r="Q97">
-        <v>-55.76297377005588</v>
+        <v>-33.16045027005586</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8113980943679441</v>
+        <v>0.8056577254201104</v>
       </c>
       <c r="T97">
-        <v>12.90471343720182</v>
+        <v>12.81229287861108</v>
       </c>
       <c r="U97">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V97">
-        <v>0.09703256092168461</v>
+        <v>0.1038763390082319</v>
       </c>
       <c r="W97">
-        <v>0.2055815164422166</v>
+        <v>0.1905815164422166</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5106976890614979</v>
+        <v>0.5467175737275365</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2376910776717536</v>
+        <v>0.2230040592243619</v>
       </c>
       <c r="C98">
-        <v>-1003.340910789488</v>
+        <v>-955.1582352304961</v>
       </c>
       <c r="D98">
-        <v>799.1310892105125</v>
+        <v>847.313764769504</v>
       </c>
       <c r="E98">
         <v>1262.372</v>
@@ -9323,37 +9323,37 @@
         <v>216.3</v>
       </c>
       <c r="M98">
-        <v>427.9965364772626</v>
+        <v>399.7984564772626</v>
       </c>
       <c r="N98">
-        <v>-211.6965364772626</v>
+        <v>-183.4984564772626</v>
       </c>
       <c r="O98">
-        <v>-40.2223419306799</v>
+        <v>-34.8647067306799</v>
       </c>
       <c r="P98">
-        <v>-171.4741945465827</v>
+        <v>-148.6337497465827</v>
       </c>
       <c r="Q98">
-        <v>-59.37419454658274</v>
+        <v>-36.53374974658274</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.002797617959928</v>
+        <v>0.9956221567751357</v>
       </c>
       <c r="T98">
-        <v>16.13089179650224</v>
+        <v>16.01536609826382</v>
       </c>
       <c r="U98">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V98">
-        <v>0.0960218050787504</v>
+        <v>0.1027942938102295</v>
       </c>
       <c r="W98">
-        <v>0.2058116384930797</v>
+        <v>0.1908116384930796</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5053779214671074</v>
+        <v>0.5410225990012081</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2395098100050043</v>
+        <v>0.2246727915576126</v>
       </c>
       <c r="C99">
-        <v>-1028.516556992497</v>
+        <v>-980.5112638025685</v>
       </c>
       <c r="D99">
-        <v>793.5374430075026</v>
+        <v>841.5427361974315</v>
       </c>
       <c r="E99">
         <v>1281.954</v>
@@ -9405,37 +9405,37 @@
         <v>216.3</v>
       </c>
       <c r="M99">
-        <v>432.4548337322341</v>
+        <v>403.963023732234</v>
       </c>
       <c r="N99">
-        <v>-216.1548337322341</v>
+        <v>-187.6630237322341</v>
       </c>
       <c r="O99">
-        <v>-41.06941840912448</v>
+        <v>-35.65597450912447</v>
       </c>
       <c r="P99">
-        <v>-175.0854153231096</v>
+        <v>-152.0070492231096</v>
       </c>
       <c r="Q99">
-        <v>-62.98541532310961</v>
+        <v>-39.9070492231096</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.321796823946571</v>
+        <v>1.312229542366848</v>
       </c>
       <c r="T99">
-        <v>21.50785572866965</v>
+        <v>21.35382146435176</v>
       </c>
       <c r="U99">
-        <v>0.2276732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V99">
-        <v>0.09503188956247463</v>
+        <v>0.1017345588224952</v>
       </c>
       <c r="W99">
-        <v>0.2060370157593888</v>
+        <v>0.1910370157593888</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.500167839802498</v>
+        <v>0.5354450464341853</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.271181090280572</v>
+        <v>0.2263415238908633</v>
       </c>
       <c r="C100">
-        <v>-1134.315044222367</v>
+        <v>-1005.786211576484</v>
       </c>
       <c r="D100">
-        <v>707.320955777633</v>
+        <v>835.8497884235159</v>
       </c>
       <c r="E100">
         <v>1301.536</v>
@@ -9487,45 +9487,45 @@
         <v>216.3</v>
       </c>
       <c r="M100">
-        <v>494.4842109872056</v>
+        <v>408.1275909872056</v>
       </c>
       <c r="N100">
-        <v>-278.1842109872056</v>
+        <v>-191.8275909872056</v>
       </c>
       <c r="O100">
-        <v>-52.85500008756906</v>
+        <v>-36.44724228756906</v>
       </c>
       <c r="P100">
-        <v>-225.3292108996365</v>
+        <v>-155.3803486996365</v>
       </c>
       <c r="Q100">
-        <v>-113.2292108996365</v>
+        <v>-43.28034869963653</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.98242263303571</v>
+        <v>1.945444313550271</v>
       </c>
       <c r="T100">
-        <v>32.64318485008431</v>
+        <v>32.03073219652763</v>
       </c>
       <c r="U100">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V100">
-        <v>0.08311084375768542</v>
+        <v>0.1006964510794085</v>
       </c>
       <c r="W100">
-        <v>0.2362577934896508</v>
+        <v>0.1912577934896508</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4374254934615023</v>
+        <v>0.5299813214705712</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2732998226138227</v>
+        <v>0.2280102562241139</v>
       </c>
       <c r="C101">
-        <v>-1159.000974464029</v>
+        <v>-1030.984652529524</v>
       </c>
       <c r="D101">
-        <v>702.2170255359705</v>
+        <v>830.2333474704756</v>
       </c>
       <c r="E101">
         <v>1321.118</v>
@@ -9569,45 +9569,45 @@
         <v>216.3</v>
       </c>
       <c r="M101">
-        <v>499.5299682421771</v>
+        <v>412.292158242177</v>
       </c>
       <c r="N101">
-        <v>-283.2299682421771</v>
+        <v>-195.9921582421771</v>
       </c>
       <c r="O101">
-        <v>-53.81369396601364</v>
+        <v>-37.23851006601364</v>
       </c>
       <c r="P101">
-        <v>-229.4162742761634</v>
+        <v>-158.7536481761634</v>
       </c>
       <c r="Q101">
-        <v>-117.3162742761634</v>
+        <v>-46.65364817616341</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.919045266071419</v>
+        <v>3.845088627100543</v>
       </c>
       <c r="T101">
-        <v>65.28636970016862</v>
+        <v>64.06146439305526</v>
       </c>
       <c r="U101">
-        <v>0.2576732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V101">
-        <v>0.08227134028538557</v>
+        <v>0.09967931520991956</v>
       </c>
       <c r="W101">
-        <v>0.2364741110637459</v>
+        <v>0.1914741110637459</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4330070541336083</v>
+        <v>0.5246279747890503</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/slovenia/slovenia_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_retail_automotive.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08795261237111252</v>
+        <v>0.08791812559754046</v>
       </c>
       <c r="C2">
-        <v>1981.457427205323</v>
+        <v>1962.482019783637</v>
       </c>
       <c r="D2">
-        <v>1904.057427205323</v>
+        <v>1904.664019783637</v>
       </c>
       <c r="E2">
-        <v>-617.5</v>
+        <v>-597.918</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.582</v>
       </c>
       <c r="G2">
         <v>77.40000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>216.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.217476254971485</v>
       </c>
       <c r="N2">
-        <v>216.3</v>
+        <v>215.0825237450285</v>
       </c>
       <c r="O2">
-        <v>41.09699999999999</v>
+        <v>40.86567951155542</v>
       </c>
       <c r="P2">
-        <v>175.203</v>
+        <v>174.2168442334731</v>
       </c>
       <c r="Q2">
-        <v>287.303</v>
+        <v>286.3168442334731</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08795261237111252</v>
+        <v>0.08829749738142163</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7165688586738307</v>
       </c>
       <c r="U2">
         <v>0.06217323332506819</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>177.6626025491282</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08791812559754046</v>
+        <v>0.08788363882396841</v>
       </c>
       <c r="C3">
-        <v>1962.482019783637</v>
+        <v>1943.506998980348</v>
       </c>
       <c r="D3">
-        <v>1904.664019783637</v>
+        <v>1905.270998980348</v>
       </c>
       <c r="E3">
-        <v>-597.918</v>
+        <v>-578.336</v>
       </c>
       <c r="F3">
-        <v>19.582</v>
+        <v>39.164</v>
       </c>
       <c r="G3">
         <v>77.40000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>216.3</v>
       </c>
       <c r="M3">
-        <v>1.217476254971485</v>
+        <v>2.434952509942971</v>
       </c>
       <c r="N3">
-        <v>215.0825237450285</v>
+        <v>213.865047490057</v>
       </c>
       <c r="O3">
-        <v>40.86567951155542</v>
+        <v>40.63435902311083</v>
       </c>
       <c r="P3">
-        <v>174.2168442334731</v>
+        <v>173.2306884669462</v>
       </c>
       <c r="Q3">
-        <v>286.3168442334731</v>
+        <v>285.3306884669462</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08829749738142163</v>
+        <v>0.08864942086132888</v>
       </c>
       <c r="T3">
-        <v>0.7165688586738307</v>
+        <v>0.7225027941259428</v>
       </c>
       <c r="U3">
         <v>0.06217323332506819</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>177.6626025491282</v>
+        <v>88.83130127456407</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08788363882396841</v>
+        <v>0.08784915205039634</v>
       </c>
       <c r="C4">
-        <v>1943.506998980348</v>
+        <v>1924.532365165199</v>
       </c>
       <c r="D4">
-        <v>1905.270998980348</v>
+        <v>1905.878365165199</v>
       </c>
       <c r="E4">
-        <v>-578.336</v>
+        <v>-558.754</v>
       </c>
       <c r="F4">
-        <v>39.164</v>
+        <v>58.746</v>
       </c>
       <c r="G4">
         <v>77.40000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>216.3</v>
       </c>
       <c r="M4">
-        <v>2.434952509942971</v>
+        <v>3.652428764914456</v>
       </c>
       <c r="N4">
-        <v>213.865047490057</v>
+        <v>212.6475712350855</v>
       </c>
       <c r="O4">
-        <v>40.63435902311083</v>
+        <v>40.40303853466625</v>
       </c>
       <c r="P4">
-        <v>173.2306884669462</v>
+        <v>172.2445327004193</v>
       </c>
       <c r="Q4">
-        <v>285.3306884669462</v>
+        <v>284.3445327004193</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08864942086132888</v>
+        <v>0.08900860049546101</v>
       </c>
       <c r="T4">
-        <v>0.7225027941259428</v>
+        <v>0.7285590787626345</v>
       </c>
       <c r="U4">
         <v>0.06217323332506819</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>88.83130127456407</v>
+        <v>59.22086751637605</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08784915205039634</v>
+        <v>0.08781466527682429</v>
       </c>
       <c r="C5">
-        <v>1924.532365165199</v>
+        <v>1905.558118708401</v>
       </c>
       <c r="D5">
-        <v>1905.878365165199</v>
+        <v>1906.4861187084</v>
       </c>
       <c r="E5">
-        <v>-558.754</v>
+        <v>-539.172</v>
       </c>
       <c r="F5">
-        <v>58.746</v>
+        <v>78.328</v>
       </c>
       <c r="G5">
         <v>77.40000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>216.3</v>
       </c>
       <c r="M5">
-        <v>3.652428764914456</v>
+        <v>4.869905019885941</v>
       </c>
       <c r="N5">
-        <v>212.6475712350855</v>
+        <v>211.430094980114</v>
       </c>
       <c r="O5">
-        <v>40.40303853466625</v>
+        <v>40.17171804622167</v>
       </c>
       <c r="P5">
-        <v>172.2445327004193</v>
+        <v>171.2583769338924</v>
       </c>
       <c r="Q5">
-        <v>284.3445327004193</v>
+        <v>283.3583769338924</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08900860049546101</v>
+        <v>0.08937526303863758</v>
       </c>
       <c r="T5">
-        <v>0.7285590787626345</v>
+        <v>0.7347415359959238</v>
       </c>
       <c r="U5">
         <v>0.06217323332506819</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.22086751637605</v>
+        <v>44.41565063728203</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08781466527682429</v>
+        <v>0.08778017850325222</v>
       </c>
       <c r="C6">
-        <v>1905.558118708401</v>
+        <v>1886.584259980639</v>
       </c>
       <c r="D6">
-        <v>1906.4861187084</v>
+        <v>1907.094259980639</v>
       </c>
       <c r="E6">
-        <v>-539.172</v>
+        <v>-519.59</v>
       </c>
       <c r="F6">
-        <v>78.328</v>
+        <v>97.91000000000001</v>
       </c>
       <c r="G6">
         <v>77.40000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>216.3</v>
       </c>
       <c r="M6">
-        <v>4.869905019885941</v>
+        <v>6.087381274857427</v>
       </c>
       <c r="N6">
-        <v>211.430094980114</v>
+        <v>210.2126187251426</v>
       </c>
       <c r="O6">
-        <v>40.17171804622167</v>
+        <v>39.94039755777709</v>
       </c>
       <c r="P6">
-        <v>171.2583769338924</v>
+        <v>170.2722211673655</v>
       </c>
       <c r="Q6">
-        <v>283.3583769338924</v>
+        <v>282.3722211673655</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08937526303863758</v>
+        <v>0.08974964479324943</v>
       </c>
       <c r="T6">
-        <v>0.7347415359959238</v>
+        <v>0.7410541502235984</v>
       </c>
       <c r="U6">
         <v>0.06217323332506819</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.41565063728203</v>
+        <v>35.53252050982562</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08778017850325222</v>
+        <v>0.08774569172968015</v>
       </c>
       <c r="C7">
-        <v>1886.584259980639</v>
+        <v>1867.610789353073</v>
       </c>
       <c r="D7">
-        <v>1907.094259980639</v>
+        <v>1907.702789353073</v>
       </c>
       <c r="E7">
-        <v>-519.59</v>
+        <v>-500.008</v>
       </c>
       <c r="F7">
-        <v>97.91000000000001</v>
+        <v>117.492</v>
       </c>
       <c r="G7">
         <v>77.40000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>216.3</v>
       </c>
       <c r="M7">
-        <v>6.087381274857427</v>
+        <v>7.304857529828912</v>
       </c>
       <c r="N7">
-        <v>210.2126187251426</v>
+        <v>208.9951424701711</v>
       </c>
       <c r="O7">
-        <v>39.94039755777709</v>
+        <v>39.7090770693325</v>
       </c>
       <c r="P7">
-        <v>170.2722211673655</v>
+        <v>169.2860654008386</v>
       </c>
       <c r="Q7">
-        <v>282.3722211673655</v>
+        <v>281.3860654008386</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08974964479324943</v>
+        <v>0.09013199211710834</v>
       </c>
       <c r="T7">
-        <v>0.7410541502235984</v>
+        <v>0.7475010753922873</v>
       </c>
       <c r="U7">
         <v>0.06217323332506819</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.53252050982562</v>
+        <v>29.61043375818802</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08774569172968015</v>
+        <v>0.0877112049561081</v>
       </c>
       <c r="C8">
-        <v>1867.610789353073</v>
+        <v>1848.637707197332</v>
       </c>
       <c r="D8">
-        <v>1907.702789353073</v>
+        <v>1908.311707197332</v>
       </c>
       <c r="E8">
-        <v>-500.008</v>
+        <v>-480.426</v>
       </c>
       <c r="F8">
-        <v>117.492</v>
+        <v>137.074</v>
       </c>
       <c r="G8">
         <v>77.40000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>216.3</v>
       </c>
       <c r="M8">
-        <v>7.304857529828912</v>
+        <v>8.522333784800395</v>
       </c>
       <c r="N8">
-        <v>208.9951424701711</v>
+        <v>207.7776662151996</v>
       </c>
       <c r="O8">
-        <v>39.7090770693325</v>
+        <v>39.47775658088792</v>
       </c>
       <c r="P8">
-        <v>169.2860654008386</v>
+        <v>168.2999096343117</v>
       </c>
       <c r="Q8">
-        <v>281.3860654008386</v>
+        <v>280.3999096343117</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09013199211710834</v>
+        <v>0.090522561964061</v>
       </c>
       <c r="T8">
-        <v>0.7475010753922873</v>
+        <v>0.7540866441129911</v>
       </c>
       <c r="U8">
         <v>0.06217323332506819</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.61043375818802</v>
+        <v>25.3803717927326</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0877112049561081</v>
+        <v>0.08767671818253604</v>
       </c>
       <c r="C9">
-        <v>1848.637707197332</v>
+        <v>1829.665013885525</v>
       </c>
       <c r="D9">
-        <v>1908.311707197332</v>
+        <v>1908.921013885525</v>
       </c>
       <c r="E9">
-        <v>-480.426</v>
+        <v>-460.844</v>
       </c>
       <c r="F9">
-        <v>137.074</v>
+        <v>156.656</v>
       </c>
       <c r="G9">
         <v>77.40000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>216.3</v>
       </c>
       <c r="M9">
-        <v>8.522333784800397</v>
+        <v>9.739810039771882</v>
       </c>
       <c r="N9">
-        <v>207.7776662151996</v>
+        <v>206.5601899602281</v>
       </c>
       <c r="O9">
-        <v>39.47775658088792</v>
+        <v>39.24643609244334</v>
       </c>
       <c r="P9">
-        <v>168.2999096343117</v>
+        <v>167.3137538677848</v>
       </c>
       <c r="Q9">
-        <v>280.3999096343117</v>
+        <v>279.4137538677847</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.090522561964061</v>
+        <v>0.09092162245986046</v>
       </c>
       <c r="T9">
-        <v>0.7540866441129911</v>
+        <v>0.7608153773711014</v>
       </c>
       <c r="U9">
         <v>0.06217323332506819</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.38037179273259</v>
+        <v>22.20782531864102</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08767671818253604</v>
+        <v>0.08764223140896397</v>
       </c>
       <c r="C10">
-        <v>1829.665013885525</v>
+        <v>1810.692709790234</v>
       </c>
       <c r="D10">
-        <v>1908.921013885525</v>
+        <v>1909.530709790234</v>
       </c>
       <c r="E10">
-        <v>-460.844</v>
+        <v>-441.262</v>
       </c>
       <c r="F10">
-        <v>156.656</v>
+        <v>176.238</v>
       </c>
       <c r="G10">
         <v>77.40000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>216.3</v>
       </c>
       <c r="M10">
-        <v>9.739810039771882</v>
+        <v>10.95728629474337</v>
       </c>
       <c r="N10">
-        <v>206.5601899602281</v>
+        <v>205.3427137052566</v>
       </c>
       <c r="O10">
-        <v>39.24643609244334</v>
+        <v>39.01511560399876</v>
       </c>
       <c r="P10">
-        <v>167.3137538677848</v>
+        <v>166.3275981012578</v>
       </c>
       <c r="Q10">
-        <v>279.4137538677847</v>
+        <v>278.4275981012578</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09092162245986046</v>
+        <v>0.09132945351600713</v>
       </c>
       <c r="T10">
-        <v>0.7608153773711014</v>
+        <v>0.7676919948766425</v>
       </c>
       <c r="U10">
         <v>0.06217323332506819</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.20782531864102</v>
+        <v>19.74028917212535</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08764223140896397</v>
+        <v>0.08760774463539192</v>
       </c>
       <c r="C11">
-        <v>1810.692709790234</v>
+        <v>1791.720795284516</v>
       </c>
       <c r="D11">
-        <v>1909.530709790234</v>
+        <v>1910.140795284515</v>
       </c>
       <c r="E11">
-        <v>-441.262</v>
+        <v>-421.68</v>
       </c>
       <c r="F11">
-        <v>176.238</v>
+        <v>195.82</v>
       </c>
       <c r="G11">
         <v>77.40000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>216.3</v>
       </c>
       <c r="M11">
-        <v>10.95728629474337</v>
+        <v>12.17476254971485</v>
       </c>
       <c r="N11">
-        <v>205.3427137052566</v>
+        <v>204.1252374502851</v>
       </c>
       <c r="O11">
-        <v>39.01511560399876</v>
+        <v>38.78379511555418</v>
       </c>
       <c r="P11">
-        <v>166.3275981012578</v>
+        <v>165.341442334731</v>
       </c>
       <c r="Q11">
-        <v>278.4275981012578</v>
+        <v>277.4414423347309</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09132945351600713</v>
+        <v>0.09174634748451266</v>
       </c>
       <c r="T11">
-        <v>0.7676919948766425</v>
+        <v>0.7747214261045293</v>
       </c>
       <c r="U11">
         <v>0.06217323332506819</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.74028917212535</v>
+        <v>17.76626025491282</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08760774463539192</v>
+        <v>0.08757325786181985</v>
       </c>
       <c r="C12">
-        <v>1791.720795284516</v>
+        <v>1772.749270741906</v>
       </c>
       <c r="D12">
-        <v>1910.140795284515</v>
+        <v>1910.751270741906</v>
       </c>
       <c r="E12">
-        <v>-421.6799999999999</v>
+        <v>-402.098</v>
       </c>
       <c r="F12">
-        <v>195.82</v>
+        <v>215.402</v>
       </c>
       <c r="G12">
         <v>77.40000000000001</v>
@@ -2271,28 +2271,28 @@
         <v>216.3</v>
       </c>
       <c r="M12">
-        <v>12.17476254971485</v>
+        <v>13.39223880468634</v>
       </c>
       <c r="N12">
-        <v>204.1252374502851</v>
+        <v>202.9077611953136</v>
       </c>
       <c r="O12">
-        <v>38.78379511555418</v>
+        <v>38.55247462710959</v>
       </c>
       <c r="P12">
-        <v>165.341442334731</v>
+        <v>164.3552865682041</v>
       </c>
       <c r="Q12">
-        <v>277.4414423347309</v>
+        <v>276.4552865682041</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09174634748451266</v>
+        <v>0.09217260985680481</v>
       </c>
       <c r="T12">
-        <v>0.7747214261045293</v>
+        <v>0.7819088220791099</v>
       </c>
       <c r="U12">
         <v>0.06217323332506819</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.76626025491281</v>
+        <v>16.15114568628437</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08757325786181985</v>
+        <v>0.0875387710882478</v>
       </c>
       <c r="C13">
-        <v>1772.749270741906</v>
+        <v>1753.778136536418</v>
       </c>
       <c r="D13">
-        <v>1910.751270741906</v>
+        <v>1911.362136536418</v>
       </c>
       <c r="E13">
-        <v>-402.098</v>
+        <v>-382.516</v>
       </c>
       <c r="F13">
-        <v>215.402</v>
+        <v>234.984</v>
       </c>
       <c r="G13">
         <v>77.40000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>216.3</v>
       </c>
       <c r="M13">
-        <v>13.39223880468634</v>
+        <v>14.60971505965782</v>
       </c>
       <c r="N13">
-        <v>202.9077611953136</v>
+        <v>201.6902849403422</v>
       </c>
       <c r="O13">
-        <v>38.55247462710959</v>
+        <v>38.32115413866502</v>
       </c>
       <c r="P13">
-        <v>164.3552865682041</v>
+        <v>163.3691308016772</v>
       </c>
       <c r="Q13">
-        <v>276.4552865682041</v>
+        <v>275.4691308016771</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09217260985680481</v>
+        <v>0.09260856001028542</v>
       </c>
       <c r="T13">
-        <v>0.7819088220791099</v>
+        <v>0.7892595679622039</v>
       </c>
       <c r="U13">
         <v>0.06217323332506819</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.15114568628437</v>
+        <v>14.80521687909401</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0875387710882478</v>
+        <v>0.08750428431467573</v>
       </c>
       <c r="C14">
-        <v>1753.778136536418</v>
+        <v>1734.807393042542</v>
       </c>
       <c r="D14">
-        <v>1911.362136536418</v>
+        <v>1911.973393042542</v>
       </c>
       <c r="E14">
-        <v>-382.516</v>
+        <v>-362.934</v>
       </c>
       <c r="F14">
-        <v>234.984</v>
+        <v>254.566</v>
       </c>
       <c r="G14">
         <v>77.40000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>216.3</v>
       </c>
       <c r="M14">
-        <v>14.60971505965782</v>
+        <v>15.82719131462931</v>
       </c>
       <c r="N14">
-        <v>201.6902849403422</v>
+        <v>200.4728086853707</v>
       </c>
       <c r="O14">
-        <v>38.32115413866502</v>
+        <v>38.08983365022043</v>
       </c>
       <c r="P14">
-        <v>163.3691308016772</v>
+        <v>162.3829750351503</v>
       </c>
       <c r="Q14">
-        <v>275.4691308016771</v>
+        <v>274.4829750351503</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09260856001028542</v>
+        <v>0.09305453200637477</v>
       </c>
       <c r="T14">
-        <v>0.7892595679622039</v>
+        <v>0.796779296509277</v>
       </c>
       <c r="U14">
         <v>0.06217323332506819</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.80521687909401</v>
+        <v>13.66635404224063</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08750428431467573</v>
+        <v>0.08763989754110366</v>
       </c>
       <c r="C15">
-        <v>1734.807393042542</v>
+        <v>1712.823984597249</v>
       </c>
       <c r="D15">
-        <v>1911.973393042542</v>
+        <v>1909.571984597249</v>
       </c>
       <c r="E15">
-        <v>-362.934</v>
+        <v>-343.352</v>
       </c>
       <c r="F15">
-        <v>254.566</v>
+        <v>274.148</v>
       </c>
       <c r="G15">
         <v>77.40000000000001</v>
@@ -2517,45 +2517,45 @@
         <v>216.3</v>
       </c>
       <c r="M15">
-        <v>15.82719131462931</v>
+        <v>17.4558895696008</v>
       </c>
       <c r="N15">
-        <v>200.4728086853707</v>
+        <v>198.8441104303992</v>
       </c>
       <c r="O15">
-        <v>38.08983365022043</v>
+        <v>37.78038098177584</v>
       </c>
       <c r="P15">
-        <v>162.3829750351503</v>
+        <v>161.0637294486233</v>
       </c>
       <c r="Q15">
-        <v>274.4829750351503</v>
+        <v>273.1637294486234</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09305453200637477</v>
+        <v>0.09351087544423364</v>
       </c>
       <c r="T15">
-        <v>0.796779296509277</v>
+        <v>0.8044739024644216</v>
       </c>
       <c r="U15">
-        <v>0.06217323332506819</v>
+        <v>0.06367323332506819</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.05036031899330524</v>
+        <v>0.05157531899330524</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.66635404224063</v>
+        <v>12.39123329335697</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08763989754110366</v>
+        <v>0.08761756076753162</v>
       </c>
       <c r="C16">
-        <v>1712.823984597249</v>
+        <v>1693.637104102941</v>
       </c>
       <c r="D16">
-        <v>1909.571984597249</v>
+        <v>1909.967104102941</v>
       </c>
       <c r="E16">
-        <v>-343.352</v>
+        <v>-323.7699999999999</v>
       </c>
       <c r="F16">
-        <v>274.148</v>
+        <v>293.7300000000001</v>
       </c>
       <c r="G16">
         <v>77.40000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>216.3</v>
       </c>
       <c r="M16">
-        <v>17.4558895696008</v>
+        <v>18.70273882457229</v>
       </c>
       <c r="N16">
-        <v>198.8441104303992</v>
+        <v>197.5972611754277</v>
       </c>
       <c r="O16">
-        <v>37.78038098177584</v>
+        <v>37.54347962333126</v>
       </c>
       <c r="P16">
-        <v>161.0637294486233</v>
+        <v>160.0537815520964</v>
       </c>
       <c r="Q16">
-        <v>273.1637294486234</v>
+        <v>272.1537815520965</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09351087544423364</v>
+        <v>0.09397795637474803</v>
       </c>
       <c r="T16">
-        <v>0.8044739024644216</v>
+        <v>0.8123495579714519</v>
       </c>
       <c r="U16">
         <v>0.06367323332506819</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.39123329335697</v>
+        <v>11.56515107379983</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0876175607675316</v>
+        <v>0.08759522399395955</v>
       </c>
       <c r="C17">
-        <v>1693.637104102941</v>
+        <v>1674.450387154952</v>
       </c>
       <c r="D17">
-        <v>1909.967104102941</v>
+        <v>1910.362387154952</v>
       </c>
       <c r="E17">
-        <v>-323.77</v>
+        <v>-304.188</v>
       </c>
       <c r="F17">
-        <v>293.73</v>
+        <v>313.312</v>
       </c>
       <c r="G17">
         <v>77.40000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>216.3</v>
       </c>
       <c r="M17">
-        <v>18.70273882457228</v>
+        <v>19.94958807954377</v>
       </c>
       <c r="N17">
-        <v>197.5972611754277</v>
+        <v>196.3504119204562</v>
       </c>
       <c r="O17">
-        <v>37.54347962333127</v>
+        <v>37.30657826488668</v>
       </c>
       <c r="P17">
-        <v>160.0537815520964</v>
+        <v>159.0438336555695</v>
       </c>
       <c r="Q17">
-        <v>272.1537815520965</v>
+        <v>271.1438336555696</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09397795637474803</v>
+        <v>0.09445615827979846</v>
       </c>
       <c r="T17">
-        <v>0.8123495579714519</v>
+        <v>0.8204127290857924</v>
       </c>
       <c r="U17">
         <v>0.06367323332506819</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.56515107379984</v>
+        <v>10.84232913168735</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08759522399395955</v>
+        <v>0.08757288722038749</v>
       </c>
       <c r="C18">
-        <v>1674.450387154952</v>
+        <v>1655.263833854844</v>
       </c>
       <c r="D18">
-        <v>1910.362387154952</v>
+        <v>1910.757833854844</v>
       </c>
       <c r="E18">
-        <v>-304.188</v>
+        <v>-284.606</v>
       </c>
       <c r="F18">
-        <v>313.312</v>
+        <v>332.894</v>
       </c>
       <c r="G18">
         <v>77.40000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>216.3</v>
       </c>
       <c r="M18">
-        <v>19.94958807954377</v>
+        <v>21.19643733451525</v>
       </c>
       <c r="N18">
-        <v>196.3504119204562</v>
+        <v>195.1035626654847</v>
       </c>
       <c r="O18">
-        <v>37.30657826488668</v>
+        <v>37.0696769064421</v>
       </c>
       <c r="P18">
-        <v>159.0438336555695</v>
+        <v>158.0338857590426</v>
       </c>
       <c r="Q18">
-        <v>271.1438336555696</v>
+        <v>270.1338857590426</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09445615827979846</v>
+        <v>0.09494588312232</v>
       </c>
       <c r="T18">
-        <v>0.8204127290857924</v>
+        <v>0.8286701934799967</v>
       </c>
       <c r="U18">
         <v>0.06367323332506819</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.84232913168735</v>
+        <v>10.2045450651175</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08757288722038749</v>
+        <v>0.08779841044681541</v>
       </c>
       <c r="C19">
-        <v>1655.263833854844</v>
+        <v>1631.696708761607</v>
       </c>
       <c r="D19">
-        <v>1910.757833854844</v>
+        <v>1906.772708761607</v>
       </c>
       <c r="E19">
-        <v>-284.606</v>
+        <v>-265.0239999999999</v>
       </c>
       <c r="F19">
-        <v>332.894</v>
+        <v>352.4760000000001</v>
       </c>
       <c r="G19">
         <v>77.40000000000001</v>
@@ -2845,45 +2845,45 @@
         <v>216.3</v>
       </c>
       <c r="M19">
-        <v>21.19643733451525</v>
+        <v>23.04249578948674</v>
       </c>
       <c r="N19">
-        <v>195.1035626654847</v>
+        <v>193.2575042105132</v>
       </c>
       <c r="O19">
-        <v>37.0696769064421</v>
+        <v>36.71892579999751</v>
       </c>
       <c r="P19">
-        <v>158.0338857590426</v>
+        <v>156.5385784105157</v>
       </c>
       <c r="Q19">
-        <v>270.1338857590426</v>
+        <v>268.6385784105157</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09494588312232</v>
+        <v>0.0954475524731957</v>
       </c>
       <c r="T19">
-        <v>0.8286701934799967</v>
+        <v>0.8371290594447911</v>
       </c>
       <c r="U19">
-        <v>0.06367323332506819</v>
+        <v>0.06537323332506818</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.05157531899330524</v>
+        <v>0.05295231899330523</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.2045450651175</v>
+        <v>9.387003993668431</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08779841044681543</v>
+        <v>0.08778984367324336</v>
       </c>
       <c r="C20">
-        <v>1631.696708761607</v>
+        <v>1612.265784824177</v>
       </c>
       <c r="D20">
-        <v>1906.772708761607</v>
+        <v>1906.923784824177</v>
       </c>
       <c r="E20">
-        <v>-265.024</v>
+        <v>-245.442</v>
       </c>
       <c r="F20">
-        <v>352.476</v>
+        <v>372.058</v>
       </c>
       <c r="G20">
         <v>77.40000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>216.3</v>
       </c>
       <c r="M20">
-        <v>23.04249578948673</v>
+        <v>24.32263444445822</v>
       </c>
       <c r="N20">
-        <v>193.2575042105132</v>
+        <v>191.9773655555418</v>
       </c>
       <c r="O20">
-        <v>36.71892579999751</v>
+        <v>36.47569945555294</v>
       </c>
       <c r="P20">
-        <v>156.5385784105157</v>
+        <v>155.5016660999888</v>
       </c>
       <c r="Q20">
-        <v>268.6385784105157</v>
+        <v>267.6016660999888</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0954475524731957</v>
+        <v>0.0959616087216239</v>
       </c>
       <c r="T20">
-        <v>0.8371290594447911</v>
+        <v>0.8457967862976052</v>
       </c>
       <c r="U20">
         <v>0.06537323332506818</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.387003993668431</v>
+        <v>8.89295115189641</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08778984367324336</v>
+        <v>0.08778127689967131</v>
       </c>
       <c r="C21">
-        <v>1612.265784824177</v>
+        <v>1592.834884828546</v>
       </c>
       <c r="D21">
-        <v>1906.923784824177</v>
+        <v>1907.074884828546</v>
       </c>
       <c r="E21">
-        <v>-245.442</v>
+        <v>-225.86</v>
       </c>
       <c r="F21">
-        <v>372.058</v>
+        <v>391.64</v>
       </c>
       <c r="G21">
         <v>77.40000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>216.3</v>
       </c>
       <c r="M21">
-        <v>24.32263444445822</v>
+        <v>25.6027730994297</v>
       </c>
       <c r="N21">
-        <v>191.9773655555418</v>
+        <v>190.6972269005703</v>
       </c>
       <c r="O21">
-        <v>36.47569945555294</v>
+        <v>36.23247311110836</v>
       </c>
       <c r="P21">
-        <v>155.5016660999888</v>
+        <v>154.4647537894619</v>
       </c>
       <c r="Q21">
-        <v>267.6016660999888</v>
+        <v>266.5647537894619</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0959616087216239</v>
+        <v>0.09648851637626282</v>
       </c>
       <c r="T21">
-        <v>0.8457967862976052</v>
+        <v>0.8546812063217399</v>
       </c>
       <c r="U21">
         <v>0.06537323332506818</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.89295115189641</v>
+        <v>8.448303594301589</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08778127689967131</v>
+        <v>0.08777271012609925</v>
       </c>
       <c r="C22">
-        <v>1592.834884828546</v>
+        <v>1573.404008780408</v>
       </c>
       <c r="D22">
-        <v>1907.074884828546</v>
+        <v>1907.226008780408</v>
       </c>
       <c r="E22">
-        <v>-225.86</v>
+        <v>-206.278</v>
       </c>
       <c r="F22">
-        <v>391.64</v>
+        <v>411.222</v>
       </c>
       <c r="G22">
         <v>77.40000000000001</v>
@@ -3091,28 +3091,28 @@
         <v>216.3</v>
       </c>
       <c r="M22">
-        <v>25.6027730994297</v>
+        <v>26.88291175440119</v>
       </c>
       <c r="N22">
-        <v>190.6972269005703</v>
+        <v>189.4170882455988</v>
       </c>
       <c r="O22">
-        <v>36.23247311110836</v>
+        <v>35.98924676666377</v>
       </c>
       <c r="P22">
-        <v>154.4647537894619</v>
+        <v>153.427841478935</v>
       </c>
       <c r="Q22">
-        <v>266.5647537894619</v>
+        <v>265.527841478935</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09648851637626282</v>
+        <v>0.09702876346519637</v>
       </c>
       <c r="T22">
-        <v>0.8546812063217399</v>
+        <v>0.8637905483718018</v>
       </c>
       <c r="U22">
         <v>0.06537323332506818</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.448303594301589</v>
+        <v>8.04600342314437</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08777271012609923</v>
+        <v>0.08776414335252718</v>
       </c>
       <c r="C23">
-        <v>1573.404008780408</v>
+        <v>1553.973156685454</v>
       </c>
       <c r="D23">
-        <v>1907.226008780408</v>
+        <v>1907.377156685454</v>
       </c>
       <c r="E23">
-        <v>-206.278</v>
+        <v>-186.696</v>
       </c>
       <c r="F23">
-        <v>411.222</v>
+        <v>430.804</v>
       </c>
       <c r="G23">
         <v>77.40000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>216.3</v>
       </c>
       <c r="M23">
-        <v>26.88291175440119</v>
+        <v>28.16305040937268</v>
       </c>
       <c r="N23">
-        <v>189.4170882455988</v>
+        <v>188.1369495906273</v>
       </c>
       <c r="O23">
-        <v>35.98924676666377</v>
+        <v>35.74602042221919</v>
       </c>
       <c r="P23">
-        <v>153.427841478935</v>
+        <v>152.3909291684081</v>
       </c>
       <c r="Q23">
-        <v>265.527841478935</v>
+        <v>264.4909291684081</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09702876346519637</v>
+        <v>0.09758286304358976</v>
       </c>
       <c r="T23">
-        <v>0.8637905483718018</v>
+        <v>0.8731334632949422</v>
       </c>
       <c r="U23">
         <v>0.06537323332506818</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.04600342314437</v>
+        <v>7.680275994819625</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08776414335252718</v>
+        <v>0.08790461657895511</v>
       </c>
       <c r="C24">
-        <v>1553.973156685454</v>
+        <v>1531.915737123129</v>
       </c>
       <c r="D24">
-        <v>1907.377156685454</v>
+        <v>1904.901737123129</v>
       </c>
       <c r="E24">
-        <v>-186.696</v>
+        <v>-167.114</v>
       </c>
       <c r="F24">
-        <v>430.804</v>
+        <v>450.386</v>
       </c>
       <c r="G24">
         <v>77.40000000000001</v>
@@ -3255,45 +3255,45 @@
         <v>216.3</v>
       </c>
       <c r="M24">
-        <v>28.16305040937268</v>
+        <v>29.80349786434417</v>
       </c>
       <c r="N24">
-        <v>188.1369495906273</v>
+        <v>186.4965021356558</v>
       </c>
       <c r="O24">
-        <v>35.74602042221919</v>
+        <v>35.4343354057746</v>
       </c>
       <c r="P24">
-        <v>152.3909291684081</v>
+        <v>151.0621667298812</v>
       </c>
       <c r="Q24">
-        <v>264.4909291684081</v>
+        <v>263.1621667298812</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09758286304358976</v>
+        <v>0.09815135481882456</v>
       </c>
       <c r="T24">
-        <v>0.8731334632949422</v>
+        <v>0.8827190513329695</v>
       </c>
       <c r="U24">
-        <v>0.06537323332506818</v>
+        <v>0.06617323332506819</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.05295231899330523</v>
+        <v>0.05360031899330524</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.680275994819625</v>
+        <v>7.257537386535207</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08790461657895511</v>
+        <v>0.08790252980538305</v>
       </c>
       <c r="C25">
-        <v>1531.915737123129</v>
+        <v>1512.370463235856</v>
       </c>
       <c r="D25">
-        <v>1904.901737123129</v>
+        <v>1904.938463235856</v>
       </c>
       <c r="E25">
-        <v>-167.114</v>
+        <v>-147.5319999999999</v>
       </c>
       <c r="F25">
-        <v>450.386</v>
+        <v>469.9680000000001</v>
       </c>
       <c r="G25">
         <v>77.40000000000001</v>
@@ -3337,28 +3337,28 @@
         <v>216.3</v>
       </c>
       <c r="M25">
-        <v>29.80349786434417</v>
+        <v>31.09930211931565</v>
       </c>
       <c r="N25">
-        <v>186.4965021356558</v>
+        <v>185.2006978806843</v>
       </c>
       <c r="O25">
-        <v>35.4343354057746</v>
+        <v>35.18813259733002</v>
       </c>
       <c r="P25">
-        <v>151.0621667298812</v>
+        <v>150.0125652833543</v>
       </c>
       <c r="Q25">
-        <v>263.1621667298812</v>
+        <v>262.1125652833543</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09815135481882456</v>
+        <v>0.09873480690393394</v>
       </c>
       <c r="T25">
-        <v>0.8827190513329695</v>
+        <v>0.892556891687787</v>
       </c>
       <c r="U25">
         <v>0.06617323332506819</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.257537386535207</v>
+        <v>6.955139995429573</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08790252980538305</v>
+        <v>0.08790044303181101</v>
       </c>
       <c r="C26">
-        <v>1512.370463235856</v>
+        <v>1492.825190764753</v>
       </c>
       <c r="D26">
-        <v>1904.938463235856</v>
+        <v>1904.975190764753</v>
       </c>
       <c r="E26">
-        <v>-147.532</v>
+        <v>-127.95</v>
       </c>
       <c r="F26">
-        <v>469.968</v>
+        <v>489.55</v>
       </c>
       <c r="G26">
         <v>77.40000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>216.3</v>
       </c>
       <c r="M26">
-        <v>31.09930211931565</v>
+        <v>32.39510637428713</v>
       </c>
       <c r="N26">
-        <v>185.2006978806843</v>
+        <v>183.9048936257128</v>
       </c>
       <c r="O26">
-        <v>35.18813259733002</v>
+        <v>34.94192978888544</v>
       </c>
       <c r="P26">
-        <v>150.0125652833543</v>
+        <v>148.9629638368274</v>
       </c>
       <c r="Q26">
-        <v>262.1125652833543</v>
+        <v>261.0629638368274</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09873480690393394</v>
+        <v>0.09933381771131292</v>
       </c>
       <c r="T26">
-        <v>0.892556891687787</v>
+        <v>0.9026570744520662</v>
       </c>
       <c r="U26">
         <v>0.06617323332506819</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.955139995429574</v>
+        <v>6.676934395612391</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08790044303181101</v>
+        <v>0.08789835625823893</v>
       </c>
       <c r="C27">
-        <v>1492.825190764753</v>
+        <v>1473.279919709904</v>
       </c>
       <c r="D27">
-        <v>1904.975190764753</v>
+        <v>1905.011919709904</v>
       </c>
       <c r="E27">
-        <v>-127.95</v>
+        <v>-108.368</v>
       </c>
       <c r="F27">
-        <v>489.55</v>
+        <v>509.132</v>
       </c>
       <c r="G27">
         <v>77.40000000000001</v>
@@ -3501,28 +3501,28 @@
         <v>216.3</v>
       </c>
       <c r="M27">
-        <v>32.39510637428713</v>
+        <v>33.69091062925862</v>
       </c>
       <c r="N27">
-        <v>183.9048936257128</v>
+        <v>182.6090893707414</v>
       </c>
       <c r="O27">
-        <v>34.94192978888544</v>
+        <v>34.69572698044086</v>
       </c>
       <c r="P27">
-        <v>148.9629638368274</v>
+        <v>147.9133623903005</v>
       </c>
       <c r="Q27">
-        <v>261.0629638368274</v>
+        <v>260.0133623903005</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09933381771131292</v>
+        <v>0.09994901799997238</v>
       </c>
       <c r="T27">
-        <v>0.9026570744520662</v>
+        <v>0.9130302351288936</v>
       </c>
       <c r="U27">
         <v>0.06617323332506819</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.676934395612391</v>
+        <v>6.420129226550377</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08789835625823893</v>
+        <v>0.08789626948466686</v>
       </c>
       <c r="C28">
-        <v>1473.279919709904</v>
+        <v>1453.73465007139</v>
       </c>
       <c r="D28">
-        <v>1905.011919709904</v>
+        <v>1905.04865007139</v>
       </c>
       <c r="E28">
-        <v>-108.368</v>
+        <v>-88.78599999999994</v>
       </c>
       <c r="F28">
-        <v>509.132</v>
+        <v>528.7140000000001</v>
       </c>
       <c r="G28">
         <v>77.40000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>216.3</v>
       </c>
       <c r="M28">
-        <v>33.69091062925862</v>
+        <v>34.98671488423011</v>
       </c>
       <c r="N28">
-        <v>182.6090893707414</v>
+        <v>181.3132851157699</v>
       </c>
       <c r="O28">
-        <v>34.69572698044086</v>
+        <v>34.44952417199627</v>
       </c>
       <c r="P28">
-        <v>147.9133623903005</v>
+        <v>146.8637609437736</v>
       </c>
       <c r="Q28">
-        <v>260.0133623903005</v>
+        <v>258.9637609437736</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09994901799997238</v>
+        <v>0.1005810730910609</v>
       </c>
       <c r="T28">
-        <v>0.9130302351288936</v>
+        <v>0.9236875919886476</v>
       </c>
       <c r="U28">
         <v>0.06617323332506819</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.420129226550377</v>
+        <v>6.182346662604065</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08789626948466686</v>
+        <v>0.08812098271109479</v>
       </c>
       <c r="C29">
-        <v>1453.73465007139</v>
+        <v>1430.20547752167</v>
       </c>
       <c r="D29">
-        <v>1905.04865007139</v>
+        <v>1901.10147752167</v>
       </c>
       <c r="E29">
-        <v>-88.78599999999994</v>
+        <v>-69.20399999999995</v>
       </c>
       <c r="F29">
-        <v>528.7140000000001</v>
+        <v>548.296</v>
       </c>
       <c r="G29">
         <v>77.40000000000001</v>
@@ -3665,45 +3665,45 @@
         <v>216.3</v>
       </c>
       <c r="M29">
-        <v>34.98671488423011</v>
+        <v>36.83081513920159</v>
       </c>
       <c r="N29">
-        <v>181.3132851157699</v>
+        <v>179.4691848607984</v>
       </c>
       <c r="O29">
-        <v>34.44952417199627</v>
+        <v>34.0991451235517</v>
       </c>
       <c r="P29">
-        <v>146.8637609437736</v>
+        <v>145.3700397372467</v>
       </c>
       <c r="Q29">
-        <v>258.9637609437736</v>
+        <v>257.4700397372467</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1005810730910609</v>
+        <v>0.101230685268013</v>
       </c>
       <c r="T29">
-        <v>0.9236875919886476</v>
+        <v>0.9346409865389503</v>
       </c>
       <c r="U29">
-        <v>0.06617323332506819</v>
+        <v>0.06717323332506819</v>
       </c>
       <c r="V29">
         <v>0.19</v>
       </c>
       <c r="W29">
-        <v>0.05360031899330524</v>
+        <v>0.05441031899330524</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.182346662604065</v>
+        <v>5.872799697277862</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08812098271109479</v>
+        <v>0.08812699593752274</v>
       </c>
       <c r="C30">
-        <v>1430.20547752167</v>
+        <v>1410.5180776253</v>
       </c>
       <c r="D30">
-        <v>1901.10147752167</v>
+        <v>1900.9960776253</v>
       </c>
       <c r="E30">
-        <v>-69.20399999999995</v>
+        <v>-49.62199999999996</v>
       </c>
       <c r="F30">
-        <v>548.296</v>
+        <v>567.878</v>
       </c>
       <c r="G30">
         <v>77.40000000000001</v>
@@ -3747,28 +3747,28 @@
         <v>216.3</v>
       </c>
       <c r="M30">
-        <v>36.83081513920159</v>
+        <v>38.14620139417308</v>
       </c>
       <c r="N30">
-        <v>179.4691848607984</v>
+        <v>178.1537986058269</v>
       </c>
       <c r="O30">
-        <v>34.0991451235517</v>
+        <v>33.84922173510711</v>
       </c>
       <c r="P30">
-        <v>145.3700397372467</v>
+        <v>144.3045768707198</v>
       </c>
       <c r="Q30">
-        <v>257.4700397372467</v>
+        <v>256.4045768707198</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.101230685268013</v>
+        <v>0.1018985963795271</v>
       </c>
       <c r="T30">
-        <v>0.9346409865389503</v>
+        <v>0.945902927414614</v>
       </c>
       <c r="U30">
         <v>0.06717323332506819</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.872799697277862</v>
+        <v>5.67028936288897</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08812699593752274</v>
+        <v>0.08813300916395068</v>
       </c>
       <c r="C31">
-        <v>1410.5180776253</v>
+        <v>1390.830689415336</v>
       </c>
       <c r="D31">
-        <v>1900.9960776253</v>
+        <v>1900.890689415336</v>
       </c>
       <c r="E31">
-        <v>-49.62200000000007</v>
+        <v>-30.03999999999996</v>
       </c>
       <c r="F31">
-        <v>567.8779999999999</v>
+        <v>587.46</v>
       </c>
       <c r="G31">
         <v>77.40000000000001</v>
@@ -3829,28 +3829,28 @@
         <v>216.3</v>
       </c>
       <c r="M31">
-        <v>38.14620139417307</v>
+        <v>39.46158764914456</v>
       </c>
       <c r="N31">
-        <v>178.1537986058269</v>
+        <v>176.8384123508554</v>
       </c>
       <c r="O31">
-        <v>33.84922173510711</v>
+        <v>33.59929834666254</v>
       </c>
       <c r="P31">
-        <v>144.3045768707198</v>
+        <v>143.2391140041929</v>
       </c>
       <c r="Q31">
-        <v>256.4045768707198</v>
+        <v>255.3391140041929</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1018985963795271</v>
+        <v>0.1025855906656559</v>
       </c>
       <c r="T31">
-        <v>0.9459029274146138</v>
+        <v>0.957486638029582</v>
       </c>
       <c r="U31">
         <v>0.06717323332506819</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.670289362888971</v>
+        <v>5.481279717459338</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08813300916395068</v>
+        <v>0.08813902239037862</v>
       </c>
       <c r="C32">
-        <v>1390.830689415336</v>
+        <v>1371.143312889835</v>
       </c>
       <c r="D32">
-        <v>1900.890689415336</v>
+        <v>1900.785312889835</v>
       </c>
       <c r="E32">
-        <v>-30.03999999999996</v>
+        <v>-10.45799999999997</v>
       </c>
       <c r="F32">
-        <v>587.46</v>
+        <v>607.042</v>
       </c>
       <c r="G32">
         <v>77.40000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>216.3</v>
       </c>
       <c r="M32">
-        <v>39.46158764914456</v>
+        <v>40.77697390411605</v>
       </c>
       <c r="N32">
-        <v>176.8384123508554</v>
+        <v>175.5230260958839</v>
       </c>
       <c r="O32">
-        <v>33.59929834666254</v>
+        <v>33.34937495821795</v>
       </c>
       <c r="P32">
-        <v>143.2391140041929</v>
+        <v>142.173651137666</v>
       </c>
       <c r="Q32">
-        <v>255.3391140041929</v>
+        <v>254.273651137666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1025855906656559</v>
+        <v>0.1032924978296435</v>
       </c>
       <c r="T32">
-        <v>0.957486638029582</v>
+        <v>0.9694061083725203</v>
       </c>
       <c r="U32">
         <v>0.06717323332506819</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.481279717459338</v>
+        <v>5.304464242702585</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08813902239037862</v>
+        <v>0.08814503561680656</v>
       </c>
       <c r="C33">
-        <v>1371.143312889835</v>
+        <v>1351.455948046854</v>
       </c>
       <c r="D33">
-        <v>1900.785312889835</v>
+        <v>1900.679948046854</v>
       </c>
       <c r="E33">
-        <v>-10.45799999999997</v>
+        <v>9.124000000000024</v>
       </c>
       <c r="F33">
-        <v>607.042</v>
+        <v>626.624</v>
       </c>
       <c r="G33">
         <v>77.40000000000001</v>
@@ -3993,28 +3993,28 @@
         <v>216.3</v>
       </c>
       <c r="M33">
-        <v>40.77697390411605</v>
+        <v>42.09236015908753</v>
       </c>
       <c r="N33">
-        <v>175.5230260958839</v>
+        <v>174.2076398409125</v>
       </c>
       <c r="O33">
-        <v>33.34937495821795</v>
+        <v>33.09945156977337</v>
       </c>
       <c r="P33">
-        <v>142.173651137666</v>
+        <v>141.1081882711391</v>
       </c>
       <c r="Q33">
-        <v>254.273651137666</v>
+        <v>253.2081882711391</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1032924978296435</v>
+        <v>0.1040201963808072</v>
       </c>
       <c r="T33">
-        <v>0.9694061083725203</v>
+        <v>0.9816761513726038</v>
       </c>
       <c r="U33">
         <v>0.06717323332506819</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.304464242702585</v>
+        <v>5.138699735118129</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08814503561680656</v>
+        <v>0.08815104884323449</v>
       </c>
       <c r="C34">
-        <v>1351.455948046854</v>
+        <v>1331.768594884451</v>
       </c>
       <c r="D34">
-        <v>1900.679948046854</v>
+        <v>1900.574594884451</v>
       </c>
       <c r="E34">
-        <v>9.124000000000024</v>
+        <v>28.70600000000002</v>
       </c>
       <c r="F34">
-        <v>626.624</v>
+        <v>646.206</v>
       </c>
       <c r="G34">
         <v>77.40000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>216.3</v>
       </c>
       <c r="M34">
-        <v>42.09236015908753</v>
+        <v>43.40774641405902</v>
       </c>
       <c r="N34">
-        <v>174.2076398409125</v>
+        <v>172.892253585941</v>
       </c>
       <c r="O34">
-        <v>33.09945156977337</v>
+        <v>32.84952818132879</v>
       </c>
       <c r="P34">
-        <v>141.1081882711391</v>
+        <v>140.0427254046122</v>
       </c>
       <c r="Q34">
-        <v>253.2081882711391</v>
+        <v>252.1427254046122</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1040201963808072</v>
+        <v>0.1047696172767817</v>
       </c>
       <c r="T34">
-        <v>0.9816761513726038</v>
+        <v>0.9943124643129883</v>
       </c>
       <c r="U34">
         <v>0.06717323332506819</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.138699735118129</v>
+        <v>4.982981561326671</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08815104884323449</v>
+        <v>0.08815706206966244</v>
       </c>
       <c r="C35">
-        <v>1331.768594884451</v>
+        <v>1312.081253400682</v>
       </c>
       <c r="D35">
-        <v>1900.574594884451</v>
+        <v>1900.469253400682</v>
       </c>
       <c r="E35">
-        <v>28.70600000000002</v>
+        <v>48.28800000000001</v>
       </c>
       <c r="F35">
-        <v>646.206</v>
+        <v>665.788</v>
       </c>
       <c r="G35">
         <v>77.40000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>216.3</v>
       </c>
       <c r="M35">
-        <v>43.40774641405902</v>
+        <v>44.72313266903051</v>
       </c>
       <c r="N35">
-        <v>172.892253585941</v>
+        <v>171.5768673309695</v>
       </c>
       <c r="O35">
-        <v>32.84952818132879</v>
+        <v>32.5996047928842</v>
       </c>
       <c r="P35">
-        <v>140.0427254046122</v>
+        <v>138.9772625380853</v>
       </c>
       <c r="Q35">
-        <v>252.1427254046122</v>
+        <v>251.0772625380853</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1047696172767817</v>
+        <v>0.1055417478968768</v>
       </c>
       <c r="T35">
-        <v>0.9943124643129883</v>
+        <v>1.007331695827324</v>
       </c>
       <c r="U35">
         <v>0.06717323332506819</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.982981561326671</v>
+        <v>4.83642328011118</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08815706206966244</v>
+        <v>0.08816307529609037</v>
       </c>
       <c r="C36">
-        <v>1312.081253400682</v>
+        <v>1292.393923593607</v>
       </c>
       <c r="D36">
-        <v>1900.469253400682</v>
+        <v>1900.363923593607</v>
       </c>
       <c r="E36">
-        <v>48.28800000000001</v>
+        <v>67.87000000000012</v>
       </c>
       <c r="F36">
-        <v>665.788</v>
+        <v>685.3700000000001</v>
       </c>
       <c r="G36">
         <v>77.40000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>216.3</v>
       </c>
       <c r="M36">
-        <v>44.72313266903051</v>
+        <v>46.038518924002</v>
       </c>
       <c r="N36">
-        <v>171.5768673309695</v>
+        <v>170.261481075998</v>
       </c>
       <c r="O36">
-        <v>32.5996047928842</v>
+        <v>32.34968140443961</v>
       </c>
       <c r="P36">
-        <v>138.9772625380853</v>
+        <v>137.9117996715584</v>
       </c>
       <c r="Q36">
-        <v>251.0772625380853</v>
+        <v>250.0117996715584</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1055417478968768</v>
+        <v>0.1063376363822054</v>
       </c>
       <c r="T36">
-        <v>1.007331695827324</v>
+        <v>1.020751519080562</v>
       </c>
       <c r="U36">
         <v>0.06717323332506819</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.83642328011118</v>
+        <v>4.698239757822288</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08816307529609037</v>
+        <v>0.08816908852251831</v>
       </c>
       <c r="C37">
-        <v>1292.393923593607</v>
+        <v>1272.706605461282</v>
       </c>
       <c r="D37">
-        <v>1900.363923593607</v>
+        <v>1900.258605461283</v>
       </c>
       <c r="E37">
-        <v>67.87000000000012</v>
+        <v>87.45200000000011</v>
       </c>
       <c r="F37">
-        <v>685.3700000000001</v>
+        <v>704.9520000000001</v>
       </c>
       <c r="G37">
         <v>77.40000000000001</v>
@@ -4321,28 +4321,28 @@
         <v>216.3</v>
       </c>
       <c r="M37">
-        <v>46.038518924002</v>
+        <v>47.35390517897348</v>
       </c>
       <c r="N37">
-        <v>170.261481075998</v>
+        <v>168.9460948210265</v>
       </c>
       <c r="O37">
-        <v>32.34968140443961</v>
+        <v>32.09975801599504</v>
       </c>
       <c r="P37">
-        <v>137.9117996715584</v>
+        <v>136.8463368050315</v>
       </c>
       <c r="Q37">
-        <v>250.0117996715584</v>
+        <v>248.9463368050315</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1063376363822054</v>
+        <v>0.1071583963827007</v>
       </c>
       <c r="T37">
-        <v>1.020751519080562</v>
+        <v>1.034590711810464</v>
       </c>
       <c r="U37">
         <v>0.06717323332506819</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.698239757822288</v>
+        <v>4.56773309788278</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08816908852251831</v>
+        <v>0.08892435174894624</v>
       </c>
       <c r="C38">
-        <v>1272.706605461283</v>
+        <v>1239.988781754145</v>
       </c>
       <c r="D38">
-        <v>1900.258605461283</v>
+        <v>1887.122781754145</v>
       </c>
       <c r="E38">
-        <v>87.452</v>
+        <v>107.034</v>
       </c>
       <c r="F38">
-        <v>704.952</v>
+        <v>724.534</v>
       </c>
       <c r="G38">
         <v>77.40000000000001</v>
@@ -4403,45 +4403,45 @@
         <v>216.3</v>
       </c>
       <c r="M38">
-        <v>47.35390517897347</v>
+        <v>50.48062643394495</v>
       </c>
       <c r="N38">
-        <v>168.9460948210265</v>
+        <v>165.819373566055</v>
       </c>
       <c r="O38">
-        <v>32.09975801599504</v>
+        <v>31.50568097755046</v>
       </c>
       <c r="P38">
-        <v>136.8463368050315</v>
+        <v>134.3136925885046</v>
       </c>
       <c r="Q38">
-        <v>248.9463368050315</v>
+        <v>246.4136925885046</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1071583963827007</v>
+        <v>0.1080052122562275</v>
       </c>
       <c r="T38">
-        <v>1.034590711810464</v>
+        <v>1.048869243992108</v>
       </c>
       <c r="U38">
-        <v>0.06717323332506819</v>
+        <v>0.06967323332506818</v>
       </c>
       <c r="V38">
         <v>0.19</v>
       </c>
       <c r="W38">
-        <v>0.05441031899330524</v>
+        <v>0.05643531899330523</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.567733097882781</v>
+        <v>4.284812120606972</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08892435174894624</v>
+        <v>0.08895061497537418</v>
       </c>
       <c r="C39">
-        <v>1239.988781754145</v>
+        <v>1219.953268361074</v>
       </c>
       <c r="D39">
-        <v>1887.122781754145</v>
+        <v>1886.669268361074</v>
       </c>
       <c r="E39">
-        <v>107.034</v>
+        <v>126.616</v>
       </c>
       <c r="F39">
-        <v>724.534</v>
+        <v>744.116</v>
       </c>
       <c r="G39">
         <v>77.40000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>216.3</v>
       </c>
       <c r="M39">
-        <v>50.48062643394495</v>
+        <v>51.84496768891643</v>
       </c>
       <c r="N39">
-        <v>165.819373566055</v>
+        <v>164.4550323110836</v>
       </c>
       <c r="O39">
-        <v>31.50568097755046</v>
+        <v>31.24645613910588</v>
       </c>
       <c r="P39">
-        <v>134.3136925885046</v>
+        <v>133.2085761719777</v>
       </c>
       <c r="Q39">
-        <v>246.4136925885046</v>
+        <v>245.3085761719777</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1080052122562275</v>
+        <v>0.1088793447708358</v>
       </c>
       <c r="T39">
-        <v>1.048869243992108</v>
+        <v>1.063608373986064</v>
       </c>
       <c r="U39">
         <v>0.06967323332506818</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.284812120606972</v>
+        <v>4.172053906906788</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08895061497537418</v>
+        <v>0.08897687820180211</v>
       </c>
       <c r="C40">
-        <v>1219.953268361074</v>
+        <v>1199.91797289233</v>
       </c>
       <c r="D40">
-        <v>1886.669268361074</v>
+        <v>1886.21597289233</v>
       </c>
       <c r="E40">
-        <v>126.616</v>
+        <v>146.1980000000001</v>
       </c>
       <c r="F40">
-        <v>744.116</v>
+        <v>763.6980000000001</v>
       </c>
       <c r="G40">
         <v>77.40000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>216.3</v>
       </c>
       <c r="M40">
-        <v>51.84496768891643</v>
+        <v>53.20930894388793</v>
       </c>
       <c r="N40">
-        <v>164.4550323110836</v>
+        <v>163.0906910561121</v>
       </c>
       <c r="O40">
-        <v>31.24645613910588</v>
+        <v>30.98723130066129</v>
       </c>
       <c r="P40">
-        <v>133.2085761719777</v>
+        <v>132.1034597554508</v>
       </c>
       <c r="Q40">
-        <v>245.3085761719777</v>
+        <v>244.2034597554508</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1088793447708358</v>
+        <v>0.1097821373678903</v>
       </c>
       <c r="T40">
-        <v>1.063608373986064</v>
+        <v>1.078830754143757</v>
       </c>
       <c r="U40">
         <v>0.06967323332506818</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.172053906906788</v>
+        <v>4.065078165704049</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08897687820180211</v>
+        <v>0.09013714142823007</v>
       </c>
       <c r="C41">
-        <v>1199.91797289233</v>
+        <v>1160.525264601042</v>
       </c>
       <c r="D41">
-        <v>1886.21597289233</v>
+        <v>1866.405264601042</v>
       </c>
       <c r="E41">
-        <v>146.1980000000001</v>
+        <v>165.7800000000001</v>
       </c>
       <c r="F41">
-        <v>763.6980000000001</v>
+        <v>783.2800000000001</v>
       </c>
       <c r="G41">
         <v>77.40000000000001</v>
@@ -4649,45 +4649,45 @@
         <v>216.3</v>
       </c>
       <c r="M41">
-        <v>53.20930894388793</v>
+        <v>57.31513019885941</v>
       </c>
       <c r="N41">
-        <v>163.0906910561121</v>
+        <v>158.9848698011406</v>
       </c>
       <c r="O41">
-        <v>30.98723130066129</v>
+        <v>30.20712526221671</v>
       </c>
       <c r="P41">
-        <v>132.1034597554508</v>
+        <v>128.7777445389239</v>
       </c>
       <c r="Q41">
-        <v>244.2034597554508</v>
+        <v>240.8777445389238</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1097821373678903</v>
+        <v>0.1107150230515133</v>
       </c>
       <c r="T41">
-        <v>1.078830754143757</v>
+        <v>1.094560546973372</v>
       </c>
       <c r="U41">
-        <v>0.06967323332506818</v>
+        <v>0.07317323332506818</v>
       </c>
       <c r="V41">
         <v>0.19</v>
       </c>
       <c r="W41">
-        <v>0.05643531899330523</v>
+        <v>0.05927031899330523</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.065078165704049</v>
+        <v>3.773872610068753</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09013714142823007</v>
+        <v>0.09019175465465799</v>
       </c>
       <c r="C42">
-        <v>1160.525264601042</v>
+        <v>1140.021030463104</v>
       </c>
       <c r="D42">
-        <v>1866.405264601042</v>
+        <v>1865.483030463104</v>
       </c>
       <c r="E42">
-        <v>165.7800000000001</v>
+        <v>185.3620000000001</v>
       </c>
       <c r="F42">
-        <v>783.2800000000001</v>
+        <v>802.8620000000001</v>
       </c>
       <c r="G42">
         <v>77.40000000000001</v>
@@ -4731,28 +4731,28 @@
         <v>216.3</v>
       </c>
       <c r="M42">
-        <v>57.31513019885941</v>
+        <v>58.7480084538309</v>
       </c>
       <c r="N42">
-        <v>158.9848698011406</v>
+        <v>157.5519915461691</v>
       </c>
       <c r="O42">
-        <v>30.20712526221671</v>
+        <v>29.93487839377213</v>
       </c>
       <c r="P42">
-        <v>128.7777445389239</v>
+        <v>127.617113152397</v>
       </c>
       <c r="Q42">
-        <v>240.8777445389238</v>
+        <v>239.717113152397</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1107150230515133</v>
+        <v>0.1116795319786489</v>
       </c>
       <c r="T42">
-        <v>1.094560546973372</v>
+        <v>1.110823553119245</v>
       </c>
       <c r="U42">
         <v>0.07317323332506818</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.773872610068753</v>
+        <v>3.681826936652442</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09019175465465799</v>
+        <v>0.09024636788108595</v>
       </c>
       <c r="C43">
-        <v>1140.021030463104</v>
+        <v>1119.51770726961</v>
       </c>
       <c r="D43">
-        <v>1865.483030463104</v>
+        <v>1864.56170726961</v>
       </c>
       <c r="E43">
-        <v>185.3620000000001</v>
+        <v>204.9440000000001</v>
       </c>
       <c r="F43">
-        <v>802.8620000000001</v>
+        <v>822.4440000000001</v>
       </c>
       <c r="G43">
         <v>77.40000000000001</v>
@@ -4813,28 +4813,28 @@
         <v>216.3</v>
       </c>
       <c r="M43">
-        <v>58.7480084538309</v>
+        <v>60.18088670880238</v>
       </c>
       <c r="N43">
-        <v>157.5519915461691</v>
+        <v>156.1191132911976</v>
       </c>
       <c r="O43">
-        <v>29.93487839377213</v>
+        <v>29.66263152532754</v>
       </c>
       <c r="P43">
-        <v>127.617113152397</v>
+        <v>126.4564817658701</v>
       </c>
       <c r="Q43">
-        <v>239.717113152397</v>
+        <v>238.55648176587</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1116795319786489</v>
+        <v>0.1126772998343065</v>
       </c>
       <c r="T43">
-        <v>1.110823553119245</v>
+        <v>1.127647352580493</v>
       </c>
       <c r="U43">
         <v>0.07317323332506818</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.681826936652442</v>
+        <v>3.59416439054167</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09024636788108595</v>
+        <v>0.09030098110751389</v>
       </c>
       <c r="C44">
-        <v>1119.51770726961</v>
+        <v>1099.015293671537</v>
       </c>
       <c r="D44">
-        <v>1864.56170726961</v>
+        <v>1863.641293671537</v>
       </c>
       <c r="E44">
-        <v>204.944</v>
+        <v>224.526</v>
       </c>
       <c r="F44">
-        <v>822.444</v>
+        <v>842.026</v>
       </c>
       <c r="G44">
         <v>77.40000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>216.3</v>
       </c>
       <c r="M44">
-        <v>60.18088670880238</v>
+        <v>61.61376496377386</v>
       </c>
       <c r="N44">
-        <v>156.1191132911976</v>
+        <v>154.6862350362261</v>
       </c>
       <c r="O44">
-        <v>29.66263152532754</v>
+        <v>29.39038465688296</v>
       </c>
       <c r="P44">
-        <v>126.4564817658701</v>
+        <v>125.2958503793432</v>
       </c>
       <c r="Q44">
-        <v>238.55648176587</v>
+        <v>237.3958503793432</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1126772998343064</v>
+        <v>0.1137100770884081</v>
       </c>
       <c r="T44">
-        <v>1.127647352580493</v>
+        <v>1.145061460794768</v>
       </c>
       <c r="U44">
         <v>0.07317323332506818</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.59416439054167</v>
+        <v>3.51057917215698</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09030098110751389</v>
+        <v>0.09135351433394183</v>
       </c>
       <c r="C45">
-        <v>1099.015293671537</v>
+        <v>1061.870467524373</v>
       </c>
       <c r="D45">
-        <v>1863.641293671537</v>
+        <v>1846.078467524374</v>
       </c>
       <c r="E45">
-        <v>224.526</v>
+        <v>244.1080000000001</v>
       </c>
       <c r="F45">
-        <v>842.026</v>
+        <v>861.6080000000001</v>
       </c>
       <c r="G45">
         <v>77.40000000000001</v>
@@ -4977,45 +4977,45 @@
         <v>216.3</v>
       </c>
       <c r="M45">
-        <v>61.61376496377386</v>
+        <v>65.45914561874535</v>
       </c>
       <c r="N45">
-        <v>154.6862350362261</v>
+        <v>150.8408543812546</v>
       </c>
       <c r="O45">
-        <v>29.39038465688296</v>
+        <v>28.65976233243838</v>
       </c>
       <c r="P45">
-        <v>125.2958503793432</v>
+        <v>122.1810920488163</v>
       </c>
       <c r="Q45">
-        <v>237.3958503793432</v>
+        <v>234.2810920488162</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1137100770884081</v>
+        <v>0.114779739244442</v>
       </c>
       <c r="T45">
-        <v>1.145061460794768</v>
+        <v>1.163097501445266</v>
       </c>
       <c r="U45">
-        <v>0.07317323332506818</v>
+        <v>0.07597323332506818</v>
       </c>
       <c r="V45">
         <v>0.19</v>
       </c>
       <c r="W45">
-        <v>0.05927031899330523</v>
+        <v>0.06153831899330523</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.51057917215698</v>
+        <v>3.304351102591519</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09135351433394183</v>
+        <v>0.09143080756036975</v>
       </c>
       <c r="C46">
-        <v>1061.870467524373</v>
+        <v>1041.011771792957</v>
       </c>
       <c r="D46">
-        <v>1846.078467524374</v>
+        <v>1844.801771792957</v>
       </c>
       <c r="E46">
-        <v>244.1080000000001</v>
+        <v>263.6900000000001</v>
       </c>
       <c r="F46">
-        <v>861.6080000000001</v>
+        <v>881.1900000000001</v>
       </c>
       <c r="G46">
         <v>77.40000000000001</v>
@@ -5059,28 +5059,28 @@
         <v>216.3</v>
       </c>
       <c r="M46">
-        <v>65.45914561874535</v>
+        <v>66.94685347371683</v>
       </c>
       <c r="N46">
-        <v>150.8408543812546</v>
+        <v>149.3531465262832</v>
       </c>
       <c r="O46">
-        <v>28.65976233243838</v>
+        <v>28.3770978399938</v>
       </c>
       <c r="P46">
-        <v>122.1810920488163</v>
+        <v>120.9760486862894</v>
       </c>
       <c r="Q46">
-        <v>234.2810920488162</v>
+        <v>233.0760486862894</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.114779739244442</v>
+        <v>0.1158882982061498</v>
       </c>
       <c r="T46">
-        <v>1.163097501445266</v>
+        <v>1.181789398119419</v>
       </c>
       <c r="U46">
         <v>0.07597323332506818</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.304351102591519</v>
+        <v>3.230921078089485</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09143080756036975</v>
+        <v>0.09150810078679769</v>
       </c>
       <c r="C47">
-        <v>1041.011771792957</v>
+        <v>1020.154840694594</v>
       </c>
       <c r="D47">
-        <v>1844.801771792957</v>
+        <v>1843.526840694594</v>
       </c>
       <c r="E47">
-        <v>263.6900000000001</v>
+        <v>283.272</v>
       </c>
       <c r="F47">
-        <v>881.1900000000001</v>
+        <v>900.772</v>
       </c>
       <c r="G47">
         <v>77.40000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>216.3</v>
       </c>
       <c r="M47">
-        <v>66.94685347371683</v>
+        <v>68.43456132868832</v>
       </c>
       <c r="N47">
-        <v>149.3531465262832</v>
+        <v>147.8654386713117</v>
       </c>
       <c r="O47">
-        <v>28.3770978399938</v>
+        <v>28.09443334754922</v>
       </c>
       <c r="P47">
-        <v>120.9760486862894</v>
+        <v>119.7710053237625</v>
       </c>
       <c r="Q47">
-        <v>233.0760486862894</v>
+        <v>231.8710053237625</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1158882982061498</v>
+        <v>0.1170379149071802</v>
       </c>
       <c r="T47">
-        <v>1.181789398119419</v>
+        <v>1.201173587262986</v>
       </c>
       <c r="U47">
         <v>0.07597323332506818</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.230921078089485</v>
+        <v>3.160683663348409</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09150810078679769</v>
+        <v>0.09158539401322563</v>
       </c>
       <c r="C48">
-        <v>1020.154840694594</v>
+        <v>999.2996705732287</v>
       </c>
       <c r="D48">
-        <v>1843.526840694594</v>
+        <v>1842.253670573229</v>
       </c>
       <c r="E48">
-        <v>283.272</v>
+        <v>302.854</v>
       </c>
       <c r="F48">
-        <v>900.772</v>
+        <v>920.354</v>
       </c>
       <c r="G48">
         <v>77.40000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>216.3</v>
       </c>
       <c r="M48">
-        <v>68.43456132868832</v>
+        <v>69.92226918365981</v>
       </c>
       <c r="N48">
-        <v>147.8654386713117</v>
+        <v>146.3777308163402</v>
       </c>
       <c r="O48">
-        <v>28.09443334754922</v>
+        <v>27.81176885510463</v>
       </c>
       <c r="P48">
-        <v>119.7710053237625</v>
+        <v>118.5659619612355</v>
       </c>
       <c r="Q48">
-        <v>231.8710053237625</v>
+        <v>230.6659619612356</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1170379149071802</v>
+        <v>0.1182309133705135</v>
       </c>
       <c r="T48">
-        <v>1.201173587262986</v>
+        <v>1.221289255242158</v>
       </c>
       <c r="U48">
         <v>0.07597323332506818</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.160683663348409</v>
+        <v>3.093435074766528</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09158539401322563</v>
+        <v>0.09166268723965358</v>
       </c>
       <c r="C49">
-        <v>999.2996705732287</v>
+        <v>978.4462577829001</v>
       </c>
       <c r="D49">
-        <v>1842.253670573229</v>
+        <v>1840.9822577829</v>
       </c>
       <c r="E49">
-        <v>302.854</v>
+        <v>322.4360000000001</v>
       </c>
       <c r="F49">
-        <v>920.354</v>
+        <v>939.9360000000001</v>
       </c>
       <c r="G49">
         <v>77.40000000000001</v>
@@ -5305,28 +5305,28 @@
         <v>216.3</v>
       </c>
       <c r="M49">
-        <v>69.92226918365981</v>
+        <v>71.4099770386313</v>
       </c>
       <c r="N49">
-        <v>146.3777308163402</v>
+        <v>144.8900229613687</v>
       </c>
       <c r="O49">
-        <v>27.81176885510463</v>
+        <v>27.52910436266005</v>
       </c>
       <c r="P49">
-        <v>118.5659619612355</v>
+        <v>117.3609185987086</v>
       </c>
       <c r="Q49">
-        <v>230.6659619612356</v>
+        <v>229.4609185987086</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1182309133705135</v>
+        <v>0.119469796390129</v>
       </c>
       <c r="T49">
-        <v>1.221289255242158</v>
+        <v>1.242178602758991</v>
       </c>
       <c r="U49">
         <v>0.07597323332506818</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.093435074766528</v>
+        <v>3.028988510708892</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09166268723965358</v>
+        <v>0.09483580046608152</v>
       </c>
       <c r="C50">
-        <v>978.4462577829003</v>
+        <v>908.1421351536778</v>
       </c>
       <c r="D50">
-        <v>1840.9822577829</v>
+        <v>1790.260135153678</v>
       </c>
       <c r="E50">
-        <v>322.436</v>
+        <v>342.018</v>
       </c>
       <c r="F50">
-        <v>939.936</v>
+        <v>959.518</v>
       </c>
       <c r="G50">
         <v>77.40000000000001</v>
@@ -5387,45 +5387,45 @@
         <v>216.3</v>
       </c>
       <c r="M50">
-        <v>71.40997703863128</v>
+        <v>80.38192529360279</v>
       </c>
       <c r="N50">
-        <v>144.8900229613687</v>
+        <v>135.9180747063972</v>
       </c>
       <c r="O50">
-        <v>27.52910436266005</v>
+        <v>25.82443419421547</v>
       </c>
       <c r="P50">
-        <v>117.3609185987086</v>
+        <v>110.0936405121817</v>
       </c>
       <c r="Q50">
-        <v>229.4609185987086</v>
+        <v>222.1936405121817</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.119469796390129</v>
+        <v>0.1207572630575725</v>
       </c>
       <c r="T50">
-        <v>1.242178602758991</v>
+        <v>1.263887140374524</v>
       </c>
       <c r="U50">
-        <v>0.07597323332506818</v>
+        <v>0.0837732333250682</v>
       </c>
       <c r="V50">
         <v>0.19</v>
       </c>
       <c r="W50">
-        <v>0.06153831899330523</v>
+        <v>0.06785631899330524</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.028988510708893</v>
+        <v>2.690903448877882</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09483580046608152</v>
+        <v>0.09497627369250945</v>
       </c>
       <c r="C51">
-        <v>908.1421351536778</v>
+        <v>886.3792009866889</v>
       </c>
       <c r="D51">
-        <v>1790.260135153678</v>
+        <v>1788.079200986689</v>
       </c>
       <c r="E51">
-        <v>342.018</v>
+        <v>361.6</v>
       </c>
       <c r="F51">
-        <v>959.518</v>
+        <v>979.1</v>
       </c>
       <c r="G51">
         <v>77.40000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>216.3</v>
       </c>
       <c r="M51">
-        <v>80.38192529360279</v>
+        <v>82.02237274857427</v>
       </c>
       <c r="N51">
-        <v>135.9180747063972</v>
+        <v>134.2776272514257</v>
       </c>
       <c r="O51">
-        <v>25.82443419421547</v>
+        <v>25.51274917777089</v>
       </c>
       <c r="P51">
-        <v>110.0936405121817</v>
+        <v>108.7648780736548</v>
       </c>
       <c r="Q51">
-        <v>222.1936405121817</v>
+        <v>220.8648780736548</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1207572630575725</v>
+        <v>0.1220962283917137</v>
       </c>
       <c r="T51">
-        <v>1.263887140374524</v>
+        <v>1.286464019494677</v>
       </c>
       <c r="U51">
         <v>0.0837732333250682</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.690903448877882</v>
+        <v>2.637085379900324</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09497627369250945</v>
+        <v>0.0951167469189374</v>
       </c>
       <c r="C52">
-        <v>886.3792009866889</v>
+        <v>864.621574077966</v>
       </c>
       <c r="D52">
-        <v>1788.079200986689</v>
+        <v>1785.903574077966</v>
       </c>
       <c r="E52">
-        <v>361.6</v>
+        <v>381.182</v>
       </c>
       <c r="F52">
-        <v>979.1</v>
+        <v>998.682</v>
       </c>
       <c r="G52">
         <v>77.40000000000001</v>
@@ -5551,28 +5551,28 @@
         <v>216.3</v>
       </c>
       <c r="M52">
-        <v>82.02237274857427</v>
+        <v>83.66282020354576</v>
       </c>
       <c r="N52">
-        <v>134.2776272514257</v>
+        <v>132.6371797964542</v>
       </c>
       <c r="O52">
-        <v>25.51274917777089</v>
+        <v>25.2010641613263</v>
       </c>
       <c r="P52">
-        <v>108.7648780736548</v>
+        <v>107.4361156351279</v>
       </c>
       <c r="Q52">
-        <v>220.8648780736548</v>
+        <v>219.5361156351279</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1220962283917137</v>
+        <v>0.1234898453721464</v>
       </c>
       <c r="T52">
-        <v>1.286464019494677</v>
+        <v>1.309962403885041</v>
       </c>
       <c r="U52">
         <v>0.0837732333250682</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.637085379900324</v>
+        <v>2.58537782343169</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0951167469189374</v>
+        <v>0.09525722014536533</v>
       </c>
       <c r="C53">
-        <v>864.621574077966</v>
+        <v>842.8692350783969</v>
       </c>
       <c r="D53">
-        <v>1785.903574077966</v>
+        <v>1783.733235078397</v>
       </c>
       <c r="E53">
-        <v>381.182</v>
+        <v>400.764</v>
       </c>
       <c r="F53">
-        <v>998.682</v>
+        <v>1018.264</v>
       </c>
       <c r="G53">
         <v>77.40000000000001</v>
@@ -5633,28 +5633,28 @@
         <v>216.3</v>
       </c>
       <c r="M53">
-        <v>83.66282020354576</v>
+        <v>85.30326765851724</v>
       </c>
       <c r="N53">
-        <v>132.6371797964542</v>
+        <v>130.9967323414828</v>
       </c>
       <c r="O53">
-        <v>25.2010641613263</v>
+        <v>24.88937914488172</v>
       </c>
       <c r="P53">
-        <v>107.4361156351279</v>
+        <v>106.107353196601</v>
       </c>
       <c r="Q53">
-        <v>219.5361156351279</v>
+        <v>218.207353196601</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1234898453721464</v>
+        <v>0.1249415297267638</v>
       </c>
       <c r="T53">
-        <v>1.309962403885041</v>
+        <v>1.334439887625003</v>
       </c>
       <c r="U53">
         <v>0.0837732333250682</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.58537782343169</v>
+        <v>2.535659019134927</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09525722014536533</v>
+        <v>0.09707196337179327</v>
       </c>
       <c r="C54">
-        <v>842.8692350783969</v>
+        <v>795.7160281864219</v>
       </c>
       <c r="D54">
-        <v>1783.733235078397</v>
+        <v>1756.162028186422</v>
       </c>
       <c r="E54">
-        <v>400.764</v>
+        <v>420.346</v>
       </c>
       <c r="F54">
-        <v>1018.264</v>
+        <v>1037.846</v>
       </c>
       <c r="G54">
         <v>77.40000000000001</v>
@@ -5715,45 +5715,45 @@
         <v>216.3</v>
       </c>
       <c r="M54">
-        <v>85.30326765851724</v>
+        <v>90.99131451348872</v>
       </c>
       <c r="N54">
-        <v>130.9967323414828</v>
+        <v>125.3086854865113</v>
       </c>
       <c r="O54">
-        <v>24.88937914488172</v>
+        <v>23.80865024243714</v>
       </c>
       <c r="P54">
-        <v>106.107353196601</v>
+        <v>101.5000352440741</v>
       </c>
       <c r="Q54">
-        <v>218.207353196601</v>
+        <v>213.6000352440741</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1249415297267638</v>
+        <v>0.1264549878837053</v>
       </c>
       <c r="T54">
-        <v>1.334439887625003</v>
+        <v>1.35995896641773</v>
       </c>
       <c r="U54">
-        <v>0.0837732333250682</v>
+        <v>0.08767323332506818</v>
       </c>
       <c r="V54">
         <v>0.19</v>
       </c>
       <c r="W54">
-        <v>0.06785631899330524</v>
+        <v>0.07101531899330524</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.535659019134927</v>
+        <v>2.377149963779623</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09707196337179327</v>
+        <v>0.09724402659822121</v>
       </c>
       <c r="C55">
-        <v>795.7160281864219</v>
+        <v>773.5640625158671</v>
       </c>
       <c r="D55">
-        <v>1756.162028186422</v>
+        <v>1753.592062515867</v>
       </c>
       <c r="E55">
-        <v>420.346</v>
+        <v>439.9280000000001</v>
       </c>
       <c r="F55">
-        <v>1037.846</v>
+        <v>1057.428</v>
       </c>
       <c r="G55">
         <v>77.40000000000001</v>
@@ -5797,28 +5797,28 @@
         <v>216.3</v>
       </c>
       <c r="M55">
-        <v>90.99131451348872</v>
+        <v>92.70813176846021</v>
       </c>
       <c r="N55">
-        <v>125.3086854865113</v>
+        <v>123.5918682315398</v>
       </c>
       <c r="O55">
-        <v>23.80865024243714</v>
+        <v>23.48245496399256</v>
       </c>
       <c r="P55">
-        <v>101.5000352440741</v>
+        <v>100.1094132675472</v>
       </c>
       <c r="Q55">
-        <v>213.6000352440741</v>
+        <v>212.2094132675472</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1264549878837053</v>
+        <v>0.1280342485692095</v>
       </c>
       <c r="T55">
-        <v>1.35995896641773</v>
+        <v>1.386587570375358</v>
       </c>
       <c r="U55">
         <v>0.08767323332506818</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.377149963779623</v>
+        <v>2.333128668154075</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09724402659822121</v>
+        <v>0.09741608982464917</v>
       </c>
       <c r="C56">
-        <v>773.5640625158671</v>
+        <v>751.419607624181</v>
       </c>
       <c r="D56">
-        <v>1753.592062515867</v>
+        <v>1751.029607624181</v>
       </c>
       <c r="E56">
-        <v>439.9280000000001</v>
+        <v>459.5100000000002</v>
       </c>
       <c r="F56">
-        <v>1057.428</v>
+        <v>1077.01</v>
       </c>
       <c r="G56">
         <v>77.40000000000001</v>
@@ -5879,28 +5879,28 @@
         <v>216.3</v>
       </c>
       <c r="M56">
-        <v>92.70813176846021</v>
+        <v>94.42494902343171</v>
       </c>
       <c r="N56">
-        <v>123.5918682315398</v>
+        <v>121.8750509765683</v>
       </c>
       <c r="O56">
-        <v>23.48245496399256</v>
+        <v>23.15625968554797</v>
       </c>
       <c r="P56">
-        <v>100.1094132675472</v>
+        <v>98.7187912910203</v>
       </c>
       <c r="Q56">
-        <v>212.2094132675472</v>
+        <v>210.8187912910203</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1280342485692095</v>
+        <v>0.1296836986185139</v>
       </c>
       <c r="T56">
-        <v>1.386587570375358</v>
+        <v>1.414399667842214</v>
       </c>
       <c r="U56">
         <v>0.08767323332506818</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.333128668154075</v>
+        <v>2.290708146914909</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09741608982464917</v>
+        <v>0.09758815305107708</v>
       </c>
       <c r="C57">
-        <v>751.419607624181</v>
+        <v>729.2826306337929</v>
       </c>
       <c r="D57">
-        <v>1751.029607624181</v>
+        <v>1748.474630633793</v>
       </c>
       <c r="E57">
-        <v>459.5100000000002</v>
+        <v>479.0920000000001</v>
       </c>
       <c r="F57">
-        <v>1077.01</v>
+        <v>1096.592</v>
       </c>
       <c r="G57">
         <v>77.40000000000001</v>
@@ -5961,28 +5961,28 @@
         <v>216.3</v>
       </c>
       <c r="M57">
-        <v>94.42494902343171</v>
+        <v>96.14176627840318</v>
       </c>
       <c r="N57">
-        <v>121.8750509765683</v>
+        <v>120.1582337215968</v>
       </c>
       <c r="O57">
-        <v>23.15625968554797</v>
+        <v>22.83006440710339</v>
       </c>
       <c r="P57">
-        <v>98.7187912910203</v>
+        <v>97.32816931449341</v>
       </c>
       <c r="Q57">
-        <v>210.8187912910203</v>
+        <v>209.4281693144934</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1296836986185139</v>
+        <v>0.1314081236700594</v>
       </c>
       <c r="T57">
-        <v>1.414399667842214</v>
+        <v>1.443475951557563</v>
       </c>
       <c r="U57">
         <v>0.08767323332506818</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.290708146914909</v>
+        <v>2.249802644291429</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09758815305107708</v>
+        <v>0.09776021627750503</v>
       </c>
       <c r="C58">
-        <v>729.2826306337929</v>
+        <v>707.1530988587408</v>
       </c>
       <c r="D58">
-        <v>1748.474630633793</v>
+        <v>1745.927098858741</v>
       </c>
       <c r="E58">
-        <v>479.0920000000001</v>
+        <v>498.6740000000002</v>
       </c>
       <c r="F58">
-        <v>1096.592</v>
+        <v>1116.174</v>
       </c>
       <c r="G58">
         <v>77.40000000000001</v>
@@ -6043,28 +6043,28 @@
         <v>216.3</v>
       </c>
       <c r="M58">
-        <v>96.14176627840318</v>
+        <v>97.85858353337467</v>
       </c>
       <c r="N58">
-        <v>120.1582337215968</v>
+        <v>118.4414164666253</v>
       </c>
       <c r="O58">
-        <v>22.83006440710339</v>
+        <v>22.50386912865881</v>
       </c>
       <c r="P58">
-        <v>97.32816931449341</v>
+        <v>95.93754733796651</v>
       </c>
       <c r="Q58">
-        <v>209.4281693144934</v>
+        <v>208.0375473379665</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1314081236700594</v>
+        <v>0.1332127545379559</v>
       </c>
       <c r="T58">
-        <v>1.443475951557563</v>
+        <v>1.473904620561999</v>
       </c>
       <c r="U58">
         <v>0.08767323332506818</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.249802644291429</v>
+        <v>2.210332422461755</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09776021627750503</v>
+        <v>0.09793227950393296</v>
       </c>
       <c r="C59">
-        <v>707.1530988587408</v>
+        <v>685.0309798032811</v>
       </c>
       <c r="D59">
-        <v>1745.927098858741</v>
+        <v>1743.386979803281</v>
       </c>
       <c r="E59">
-        <v>498.6740000000002</v>
+        <v>518.2560000000001</v>
       </c>
       <c r="F59">
-        <v>1116.174</v>
+        <v>1135.756</v>
       </c>
       <c r="G59">
         <v>77.40000000000001</v>
@@ -6125,28 +6125,28 @@
         <v>216.3</v>
       </c>
       <c r="M59">
-        <v>97.85858353337467</v>
+        <v>99.57540078834614</v>
       </c>
       <c r="N59">
-        <v>118.4414164666253</v>
+        <v>116.7245992116538</v>
       </c>
       <c r="O59">
-        <v>22.50386912865881</v>
+        <v>22.17767385021423</v>
       </c>
       <c r="P59">
-        <v>95.93754733796651</v>
+        <v>94.54692536143961</v>
       </c>
       <c r="Q59">
-        <v>208.0375473379665</v>
+        <v>206.6469253614396</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1332127545379559</v>
+        <v>0.1351033202090856</v>
       </c>
       <c r="T59">
-        <v>1.473904620561999</v>
+        <v>1.505782273804741</v>
       </c>
       <c r="U59">
         <v>0.08767323332506818</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.210332422461755</v>
+        <v>2.172223242764138</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09793227950393296</v>
+        <v>0.09810434273036089</v>
       </c>
       <c r="C60">
-        <v>685.0309798032813</v>
+        <v>662.9162411605048</v>
       </c>
       <c r="D60">
-        <v>1743.386979803281</v>
+        <v>1740.854241160505</v>
       </c>
       <c r="E60">
-        <v>518.2559999999999</v>
+        <v>537.838</v>
       </c>
       <c r="F60">
-        <v>1135.756</v>
+        <v>1155.338</v>
       </c>
       <c r="G60">
         <v>77.40000000000001</v>
@@ -6207,28 +6207,28 @@
         <v>216.3</v>
       </c>
       <c r="M60">
-        <v>99.57540078834613</v>
+        <v>101.2922180433176</v>
       </c>
       <c r="N60">
-        <v>116.7245992116539</v>
+        <v>115.0077819566824</v>
       </c>
       <c r="O60">
-        <v>22.17767385021423</v>
+        <v>21.85147857176965</v>
       </c>
       <c r="P60">
-        <v>94.54692536143962</v>
+        <v>93.15630338491272</v>
       </c>
       <c r="Q60">
-        <v>206.6469253614396</v>
+        <v>205.2563033849127</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1351033202090855</v>
+        <v>0.13708610859588</v>
       </c>
       <c r="T60">
-        <v>1.50578227380474</v>
+        <v>1.539214934522738</v>
       </c>
       <c r="U60">
         <v>0.08767323332506818</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.172223242764138</v>
+        <v>2.135405899666441</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09810434273036089</v>
+        <v>0.09827640595678883</v>
       </c>
       <c r="C61">
-        <v>662.9162411605048</v>
+        <v>640.8088508109688</v>
       </c>
       <c r="D61">
-        <v>1740.854241160505</v>
+        <v>1738.328850810969</v>
       </c>
       <c r="E61">
-        <v>537.838</v>
+        <v>557.4200000000001</v>
       </c>
       <c r="F61">
-        <v>1155.338</v>
+        <v>1174.92</v>
       </c>
       <c r="G61">
         <v>77.40000000000001</v>
@@ -6289,28 +6289,28 @@
         <v>216.3</v>
       </c>
       <c r="M61">
-        <v>101.2922180433176</v>
+        <v>103.0090352982891</v>
       </c>
       <c r="N61">
-        <v>115.0077819566824</v>
+        <v>113.2909647017109</v>
       </c>
       <c r="O61">
-        <v>21.85147857176965</v>
+        <v>21.52528329332506</v>
       </c>
       <c r="P61">
-        <v>93.15630338491272</v>
+        <v>91.7656814083858</v>
       </c>
       <c r="Q61">
-        <v>205.2563033849127</v>
+        <v>203.8656814083858</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.13708610859588</v>
+        <v>0.1391680364020142</v>
       </c>
       <c r="T61">
-        <v>1.539214934522738</v>
+        <v>1.574319228276635</v>
       </c>
       <c r="U61">
         <v>0.08767323332506818</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.135405899666441</v>
+        <v>2.099815801338667</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09827640595678883</v>
+        <v>0.09844846918321679</v>
       </c>
       <c r="C62">
-        <v>640.8088508109688</v>
+        <v>618.7087768213373</v>
       </c>
       <c r="D62">
-        <v>1738.328850810969</v>
+        <v>1735.810776821337</v>
       </c>
       <c r="E62">
-        <v>557.4200000000001</v>
+        <v>577.002</v>
       </c>
       <c r="F62">
-        <v>1174.92</v>
+        <v>1194.502</v>
       </c>
       <c r="G62">
         <v>77.40000000000001</v>
@@ -6371,28 +6371,28 @@
         <v>216.3</v>
       </c>
       <c r="M62">
-        <v>103.0090352982891</v>
+        <v>104.7258525532606</v>
       </c>
       <c r="N62">
-        <v>113.2909647017109</v>
+        <v>111.5741474467394</v>
       </c>
       <c r="O62">
-        <v>21.52528329332506</v>
+        <v>21.19908801488048</v>
       </c>
       <c r="P62">
-        <v>91.7656814083858</v>
+        <v>90.3750594318589</v>
       </c>
       <c r="Q62">
-        <v>203.8656814083858</v>
+        <v>202.4750594318589</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1391680364020142</v>
+        <v>0.1413567297366682</v>
       </c>
       <c r="T62">
-        <v>1.574319228276635</v>
+        <v>1.61122374222304</v>
       </c>
       <c r="U62">
         <v>0.08767323332506818</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.099815801338667</v>
+        <v>2.065392591480656</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09844846918321679</v>
+        <v>0.09862053240964472</v>
       </c>
       <c r="C63">
-        <v>618.7087768213373</v>
+        <v>596.6159874430377</v>
       </c>
       <c r="D63">
-        <v>1735.810776821337</v>
+        <v>1733.299987443038</v>
       </c>
       <c r="E63">
-        <v>577.002</v>
+        <v>596.5840000000001</v>
       </c>
       <c r="F63">
-        <v>1194.502</v>
+        <v>1214.084</v>
       </c>
       <c r="G63">
         <v>77.40000000000001</v>
@@ -6453,28 +6453,28 @@
         <v>216.3</v>
       </c>
       <c r="M63">
-        <v>104.7258525532606</v>
+        <v>106.4426698082321</v>
       </c>
       <c r="N63">
-        <v>111.5741474467394</v>
+        <v>109.8573301917679</v>
       </c>
       <c r="O63">
-        <v>21.19908801488048</v>
+        <v>20.8728927364359</v>
       </c>
       <c r="P63">
-        <v>90.3750594318589</v>
+        <v>88.984437455332</v>
       </c>
       <c r="Q63">
-        <v>202.4750594318589</v>
+        <v>201.084437455332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1413567297366682</v>
+        <v>0.1436606174573565</v>
       </c>
       <c r="T63">
-        <v>1.61122374222304</v>
+        <v>1.650070599008729</v>
       </c>
       <c r="U63">
         <v>0.08767323332506818</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.065392591480656</v>
+        <v>2.032079807747097</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09862053240964472</v>
+        <v>0.1060388556360727</v>
       </c>
       <c r="C64">
-        <v>596.6159874430377</v>
+        <v>475.2858490377828</v>
       </c>
       <c r="D64">
-        <v>1733.299987443038</v>
+        <v>1631.551849037783</v>
       </c>
       <c r="E64">
-        <v>596.5840000000001</v>
+        <v>616.1659999999999</v>
       </c>
       <c r="F64">
-        <v>1214.084</v>
+        <v>1233.666</v>
       </c>
       <c r="G64">
         <v>77.40000000000001</v>
@@ -6535,45 +6535,45 @@
         <v>216.3</v>
       </c>
       <c r="M64">
-        <v>106.4426698082321</v>
+        <v>125.6775442632036</v>
       </c>
       <c r="N64">
-        <v>109.8573301917679</v>
+        <v>90.62245573679641</v>
       </c>
       <c r="O64">
-        <v>20.8728927364359</v>
+        <v>17.21826658999132</v>
       </c>
       <c r="P64">
-        <v>88.984437455332</v>
+        <v>73.40418914680509</v>
       </c>
       <c r="Q64">
-        <v>201.084437455332</v>
+        <v>185.5041891468051</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1436606174573565</v>
+        <v>0.1460890396494334</v>
       </c>
       <c r="T64">
-        <v>1.650070599008729</v>
+        <v>1.691017285890942</v>
       </c>
       <c r="U64">
-        <v>0.08767323332506818</v>
+        <v>0.1018732333250682</v>
       </c>
       <c r="V64">
         <v>0.19</v>
       </c>
       <c r="W64">
-        <v>0.07101531899330524</v>
+        <v>0.08251731899330524</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.032079807747097</v>
+        <v>1.721071184737728</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1060388556360727</v>
+        <v>0.1063259388625006</v>
       </c>
       <c r="C65">
-        <v>475.2858490377828</v>
+        <v>452.0058209307269</v>
       </c>
       <c r="D65">
-        <v>1631.551849037783</v>
+        <v>1627.853820930727</v>
       </c>
       <c r="E65">
-        <v>616.1659999999999</v>
+        <v>635.748</v>
       </c>
       <c r="F65">
-        <v>1233.666</v>
+        <v>1253.248</v>
       </c>
       <c r="G65">
         <v>77.40000000000001</v>
@@ -6617,28 +6617,28 @@
         <v>216.3</v>
       </c>
       <c r="M65">
-        <v>125.6775442632036</v>
+        <v>127.6724259181751</v>
       </c>
       <c r="N65">
-        <v>90.62245573679641</v>
+        <v>88.62757408182492</v>
       </c>
       <c r="O65">
-        <v>17.21826658999132</v>
+        <v>16.83923907554674</v>
       </c>
       <c r="P65">
-        <v>73.40418914680509</v>
+        <v>71.78833500627817</v>
       </c>
       <c r="Q65">
-        <v>185.5041891468051</v>
+        <v>183.8883350062782</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1460890396494334</v>
+        <v>0.1486523741855146</v>
       </c>
       <c r="T65">
-        <v>1.691017285890942</v>
+        <v>1.734238788711057</v>
       </c>
       <c r="U65">
         <v>0.1018732333250682</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.721071184737728</v>
+        <v>1.694179447476201</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1063259388625006</v>
+        <v>0.1066130220889285</v>
       </c>
       <c r="C66">
-        <v>452.0058209307269</v>
+        <v>428.7425186000455</v>
       </c>
       <c r="D66">
-        <v>1627.853820930727</v>
+        <v>1624.172518600046</v>
       </c>
       <c r="E66">
-        <v>635.748</v>
+        <v>655.3300000000002</v>
       </c>
       <c r="F66">
-        <v>1253.248</v>
+        <v>1272.83</v>
       </c>
       <c r="G66">
         <v>77.40000000000001</v>
@@ -6699,28 +6699,28 @@
         <v>216.3</v>
       </c>
       <c r="M66">
-        <v>127.6724259181751</v>
+        <v>129.6673075731466</v>
       </c>
       <c r="N66">
-        <v>88.62757408182492</v>
+        <v>86.63269242685342</v>
       </c>
       <c r="O66">
-        <v>16.83923907554674</v>
+        <v>16.46021156110215</v>
       </c>
       <c r="P66">
-        <v>71.78833500627817</v>
+        <v>70.17248086575127</v>
       </c>
       <c r="Q66">
-        <v>183.8883350062782</v>
+        <v>182.2724808657513</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1486523741855146</v>
+        <v>0.1513621849808004</v>
       </c>
       <c r="T66">
-        <v>1.734238788711057</v>
+        <v>1.77993009169232</v>
       </c>
       <c r="U66">
         <v>0.1018732333250682</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.694179447476201</v>
+        <v>1.668115148284259</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1066130220889285</v>
+        <v>0.1069001053153565</v>
       </c>
       <c r="C67">
-        <v>428.7425186000455</v>
+        <v>405.495828828489</v>
       </c>
       <c r="D67">
-        <v>1624.172518600046</v>
+        <v>1620.507828828489</v>
       </c>
       <c r="E67">
-        <v>655.3300000000002</v>
+        <v>674.912</v>
       </c>
       <c r="F67">
-        <v>1272.83</v>
+        <v>1292.412</v>
       </c>
       <c r="G67">
         <v>77.40000000000001</v>
@@ -6781,28 +6781,28 @@
         <v>216.3</v>
       </c>
       <c r="M67">
-        <v>129.6673075731466</v>
+        <v>131.662189228118</v>
       </c>
       <c r="N67">
-        <v>86.63269242685342</v>
+        <v>84.63781077188196</v>
       </c>
       <c r="O67">
-        <v>16.46021156110215</v>
+        <v>16.08118404665757</v>
       </c>
       <c r="P67">
-        <v>70.17248086575127</v>
+        <v>68.55662672522439</v>
       </c>
       <c r="Q67">
-        <v>182.2724808657513</v>
+        <v>180.6566267252244</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1513621849808004</v>
+        <v>0.154231396411103</v>
       </c>
       <c r="T67">
-        <v>1.77993009169232</v>
+        <v>1.828309118378363</v>
       </c>
       <c r="U67">
         <v>0.1018732333250682</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.668115148284259</v>
+        <v>1.642840676340558</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1069001053153565</v>
+        <v>0.1071871885417844</v>
       </c>
       <c r="C68">
-        <v>405.495828828489</v>
+        <v>382.2656394183357</v>
       </c>
       <c r="D68">
-        <v>1620.507828828489</v>
+        <v>1616.859639418336</v>
       </c>
       <c r="E68">
-        <v>674.912</v>
+        <v>694.4940000000001</v>
       </c>
       <c r="F68">
-        <v>1292.412</v>
+        <v>1311.994</v>
       </c>
       <c r="G68">
         <v>77.40000000000001</v>
@@ -6863,28 +6863,28 @@
         <v>216.3</v>
       </c>
       <c r="M68">
-        <v>131.662189228118</v>
+        <v>133.6570708830895</v>
       </c>
       <c r="N68">
-        <v>84.63781077188196</v>
+        <v>82.64292911691047</v>
       </c>
       <c r="O68">
-        <v>16.08118404665757</v>
+        <v>15.70215653221299</v>
       </c>
       <c r="P68">
-        <v>68.55662672522439</v>
+        <v>66.94077258469747</v>
       </c>
       <c r="Q68">
-        <v>180.6566267252244</v>
+        <v>179.0407725846975</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.154231396411103</v>
+        <v>0.1572744994432421</v>
       </c>
       <c r="T68">
-        <v>1.828309118378363</v>
+        <v>1.879620207287803</v>
       </c>
       <c r="U68">
         <v>0.1018732333250682</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.642840676340558</v>
+        <v>1.618320666245923</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1071871885417844</v>
+        <v>0.1074742717682124</v>
       </c>
       <c r="C69">
-        <v>382.2656394183357</v>
+        <v>359.0518391799405</v>
       </c>
       <c r="D69">
-        <v>1616.859639418336</v>
+        <v>1613.22783917994</v>
       </c>
       <c r="E69">
-        <v>694.4940000000001</v>
+        <v>714.076</v>
       </c>
       <c r="F69">
-        <v>1311.994</v>
+        <v>1331.576</v>
       </c>
       <c r="G69">
         <v>77.40000000000001</v>
@@ -6945,28 +6945,28 @@
         <v>216.3</v>
       </c>
       <c r="M69">
-        <v>133.6570708830895</v>
+        <v>135.651952538061</v>
       </c>
       <c r="N69">
-        <v>82.64292911691047</v>
+        <v>80.64804746193897</v>
       </c>
       <c r="O69">
-        <v>15.70215653221299</v>
+        <v>15.32312901776841</v>
       </c>
       <c r="P69">
-        <v>66.94077258469747</v>
+        <v>65.32491844417056</v>
       </c>
       <c r="Q69">
-        <v>179.0407725846975</v>
+        <v>177.4249184441705</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1572744994432421</v>
+        <v>0.16050779641489</v>
       </c>
       <c r="T69">
-        <v>1.879620207287803</v>
+        <v>1.934138239254083</v>
       </c>
       <c r="U69">
         <v>0.1018732333250682</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.618320666245923</v>
+        <v>1.594521832918777</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1074742717682124</v>
+        <v>0.1077613549946403</v>
       </c>
       <c r="C70">
-        <v>359.0518391799405</v>
+        <v>335.8543179204385</v>
       </c>
       <c r="D70">
-        <v>1613.22783917994</v>
+        <v>1609.612317920438</v>
       </c>
       <c r="E70">
-        <v>714.076</v>
+        <v>733.6580000000001</v>
       </c>
       <c r="F70">
-        <v>1331.576</v>
+        <v>1351.158</v>
       </c>
       <c r="G70">
         <v>77.40000000000001</v>
@@ -7027,28 +7027,28 @@
         <v>216.3</v>
       </c>
       <c r="M70">
-        <v>135.651952538061</v>
+        <v>137.6468341930325</v>
       </c>
       <c r="N70">
-        <v>80.64804746193897</v>
+        <v>78.65316580696748</v>
       </c>
       <c r="O70">
-        <v>15.32312901776841</v>
+        <v>14.94410150332382</v>
       </c>
       <c r="P70">
-        <v>65.32491844417056</v>
+        <v>63.70906430364366</v>
       </c>
       <c r="Q70">
-        <v>177.4249184441705</v>
+        <v>175.8090643036437</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.16050779641489</v>
+        <v>0.1639496931911603</v>
       </c>
       <c r="T70">
-        <v>1.934138239254083</v>
+        <v>1.992173563605284</v>
       </c>
       <c r="U70">
         <v>0.1018732333250682</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.594521832918777</v>
+        <v>1.57141282084749</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1077613549946403</v>
+        <v>0.1080484382210682</v>
       </c>
       <c r="C71">
-        <v>335.8543179204385</v>
+        <v>312.6729664326015</v>
       </c>
       <c r="D71">
-        <v>1609.612317920438</v>
+        <v>1606.012966432602</v>
       </c>
       <c r="E71">
-        <v>733.6580000000001</v>
+        <v>753.2400000000002</v>
       </c>
       <c r="F71">
-        <v>1351.158</v>
+        <v>1370.74</v>
       </c>
       <c r="G71">
         <v>77.40000000000001</v>
@@ -7109,28 +7109,28 @@
         <v>216.3</v>
       </c>
       <c r="M71">
-        <v>137.6468341930325</v>
+        <v>139.641715848004</v>
       </c>
       <c r="N71">
-        <v>78.65316580696748</v>
+        <v>76.65828415199599</v>
       </c>
       <c r="O71">
-        <v>14.94410150332382</v>
+        <v>14.56507398887924</v>
       </c>
       <c r="P71">
-        <v>63.70906430364366</v>
+        <v>62.09321016311675</v>
       </c>
       <c r="Q71">
-        <v>175.8090643036437</v>
+        <v>174.1932101631168</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1639496931911603</v>
+        <v>0.1676210497525152</v>
       </c>
       <c r="T71">
-        <v>1.992173563605284</v>
+        <v>2.054077909579899</v>
       </c>
       <c r="U71">
         <v>0.1018732333250682</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.57141282084749</v>
+        <v>1.548964066263955</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1080484382210682</v>
+        <v>0.1083355214474962</v>
       </c>
       <c r="C72">
-        <v>312.6729664326015</v>
+        <v>289.5076764838402</v>
       </c>
       <c r="D72">
-        <v>1606.012966432602</v>
+        <v>1602.42967648384</v>
       </c>
       <c r="E72">
-        <v>753.2400000000002</v>
+        <v>772.8220000000001</v>
       </c>
       <c r="F72">
-        <v>1370.74</v>
+        <v>1390.322</v>
       </c>
       <c r="G72">
         <v>77.40000000000001</v>
@@ -7191,28 +7191,28 @@
         <v>216.3</v>
       </c>
       <c r="M72">
-        <v>139.641715848004</v>
+        <v>141.6365975029755</v>
       </c>
       <c r="N72">
-        <v>76.65828415199599</v>
+        <v>74.66340249702452</v>
       </c>
       <c r="O72">
-        <v>14.56507398887924</v>
+        <v>14.18604647443466</v>
       </c>
       <c r="P72">
-        <v>62.09321016311675</v>
+        <v>60.47735602258986</v>
       </c>
       <c r="Q72">
-        <v>174.1932101631168</v>
+        <v>172.5773560225899</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1676210497525152</v>
+        <v>0.1715456033181016</v>
       </c>
       <c r="T72">
-        <v>2.054077909579899</v>
+        <v>2.120251520794143</v>
       </c>
       <c r="U72">
         <v>0.1018732333250682</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.548964066263955</v>
+        <v>1.527147670964462</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1083355214474962</v>
+        <v>0.1086226046739241</v>
       </c>
       <c r="C73">
-        <v>289.5076764838404</v>
+        <v>266.3583408053578</v>
       </c>
       <c r="D73">
-        <v>1602.42967648384</v>
+        <v>1598.862340805358</v>
       </c>
       <c r="E73">
-        <v>772.8219999999999</v>
+        <v>792.404</v>
       </c>
       <c r="F73">
-        <v>1390.322</v>
+        <v>1409.904</v>
       </c>
       <c r="G73">
         <v>77.40000000000001</v>
@@ -7273,28 +7273,28 @@
         <v>216.3</v>
       </c>
       <c r="M73">
-        <v>141.6365975029754</v>
+        <v>143.6314791579469</v>
       </c>
       <c r="N73">
-        <v>74.66340249702455</v>
+        <v>72.66852084205306</v>
       </c>
       <c r="O73">
-        <v>14.18604647443467</v>
+        <v>13.80701895999008</v>
       </c>
       <c r="P73">
-        <v>60.47735602258989</v>
+        <v>58.86150188206297</v>
       </c>
       <c r="Q73">
-        <v>172.5773560225899</v>
+        <v>170.961501882063</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1715456033181015</v>
+        <v>0.1757504821383726</v>
       </c>
       <c r="T73">
-        <v>2.120251520794142</v>
+        <v>2.191151818523688</v>
       </c>
       <c r="U73">
         <v>0.1018732333250682</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.527147670964463</v>
+        <v>1.505937286645512</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1086226046739241</v>
+        <v>0.1437875690469573</v>
       </c>
       <c r="C74">
-        <v>266.3583408053578</v>
+        <v>-95.79907972603633</v>
       </c>
       <c r="D74">
-        <v>1598.862340805358</v>
+        <v>1256.286920273964</v>
       </c>
       <c r="E74">
-        <v>792.404</v>
+        <v>811.9860000000001</v>
       </c>
       <c r="F74">
-        <v>1409.904</v>
+        <v>1429.486</v>
       </c>
       <c r="G74">
         <v>77.40000000000001</v>
@@ -7355,45 +7355,45 @@
         <v>216.3</v>
       </c>
       <c r="M74">
-        <v>143.6314791579469</v>
+        <v>226.8211656129184</v>
       </c>
       <c r="N74">
-        <v>72.66852084205306</v>
+        <v>-10.52116561291845</v>
       </c>
       <c r="O74">
-        <v>13.80701895999008</v>
+        <v>-1.999021466454506</v>
       </c>
       <c r="P74">
-        <v>58.86150188206297</v>
+        <v>-8.522144146463946</v>
       </c>
       <c r="Q74">
-        <v>170.961501882063</v>
+        <v>103.5778558535361</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1757504821383726</v>
+        <v>0.1812712583643203</v>
       </c>
       <c r="T74">
-        <v>2.191151818523688</v>
+        <v>2.284240036959591</v>
       </c>
       <c r="U74">
-        <v>0.1018732333250682</v>
+        <v>0.1586732333250682</v>
       </c>
       <c r="V74">
-        <v>0.19</v>
+        <v>0.1811867948431853</v>
       </c>
       <c r="W74">
-        <v>0.08251731899330524</v>
+        <v>0.1299237387514942</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.505937286645512</v>
+        <v>0.9536147097009749</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1437875690469573</v>
+        <v>0.1449163013802079</v>
       </c>
       <c r="C75">
-        <v>-95.79907972603633</v>
+        <v>-123.9620845155916</v>
       </c>
       <c r="D75">
-        <v>1256.286920273964</v>
+        <v>1247.705915484408</v>
       </c>
       <c r="E75">
-        <v>811.9860000000001</v>
+        <v>831.568</v>
       </c>
       <c r="F75">
-        <v>1429.486</v>
+        <v>1449.068</v>
       </c>
       <c r="G75">
         <v>77.40000000000001</v>
@@ -7437,37 +7437,37 @@
         <v>216.3</v>
       </c>
       <c r="M75">
-        <v>226.8211656129184</v>
+        <v>229.9283048678899</v>
       </c>
       <c r="N75">
-        <v>-10.52116561291845</v>
+        <v>-13.62830486788994</v>
       </c>
       <c r="O75">
-        <v>-1.999021466454506</v>
+        <v>-2.589377924899088</v>
       </c>
       <c r="P75">
-        <v>-8.522144146463946</v>
+        <v>-11.03892694299085</v>
       </c>
       <c r="Q75">
-        <v>103.5778558535361</v>
+        <v>101.0610730570091</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1812712583643203</v>
+        <v>0.1864816913783327</v>
       </c>
       <c r="T75">
-        <v>2.284240036959591</v>
+        <v>2.372095422996499</v>
       </c>
       <c r="U75">
         <v>0.1586732333250682</v>
       </c>
       <c r="V75">
-        <v>0.1811867948431853</v>
+        <v>0.1787383246426017</v>
       </c>
       <c r="W75">
-        <v>0.1299237387514942</v>
+        <v>0.1303122454349209</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9536147097009749</v>
+        <v>0.9407280244347456</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1449163013802079</v>
+        <v>0.1460450337134586</v>
       </c>
       <c r="C76">
-        <v>-123.9620845155916</v>
+        <v>-152.0086603219479</v>
       </c>
       <c r="D76">
-        <v>1247.705915484408</v>
+        <v>1239.241339678052</v>
       </c>
       <c r="E76">
-        <v>831.568</v>
+        <v>851.1500000000001</v>
       </c>
       <c r="F76">
-        <v>1449.068</v>
+        <v>1468.65</v>
       </c>
       <c r="G76">
         <v>77.40000000000001</v>
@@ -7519,37 +7519,37 @@
         <v>216.3</v>
       </c>
       <c r="M76">
-        <v>229.9283048678899</v>
+        <v>233.0354441228614</v>
       </c>
       <c r="N76">
-        <v>-13.62830486788994</v>
+        <v>-16.73544412286142</v>
       </c>
       <c r="O76">
-        <v>-2.589377924899088</v>
+        <v>-3.17973438334367</v>
       </c>
       <c r="P76">
-        <v>-11.03892694299085</v>
+        <v>-13.55570973951775</v>
       </c>
       <c r="Q76">
-        <v>101.0610730570091</v>
+        <v>98.54429026048224</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1864816913783327</v>
+        <v>0.192108959033466</v>
       </c>
       <c r="T76">
-        <v>2.372095422996499</v>
+        <v>2.466979239916359</v>
       </c>
       <c r="U76">
         <v>0.1586732333250682</v>
       </c>
       <c r="V76">
-        <v>0.1787383246426017</v>
+        <v>0.1763551469807003</v>
       </c>
       <c r="W76">
-        <v>0.1303122454349209</v>
+        <v>0.1306903919401228</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9407280244347456</v>
+        <v>0.928184984108949</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1460450337134586</v>
+        <v>0.1471737660467093</v>
       </c>
       <c r="C77">
-        <v>-152.0086603219479</v>
+        <v>-179.9411607793313</v>
       </c>
       <c r="D77">
-        <v>1239.241339678052</v>
+        <v>1230.890839220669</v>
       </c>
       <c r="E77">
-        <v>851.1500000000001</v>
+        <v>870.732</v>
       </c>
       <c r="F77">
-        <v>1468.65</v>
+        <v>1488.232</v>
       </c>
       <c r="G77">
         <v>77.40000000000001</v>
@@ -7601,37 +7601,37 @@
         <v>216.3</v>
       </c>
       <c r="M77">
-        <v>233.0354441228614</v>
+        <v>236.1425833778329</v>
       </c>
       <c r="N77">
-        <v>-16.73544412286142</v>
+        <v>-19.84258337783291</v>
       </c>
       <c r="O77">
-        <v>-3.17973438334367</v>
+        <v>-3.770090841788253</v>
       </c>
       <c r="P77">
-        <v>-13.55570973951775</v>
+        <v>-16.07249253604466</v>
       </c>
       <c r="Q77">
-        <v>98.54429026048224</v>
+        <v>96.02750746395535</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.192108959033466</v>
+        <v>0.1982051656598604</v>
       </c>
       <c r="T77">
-        <v>2.466979239916359</v>
+        <v>2.56977004157954</v>
       </c>
       <c r="U77">
         <v>0.1586732333250682</v>
       </c>
       <c r="V77">
-        <v>0.1763551469807003</v>
+        <v>0.1740346845204279</v>
       </c>
       <c r="W77">
-        <v>0.1306903919401228</v>
+        <v>0.1310585872215037</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.928184984108949</v>
+        <v>0.9159720237917259</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1471737660467093</v>
+        <v>0.14830249837996</v>
       </c>
       <c r="C78">
-        <v>-179.9411607793313</v>
+        <v>-207.7618765076945</v>
       </c>
       <c r="D78">
-        <v>1230.890839220669</v>
+        <v>1222.652123492305</v>
       </c>
       <c r="E78">
-        <v>870.732</v>
+        <v>890.3140000000001</v>
       </c>
       <c r="F78">
-        <v>1488.232</v>
+        <v>1507.814</v>
       </c>
       <c r="G78">
         <v>77.40000000000001</v>
@@ -7683,37 +7683,37 @@
         <v>216.3</v>
       </c>
       <c r="M78">
-        <v>236.1425833778329</v>
+        <v>239.2497226328044</v>
       </c>
       <c r="N78">
-        <v>-19.84258337783291</v>
+        <v>-22.9497226328044</v>
       </c>
       <c r="O78">
-        <v>-3.770090841788253</v>
+        <v>-4.360447300232835</v>
       </c>
       <c r="P78">
-        <v>-16.07249253604466</v>
+        <v>-18.58927533257156</v>
       </c>
       <c r="Q78">
-        <v>96.02750746395535</v>
+        <v>93.51072466742843</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1982051656598604</v>
+        <v>0.2048314772102891</v>
       </c>
       <c r="T78">
-        <v>2.56977004157954</v>
+        <v>2.681499173822129</v>
       </c>
       <c r="U78">
         <v>0.1586732333250682</v>
       </c>
       <c r="V78">
-        <v>0.1740346845204279</v>
+        <v>0.1717744938123704</v>
       </c>
       <c r="W78">
-        <v>0.1310585872215037</v>
+        <v>0.1314172189890825</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9159720237917259</v>
+        <v>0.9040762832230023</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.14830249837996</v>
+        <v>0.1494312307132107</v>
       </c>
       <c r="C79">
-        <v>-207.7618765076945</v>
+        <v>-235.4730372075599</v>
       </c>
       <c r="D79">
-        <v>1222.652123492305</v>
+        <v>1214.52296279244</v>
       </c>
       <c r="E79">
-        <v>890.3140000000001</v>
+        <v>909.8960000000002</v>
       </c>
       <c r="F79">
-        <v>1507.814</v>
+        <v>1527.396</v>
       </c>
       <c r="G79">
         <v>77.40000000000001</v>
@@ -7765,37 +7765,37 @@
         <v>216.3</v>
       </c>
       <c r="M79">
-        <v>239.2497226328044</v>
+        <v>242.3568618877759</v>
       </c>
       <c r="N79">
-        <v>-22.9497226328044</v>
+        <v>-26.05686188777591</v>
       </c>
       <c r="O79">
-        <v>-4.360447300232835</v>
+        <v>-4.950803758677423</v>
       </c>
       <c r="P79">
-        <v>-18.58927533257156</v>
+        <v>-21.10605812909849</v>
       </c>
       <c r="Q79">
-        <v>93.51072466742843</v>
+        <v>90.99394187090151</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2048314772102891</v>
+        <v>0.2120601807198478</v>
       </c>
       <c r="T79">
-        <v>2.681499173822129</v>
+        <v>2.803385499904953</v>
       </c>
       <c r="U79">
         <v>0.1586732333250682</v>
       </c>
       <c r="V79">
-        <v>0.1717744938123704</v>
+        <v>0.1695722567122118</v>
       </c>
       <c r="W79">
-        <v>0.1314172189890825</v>
+        <v>0.131766655070313</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9040762832230023</v>
+        <v>0.8924855616432201</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1494312307132107</v>
+        <v>0.1505599630464614</v>
       </c>
       <c r="C80">
-        <v>-235.4730372075599</v>
+        <v>-263.076813671845</v>
       </c>
       <c r="D80">
-        <v>1214.52296279244</v>
+        <v>1206.501186328155</v>
       </c>
       <c r="E80">
-        <v>909.8960000000002</v>
+        <v>929.4780000000001</v>
       </c>
       <c r="F80">
-        <v>1527.396</v>
+        <v>1546.978</v>
       </c>
       <c r="G80">
         <v>77.40000000000001</v>
@@ -7847,37 +7847,37 @@
         <v>216.3</v>
       </c>
       <c r="M80">
-        <v>242.3568618877759</v>
+        <v>245.4640011427473</v>
       </c>
       <c r="N80">
-        <v>-26.05686188777591</v>
+        <v>-29.16400114274737</v>
       </c>
       <c r="O80">
-        <v>-4.950803758677423</v>
+        <v>-5.541160217122</v>
       </c>
       <c r="P80">
-        <v>-21.10605812909849</v>
+        <v>-23.62284092562537</v>
       </c>
       <c r="Q80">
-        <v>90.99394187090151</v>
+        <v>88.47715907437463</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2120601807198478</v>
+        <v>0.2199773321826976</v>
       </c>
       <c r="T80">
-        <v>2.803385499904953</v>
+        <v>2.936880047519475</v>
       </c>
       <c r="U80">
         <v>0.1586732333250682</v>
       </c>
       <c r="V80">
-        <v>0.1695722567122118</v>
+        <v>0.167425772450032</v>
       </c>
       <c r="W80">
-        <v>0.131766655070313</v>
+        <v>0.1321072446684745</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8924855616432201</v>
+        <v>0.8811882760527997</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1505599630464614</v>
+        <v>0.151688695379712</v>
       </c>
       <c r="C81">
-        <v>-263.076813671845</v>
+        <v>-290.5753197184899</v>
       </c>
       <c r="D81">
-        <v>1206.501186328155</v>
+        <v>1198.58468028151</v>
       </c>
       <c r="E81">
-        <v>929.4780000000001</v>
+        <v>949.0600000000002</v>
       </c>
       <c r="F81">
-        <v>1546.978</v>
+        <v>1566.56</v>
       </c>
       <c r="G81">
         <v>77.40000000000001</v>
@@ -7929,37 +7929,37 @@
         <v>216.3</v>
       </c>
       <c r="M81">
-        <v>245.4640011427473</v>
+        <v>248.5711403977189</v>
       </c>
       <c r="N81">
-        <v>-29.16400114274737</v>
+        <v>-32.27114039771888</v>
       </c>
       <c r="O81">
-        <v>-5.541160217122</v>
+        <v>-6.131516675566587</v>
       </c>
       <c r="P81">
-        <v>-23.62284092562537</v>
+        <v>-26.13962372215229</v>
       </c>
       <c r="Q81">
-        <v>88.47715907437463</v>
+        <v>85.9603762778477</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2199773321826976</v>
+        <v>0.2286861987918325</v>
       </c>
       <c r="T81">
-        <v>2.936880047519475</v>
+        <v>3.083724049895449</v>
       </c>
       <c r="U81">
         <v>0.1586732333250682</v>
       </c>
       <c r="V81">
-        <v>0.167425772450032</v>
+        <v>0.1653329502944065</v>
       </c>
       <c r="W81">
-        <v>0.1321072446684745</v>
+        <v>0.1324393195266819</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8811882760527997</v>
+        <v>0.8701734226021396</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.151688695379712</v>
+        <v>0.1528174277129627</v>
       </c>
       <c r="C82">
-        <v>-290.5753197184899</v>
+        <v>-317.9706140474857</v>
       </c>
       <c r="D82">
-        <v>1198.58468028151</v>
+        <v>1190.771385952514</v>
       </c>
       <c r="E82">
-        <v>949.0600000000002</v>
+        <v>968.6420000000001</v>
       </c>
       <c r="F82">
-        <v>1566.56</v>
+        <v>1586.142</v>
       </c>
       <c r="G82">
         <v>77.40000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>216.3</v>
       </c>
       <c r="M82">
-        <v>248.5711403977189</v>
+        <v>251.6782796526903</v>
       </c>
       <c r="N82">
-        <v>-32.27114039771888</v>
+        <v>-35.37827965269034</v>
       </c>
       <c r="O82">
-        <v>-6.131516675566587</v>
+        <v>-6.721873134011164</v>
       </c>
       <c r="P82">
-        <v>-26.13962372215229</v>
+        <v>-28.65640651867917</v>
       </c>
       <c r="Q82">
-        <v>85.9603762778477</v>
+        <v>83.44359348132082</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2286861987918325</v>
+        <v>0.238311788201929</v>
       </c>
       <c r="T82">
-        <v>3.083724049895449</v>
+        <v>3.24602531567942</v>
       </c>
       <c r="U82">
         <v>0.1586732333250682</v>
       </c>
       <c r="V82">
-        <v>0.1653329502944065</v>
+        <v>0.1632918027599077</v>
       </c>
       <c r="W82">
-        <v>0.1324393195266819</v>
+        <v>0.1327631950056744</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8701734226021396</v>
+        <v>0.8594305408416194</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1528174277129627</v>
+        <v>0.1539461600462134</v>
       </c>
       <c r="C83">
-        <v>-317.9706140474857</v>
+        <v>-345.264702025748</v>
       </c>
       <c r="D83">
-        <v>1190.771385952514</v>
+        <v>1183.059297974252</v>
       </c>
       <c r="E83">
-        <v>968.6420000000001</v>
+        <v>988.2240000000002</v>
       </c>
       <c r="F83">
-        <v>1586.142</v>
+        <v>1605.724</v>
       </c>
       <c r="G83">
         <v>77.40000000000001</v>
@@ -8093,37 +8093,37 @@
         <v>216.3</v>
       </c>
       <c r="M83">
-        <v>251.6782796526903</v>
+        <v>254.7854189076618</v>
       </c>
       <c r="N83">
-        <v>-35.37827965269034</v>
+        <v>-38.48541890766185</v>
       </c>
       <c r="O83">
-        <v>-6.721873134011164</v>
+        <v>-7.312229592455752</v>
       </c>
       <c r="P83">
-        <v>-28.65640651867917</v>
+        <v>-31.1731893152061</v>
       </c>
       <c r="Q83">
-        <v>83.44359348132082</v>
+        <v>80.92681068479389</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.238311788201929</v>
+        <v>0.2490068875464806</v>
       </c>
       <c r="T83">
-        <v>3.24602531567942</v>
+        <v>3.426360055439388</v>
       </c>
       <c r="U83">
         <v>0.1586732333250682</v>
       </c>
       <c r="V83">
-        <v>0.1632918027599077</v>
+        <v>0.1613004393116161</v>
       </c>
       <c r="W83">
-        <v>0.1327631950056744</v>
+        <v>0.1330791710827401</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8594305408416194</v>
+        <v>0.8489496805874532</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1539461600462134</v>
+        <v>0.1550748923794641</v>
       </c>
       <c r="C84">
-        <v>-345.264702025748</v>
+        <v>-372.4595374030721</v>
       </c>
       <c r="D84">
-        <v>1183.059297974252</v>
+        <v>1175.446462596928</v>
       </c>
       <c r="E84">
-        <v>988.2240000000002</v>
+        <v>1007.806</v>
       </c>
       <c r="F84">
-        <v>1605.724</v>
+        <v>1625.306</v>
       </c>
       <c r="G84">
         <v>77.40000000000001</v>
@@ -8175,37 +8175,37 @@
         <v>216.3</v>
       </c>
       <c r="M84">
-        <v>254.7854189076618</v>
+        <v>257.8925581626333</v>
       </c>
       <c r="N84">
-        <v>-38.48541890766185</v>
+        <v>-41.59255816263337</v>
       </c>
       <c r="O84">
-        <v>-7.312229592455752</v>
+        <v>-7.902586050900339</v>
       </c>
       <c r="P84">
-        <v>-31.1731893152061</v>
+        <v>-33.68997211173303</v>
       </c>
       <c r="Q84">
-        <v>80.92681068479389</v>
+        <v>78.41002788826697</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2490068875464806</v>
+        <v>0.2609602338727442</v>
       </c>
       <c r="T84">
-        <v>3.426360055439388</v>
+        <v>3.627910646935823</v>
       </c>
       <c r="U84">
         <v>0.1586732333250682</v>
       </c>
       <c r="V84">
-        <v>0.1613004393116161</v>
+        <v>0.1593570605247291</v>
       </c>
       <c r="W84">
-        <v>0.1330791710827401</v>
+        <v>0.1333875332784308</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8489496805874532</v>
+        <v>0.838721371182785</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1550748923794641</v>
+        <v>0.1562036247127148</v>
       </c>
       <c r="C85">
-        <v>-372.4595374030721</v>
+        <v>-399.5570239622641</v>
       </c>
       <c r="D85">
-        <v>1175.446462596928</v>
+        <v>1167.930976037736</v>
       </c>
       <c r="E85">
-        <v>1007.806</v>
+        <v>1027.388</v>
       </c>
       <c r="F85">
-        <v>1625.306</v>
+        <v>1644.888</v>
       </c>
       <c r="G85">
         <v>77.40000000000001</v>
@@ -8257,37 +8257,37 @@
         <v>216.3</v>
       </c>
       <c r="M85">
-        <v>257.8925581626333</v>
+        <v>260.9996974176048</v>
       </c>
       <c r="N85">
-        <v>-41.59255816263337</v>
+        <v>-44.69969741760482</v>
       </c>
       <c r="O85">
-        <v>-7.902586050900339</v>
+        <v>-8.492942509344916</v>
       </c>
       <c r="P85">
-        <v>-33.68997211173303</v>
+        <v>-36.20675490825991</v>
       </c>
       <c r="Q85">
-        <v>78.41002788826697</v>
+        <v>75.89324509174008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2609602338727442</v>
+        <v>0.2744077484897907</v>
       </c>
       <c r="T85">
-        <v>3.627910646935823</v>
+        <v>3.854655062369313</v>
       </c>
       <c r="U85">
         <v>0.1586732333250682</v>
       </c>
       <c r="V85">
-        <v>0.1593570605247291</v>
+        <v>0.1574599526613395</v>
       </c>
       <c r="W85">
-        <v>0.1333875332784308</v>
+        <v>0.1336885535170813</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.838721371182785</v>
+        <v>0.8287365929544186</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1562036247127148</v>
+        <v>0.1573323570459655</v>
       </c>
       <c r="C86">
-        <v>-399.5570239622639</v>
+        <v>-426.5590171063691</v>
       </c>
       <c r="D86">
-        <v>1167.930976037736</v>
+        <v>1160.510982893631</v>
       </c>
       <c r="E86">
-        <v>1027.388</v>
+        <v>1046.97</v>
       </c>
       <c r="F86">
-        <v>1644.888</v>
+        <v>1664.47</v>
       </c>
       <c r="G86">
         <v>77.40000000000001</v>
@@ -8339,37 +8339,37 @@
         <v>216.3</v>
       </c>
       <c r="M86">
-        <v>260.9996974176048</v>
+        <v>264.1068366725763</v>
       </c>
       <c r="N86">
-        <v>-44.69969741760477</v>
+        <v>-47.80683667257628</v>
       </c>
       <c r="O86">
-        <v>-8.492942509344905</v>
+        <v>-9.083298967789494</v>
       </c>
       <c r="P86">
-        <v>-36.20675490825986</v>
+        <v>-38.72353770478679</v>
       </c>
       <c r="Q86">
-        <v>75.89324509174014</v>
+        <v>73.3764622952132</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2744077484897905</v>
+        <v>0.2896482650557767</v>
       </c>
       <c r="T86">
-        <v>3.854655062369309</v>
+        <v>4.111632066527265</v>
       </c>
       <c r="U86">
         <v>0.1586732333250682</v>
       </c>
       <c r="V86">
-        <v>0.1574599526613396</v>
+        <v>0.1556074826300297</v>
       </c>
       <c r="W86">
-        <v>0.1336885535170813</v>
+        <v>0.133982490926587</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8287365929544188</v>
+        <v>0.8189867506843668</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1573323570459655</v>
+        <v>0.1584610893792161</v>
       </c>
       <c r="C87">
-        <v>-426.5590171063691</v>
+        <v>-453.4673253857791</v>
       </c>
       <c r="D87">
-        <v>1160.510982893631</v>
+        <v>1153.184674614221</v>
       </c>
       <c r="E87">
-        <v>1046.97</v>
+        <v>1066.552</v>
       </c>
       <c r="F87">
-        <v>1664.47</v>
+        <v>1684.052</v>
       </c>
       <c r="G87">
         <v>77.40000000000001</v>
@@ -8421,37 +8421,37 @@
         <v>216.3</v>
       </c>
       <c r="M87">
-        <v>264.1068366725763</v>
+        <v>267.2139759275477</v>
       </c>
       <c r="N87">
-        <v>-47.80683667257628</v>
+        <v>-50.91397592754774</v>
       </c>
       <c r="O87">
-        <v>-9.083298967789494</v>
+        <v>-9.67365542623407</v>
       </c>
       <c r="P87">
-        <v>-38.72353770478679</v>
+        <v>-41.24032050131367</v>
       </c>
       <c r="Q87">
-        <v>73.3764622952132</v>
+        <v>70.85967949868632</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2896482650557767</v>
+        <v>0.3070659982740464</v>
       </c>
       <c r="T87">
-        <v>4.111632066527265</v>
+        <v>4.405320071279212</v>
       </c>
       <c r="U87">
         <v>0.1586732333250682</v>
       </c>
       <c r="V87">
-        <v>0.1556074826300297</v>
+        <v>0.1537980932971224</v>
       </c>
       <c r="W87">
-        <v>0.133982490926587</v>
+        <v>0.1342695925823833</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8189867506843668</v>
+        <v>0.809463648932223</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1584610893792161</v>
+        <v>0.1595898217124668</v>
       </c>
       <c r="C88">
-        <v>-453.4673253857791</v>
+        <v>-480.2837119678591</v>
       </c>
       <c r="D88">
-        <v>1153.184674614221</v>
+        <v>1145.950288032141</v>
       </c>
       <c r="E88">
-        <v>1066.552</v>
+        <v>1086.134</v>
       </c>
       <c r="F88">
-        <v>1684.052</v>
+        <v>1703.634</v>
       </c>
       <c r="G88">
         <v>77.40000000000001</v>
@@ -8503,37 +8503,37 @@
         <v>216.3</v>
       </c>
       <c r="M88">
-        <v>267.2139759275477</v>
+        <v>270.3211151825192</v>
       </c>
       <c r="N88">
-        <v>-50.91397592754774</v>
+        <v>-54.02111518251925</v>
       </c>
       <c r="O88">
-        <v>-9.67365542623407</v>
+        <v>-10.26401188467866</v>
       </c>
       <c r="P88">
-        <v>-41.24032050131367</v>
+        <v>-43.75710329784059</v>
       </c>
       <c r="Q88">
-        <v>70.85967949868632</v>
+        <v>68.34289670215941</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3070659982740464</v>
+        <v>0.3271633827566653</v>
       </c>
       <c r="T88">
-        <v>4.405320071279212</v>
+        <v>4.744190845992997</v>
       </c>
       <c r="U88">
         <v>0.1586732333250682</v>
       </c>
       <c r="V88">
-        <v>0.1537980932971224</v>
+        <v>0.1520302991212934</v>
       </c>
       <c r="W88">
-        <v>0.1342695925823833</v>
+        <v>0.1345500942001153</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.809463648932223</v>
+        <v>0.8001594690594388</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1595898217124668</v>
+        <v>0.2096542005583565</v>
       </c>
       <c r="C89">
-        <v>-480.2837119678591</v>
+        <v>-749.3191457636556</v>
       </c>
       <c r="D89">
-        <v>1145.950288032141</v>
+        <v>896.4968542363446</v>
       </c>
       <c r="E89">
-        <v>1086.134</v>
+        <v>1105.716</v>
       </c>
       <c r="F89">
-        <v>1703.634</v>
+        <v>1723.216</v>
       </c>
       <c r="G89">
         <v>77.40000000000001</v>
@@ -8585,45 +8585,45 @@
         <v>216.3</v>
       </c>
       <c r="M89">
-        <v>270.3211151825192</v>
+        <v>366.4819184374907</v>
       </c>
       <c r="N89">
-        <v>-54.02111518251925</v>
+        <v>-150.1819184374907</v>
       </c>
       <c r="O89">
-        <v>-10.26401188467866</v>
+        <v>-28.53456450312324</v>
       </c>
       <c r="P89">
-        <v>-43.75710329784059</v>
+        <v>-121.6473539343675</v>
       </c>
       <c r="Q89">
-        <v>68.34289670215941</v>
+        <v>-9.547353934367507</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3271633827566653</v>
+        <v>0.3624073855917122</v>
       </c>
       <c r="T89">
-        <v>4.744190845992997</v>
+        <v>5.338455366087944</v>
       </c>
       <c r="U89">
-        <v>0.1586732333250682</v>
+        <v>0.2126732333250682</v>
       </c>
       <c r="V89">
-        <v>0.1520302991212934</v>
+        <v>0.1121392296111595</v>
       </c>
       <c r="W89">
-        <v>0.1345500942001153</v>
+        <v>0.1888242207810807</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8001594690594388</v>
+        <v>0.5902064716376816</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2096542005583565</v>
+        <v>0.2113229328916071</v>
       </c>
       <c r="C90">
-        <v>-749.3191457636556</v>
+        <v>-775.3590347823681</v>
       </c>
       <c r="D90">
-        <v>896.4968542363446</v>
+        <v>890.0389652176319</v>
       </c>
       <c r="E90">
-        <v>1105.716</v>
+        <v>1125.298</v>
       </c>
       <c r="F90">
-        <v>1723.216</v>
+        <v>1742.798</v>
       </c>
       <c r="G90">
         <v>77.40000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>216.3</v>
       </c>
       <c r="M90">
-        <v>366.4819184374907</v>
+        <v>370.6464856924622</v>
       </c>
       <c r="N90">
-        <v>-150.1819184374907</v>
+        <v>-154.3464856924622</v>
       </c>
       <c r="O90">
-        <v>-28.53456450312324</v>
+        <v>-29.32583228156782</v>
       </c>
       <c r="P90">
-        <v>-121.6473539343675</v>
+        <v>-125.0206534108944</v>
       </c>
       <c r="Q90">
-        <v>-9.547353934367507</v>
+        <v>-12.9206534108944</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3624073855917122</v>
+        <v>0.3911898751909587</v>
       </c>
       <c r="T90">
-        <v>5.338455366087944</v>
+        <v>5.823769490277756</v>
       </c>
       <c r="U90">
         <v>0.2126732333250682</v>
       </c>
       <c r="V90">
-        <v>0.1121392296111595</v>
+        <v>0.1108792382672139</v>
       </c>
       <c r="W90">
-        <v>0.1888242207810807</v>
+        <v>0.1890921872141592</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5902064716376816</v>
+        <v>0.583574938248494</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2113229328916071</v>
+        <v>0.2129916652248578</v>
       </c>
       <c r="C91">
-        <v>-775.3590347823681</v>
+        <v>-801.3065507759885</v>
       </c>
       <c r="D91">
-        <v>890.0389652176319</v>
+        <v>883.6734492240116</v>
       </c>
       <c r="E91">
-        <v>1125.298</v>
+        <v>1144.88</v>
       </c>
       <c r="F91">
-        <v>1742.798</v>
+        <v>1762.38</v>
       </c>
       <c r="G91">
         <v>77.40000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>216.3</v>
       </c>
       <c r="M91">
-        <v>370.6464856924622</v>
+        <v>374.8110529474337</v>
       </c>
       <c r="N91">
-        <v>-154.3464856924622</v>
+        <v>-158.5110529474337</v>
       </c>
       <c r="O91">
-        <v>-29.32583228156782</v>
+        <v>-30.1171000600124</v>
       </c>
       <c r="P91">
-        <v>-125.0206534108944</v>
+        <v>-128.3939528874213</v>
       </c>
       <c r="Q91">
-        <v>-12.9206534108944</v>
+        <v>-16.29395288742128</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3911898751909587</v>
+        <v>0.4257288627100547</v>
       </c>
       <c r="T91">
-        <v>5.823769490277756</v>
+        <v>6.406146439305533</v>
       </c>
       <c r="U91">
         <v>0.2126732333250682</v>
       </c>
       <c r="V91">
-        <v>0.1108792382672139</v>
+        <v>0.1096472467309115</v>
       </c>
       <c r="W91">
-        <v>0.1890921872141592</v>
+        <v>0.1893541988376137</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.583574938248494</v>
+        <v>0.5770907722679552</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2129916652248578</v>
+        <v>0.2146603975581085</v>
       </c>
       <c r="C92">
-        <v>-801.3065507759885</v>
+        <v>-827.1636616127531</v>
       </c>
       <c r="D92">
-        <v>883.6734492240116</v>
+        <v>877.3983383872469</v>
       </c>
       <c r="E92">
-        <v>1144.88</v>
+        <v>1164.462</v>
       </c>
       <c r="F92">
-        <v>1762.38</v>
+        <v>1781.962</v>
       </c>
       <c r="G92">
         <v>77.40000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>216.3</v>
       </c>
       <c r="M92">
-        <v>374.8110529474337</v>
+        <v>378.9756202024051</v>
       </c>
       <c r="N92">
-        <v>-158.5110529474337</v>
+        <v>-162.6756202024052</v>
       </c>
       <c r="O92">
-        <v>-30.1171000600124</v>
+        <v>-30.90836783845698</v>
       </c>
       <c r="P92">
-        <v>-128.3939528874213</v>
+        <v>-131.7672523639482</v>
       </c>
       <c r="Q92">
-        <v>-16.29395288742128</v>
+        <v>-19.66725236394819</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4257288627100547</v>
+        <v>0.4679431807889497</v>
       </c>
       <c r="T92">
-        <v>6.406146439305533</v>
+        <v>7.117940488117259</v>
       </c>
       <c r="U92">
         <v>0.2126732333250682</v>
       </c>
       <c r="V92">
-        <v>0.1096472467309115</v>
+        <v>0.1084423319316707</v>
       </c>
       <c r="W92">
-        <v>0.1893541988376137</v>
+        <v>0.1896104519638495</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5770907722679552</v>
+        <v>0.5707491154298459</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2146603975581085</v>
+        <v>0.2163291298913592</v>
       </c>
       <c r="C93">
-        <v>-827.1636616127531</v>
+        <v>-852.932279658404</v>
       </c>
       <c r="D93">
-        <v>877.3983383872469</v>
+        <v>871.2117203415961</v>
       </c>
       <c r="E93">
-        <v>1164.462</v>
+        <v>1184.044</v>
       </c>
       <c r="F93">
-        <v>1781.962</v>
+        <v>1801.544</v>
       </c>
       <c r="G93">
         <v>77.40000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>216.3</v>
       </c>
       <c r="M93">
-        <v>378.9756202024051</v>
+        <v>383.1401874573767</v>
       </c>
       <c r="N93">
-        <v>-162.6756202024052</v>
+        <v>-166.8401874573767</v>
       </c>
       <c r="O93">
-        <v>-30.90836783845698</v>
+        <v>-31.69963561690157</v>
       </c>
       <c r="P93">
-        <v>-131.7672523639482</v>
+        <v>-135.1405518404751</v>
       </c>
       <c r="Q93">
-        <v>-19.66725236394819</v>
+        <v>-23.04055184047513</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4679431807889497</v>
+        <v>0.5207110783875686</v>
       </c>
       <c r="T93">
-        <v>7.117940488117259</v>
+        <v>8.00768304913192</v>
       </c>
       <c r="U93">
         <v>0.2126732333250682</v>
       </c>
       <c r="V93">
-        <v>0.1084423319316707</v>
+        <v>0.1072636109324134</v>
       </c>
       <c r="W93">
-        <v>0.1896104519638495</v>
+        <v>0.1898611343699497</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5707491154298459</v>
+        <v>0.5645453206969128</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2163291298913592</v>
+        <v>0.2179978622246099</v>
       </c>
       <c r="C94">
-        <v>-852.932279658404</v>
+        <v>-878.6142637192548</v>
       </c>
       <c r="D94">
-        <v>871.2117203415961</v>
+        <v>865.1117362807454</v>
       </c>
       <c r="E94">
-        <v>1184.044</v>
+        <v>1203.626</v>
       </c>
       <c r="F94">
-        <v>1801.544</v>
+        <v>1821.126</v>
       </c>
       <c r="G94">
         <v>77.40000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>216.3</v>
       </c>
       <c r="M94">
-        <v>383.1401874573767</v>
+        <v>387.3047547123481</v>
       </c>
       <c r="N94">
-        <v>-166.8401874573767</v>
+        <v>-171.0047547123482</v>
       </c>
       <c r="O94">
-        <v>-31.69963561690157</v>
+        <v>-32.49090339534615</v>
       </c>
       <c r="P94">
-        <v>-135.1405518404751</v>
+        <v>-138.513851317002</v>
       </c>
       <c r="Q94">
-        <v>-23.04055184047513</v>
+        <v>-26.41385131700201</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5207110783875686</v>
+        <v>0.5885555181572213</v>
       </c>
       <c r="T94">
-        <v>8.00768304913192</v>
+        <v>9.151637770436482</v>
       </c>
       <c r="U94">
         <v>0.2126732333250682</v>
       </c>
       <c r="V94">
-        <v>0.1072636109324134</v>
+        <v>0.1061102387718498</v>
       </c>
       <c r="W94">
-        <v>0.1898611343699497</v>
+        <v>0.1901064257565639</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5645453206969128</v>
+        <v>0.5584749409044729</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2179978622246099</v>
+        <v>0.2196665945578605</v>
       </c>
       <c r="C95">
-        <v>-878.6142637192548</v>
+        <v>-904.2114209041932</v>
       </c>
       <c r="D95">
-        <v>865.1117362807454</v>
+        <v>859.0965790958069</v>
       </c>
       <c r="E95">
-        <v>1203.626</v>
+        <v>1223.208</v>
       </c>
       <c r="F95">
-        <v>1821.126</v>
+        <v>1840.708</v>
       </c>
       <c r="G95">
         <v>77.40000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>216.3</v>
       </c>
       <c r="M95">
-        <v>387.3047547123481</v>
+        <v>391.4693219673196</v>
       </c>
       <c r="N95">
-        <v>-171.0047547123482</v>
+        <v>-175.1693219673196</v>
       </c>
       <c r="O95">
-        <v>-32.49090339534615</v>
+        <v>-33.28217117379073</v>
       </c>
       <c r="P95">
-        <v>-138.513851317002</v>
+        <v>-141.8871507935289</v>
       </c>
       <c r="Q95">
-        <v>-26.41385131700201</v>
+        <v>-29.78715079352892</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5885555181572213</v>
+        <v>0.6790147711834249</v>
       </c>
       <c r="T95">
-        <v>9.151637770436482</v>
+        <v>10.6769107321759</v>
       </c>
       <c r="U95">
         <v>0.2126732333250682</v>
       </c>
       <c r="V95">
-        <v>0.1061102387718498</v>
+        <v>0.1049814064444897</v>
       </c>
       <c r="W95">
-        <v>0.1901064257565639</v>
+        <v>0.1903464981775054</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5584749409044729</v>
+        <v>0.5525337181288934</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2196665945578605</v>
+        <v>0.2213353268911112</v>
       </c>
       <c r="C96">
-        <v>-904.2114209041932</v>
+        <v>-929.7255084095459</v>
       </c>
       <c r="D96">
-        <v>859.0965790958069</v>
+        <v>853.1644915904543</v>
       </c>
       <c r="E96">
-        <v>1223.208</v>
+        <v>1242.79</v>
       </c>
       <c r="F96">
-        <v>1840.708</v>
+        <v>1860.29</v>
       </c>
       <c r="G96">
         <v>77.40000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>216.3</v>
       </c>
       <c r="M96">
-        <v>391.4693219673196</v>
+        <v>395.6338892222911</v>
       </c>
       <c r="N96">
-        <v>-175.1693219673196</v>
+        <v>-179.3338892222912</v>
       </c>
       <c r="O96">
-        <v>-33.28217117379073</v>
+        <v>-34.07343895223532</v>
       </c>
       <c r="P96">
-        <v>-141.8871507935289</v>
+        <v>-145.2604502700559</v>
       </c>
       <c r="Q96">
-        <v>-29.78715079352892</v>
+        <v>-33.16045027005586</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6790147711834249</v>
+        <v>0.8056577254201104</v>
       </c>
       <c r="T96">
-        <v>10.6769107321759</v>
+        <v>12.81229287861108</v>
       </c>
       <c r="U96">
         <v>0.2126732333250682</v>
       </c>
       <c r="V96">
-        <v>0.1049814064444897</v>
+        <v>0.1038763390082319</v>
       </c>
       <c r="W96">
-        <v>0.1903464981775054</v>
+        <v>0.1905815164422166</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5525337181288934</v>
+        <v>0.5467175737275365</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2213353268911112</v>
+        <v>0.2230040592243619</v>
       </c>
       <c r="C97">
-        <v>-929.7255084095459</v>
+        <v>-955.1582352304963</v>
       </c>
       <c r="D97">
-        <v>853.1644915904543</v>
+        <v>847.313764769504</v>
       </c>
       <c r="E97">
-        <v>1242.79</v>
+        <v>1262.372</v>
       </c>
       <c r="F97">
-        <v>1860.29</v>
+        <v>1879.872</v>
       </c>
       <c r="G97">
         <v>77.40000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>216.3</v>
       </c>
       <c r="M97">
-        <v>395.6338892222911</v>
+        <v>399.7984564772626</v>
       </c>
       <c r="N97">
-        <v>-179.3338892222912</v>
+        <v>-183.4984564772626</v>
       </c>
       <c r="O97">
-        <v>-34.07343895223532</v>
+        <v>-34.8647067306799</v>
       </c>
       <c r="P97">
-        <v>-145.2604502700559</v>
+        <v>-148.6337497465827</v>
       </c>
       <c r="Q97">
-        <v>-33.16045027005586</v>
+        <v>-36.53374974658274</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8056577254201104</v>
+        <v>0.9956221567751381</v>
       </c>
       <c r="T97">
-        <v>12.81229287861108</v>
+        <v>16.01536609826386</v>
       </c>
       <c r="U97">
         <v>0.2126732333250682</v>
       </c>
       <c r="V97">
-        <v>0.1038763390082319</v>
+        <v>0.1027942938102295</v>
       </c>
       <c r="W97">
-        <v>0.1905815164422166</v>
+        <v>0.1908116384930796</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5467175737275365</v>
+        <v>0.5410225990012081</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2230040592243619</v>
+        <v>0.2246727915576126</v>
       </c>
       <c r="C98">
-        <v>-955.1582352304961</v>
+        <v>-980.5112638025685</v>
       </c>
       <c r="D98">
-        <v>847.313764769504</v>
+        <v>841.5427361974315</v>
       </c>
       <c r="E98">
-        <v>1262.372</v>
+        <v>1281.954</v>
       </c>
       <c r="F98">
-        <v>1879.872</v>
+        <v>1899.454</v>
       </c>
       <c r="G98">
         <v>77.40000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>216.3</v>
       </c>
       <c r="M98">
-        <v>399.7984564772626</v>
+        <v>403.963023732234</v>
       </c>
       <c r="N98">
-        <v>-183.4984564772626</v>
+        <v>-187.6630237322341</v>
       </c>
       <c r="O98">
-        <v>-34.8647067306799</v>
+        <v>-35.65597450912447</v>
       </c>
       <c r="P98">
-        <v>-148.6337497465827</v>
+        <v>-152.0070492231096</v>
       </c>
       <c r="Q98">
-        <v>-36.53374974658274</v>
+        <v>-39.9070492231096</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9956221567751357</v>
+        <v>1.312229542366848</v>
       </c>
       <c r="T98">
-        <v>16.01536609826382</v>
+        <v>21.35382146435176</v>
       </c>
       <c r="U98">
         <v>0.2126732333250682</v>
       </c>
       <c r="V98">
-        <v>0.1027942938102295</v>
+        <v>0.1017345588224952</v>
       </c>
       <c r="W98">
-        <v>0.1908116384930796</v>
+        <v>0.1910370157593888</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5410225990012081</v>
+        <v>0.5354450464341853</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2246727915576126</v>
+        <v>0.2263415238908633</v>
       </c>
       <c r="C99">
-        <v>-980.5112638025685</v>
+        <v>-1005.786211576484</v>
       </c>
       <c r="D99">
-        <v>841.5427361974315</v>
+        <v>835.8497884235159</v>
       </c>
       <c r="E99">
-        <v>1281.954</v>
+        <v>1301.536</v>
       </c>
       <c r="F99">
-        <v>1899.454</v>
+        <v>1919.036</v>
       </c>
       <c r="G99">
         <v>77.40000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>216.3</v>
       </c>
       <c r="M99">
-        <v>403.963023732234</v>
+        <v>408.1275909872056</v>
       </c>
       <c r="N99">
-        <v>-187.6630237322341</v>
+        <v>-191.8275909872056</v>
       </c>
       <c r="O99">
-        <v>-35.65597450912447</v>
+        <v>-36.44724228756906</v>
       </c>
       <c r="P99">
-        <v>-152.0070492231096</v>
+        <v>-155.3803486996365</v>
       </c>
       <c r="Q99">
-        <v>-39.9070492231096</v>
+        <v>-43.28034869963653</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.312229542366848</v>
+        <v>1.945444313550271</v>
       </c>
       <c r="T99">
-        <v>21.35382146435176</v>
+        <v>32.03073219652763</v>
       </c>
       <c r="U99">
         <v>0.2126732333250682</v>
       </c>
       <c r="V99">
-        <v>0.1017345588224952</v>
+        <v>0.1006964510794085</v>
       </c>
       <c r="W99">
-        <v>0.1910370157593888</v>
+        <v>0.1912577934896508</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5354450464341853</v>
+        <v>0.5299813214705712</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2263415238908633</v>
+        <v>0.2280102562241139</v>
       </c>
       <c r="C100">
-        <v>-1005.786211576484</v>
+        <v>-1030.984652529524</v>
       </c>
       <c r="D100">
-        <v>835.8497884235159</v>
+        <v>830.2333474704756</v>
       </c>
       <c r="E100">
-        <v>1301.536</v>
+        <v>1321.118</v>
       </c>
       <c r="F100">
-        <v>1919.036</v>
+        <v>1938.618</v>
       </c>
       <c r="G100">
         <v>77.40000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>216.3</v>
       </c>
       <c r="M100">
-        <v>408.1275909872056</v>
+        <v>412.292158242177</v>
       </c>
       <c r="N100">
-        <v>-191.8275909872056</v>
+        <v>-195.9921582421771</v>
       </c>
       <c r="O100">
-        <v>-36.44724228756906</v>
+        <v>-37.23851006601364</v>
       </c>
       <c r="P100">
-        <v>-155.3803486996365</v>
+        <v>-158.7536481761634</v>
       </c>
       <c r="Q100">
-        <v>-43.28034869963653</v>
+        <v>-46.65364817616341</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.945444313550271</v>
+        <v>3.845088627100543</v>
       </c>
       <c r="T100">
-        <v>32.03073219652763</v>
+        <v>64.06146439305526</v>
       </c>
       <c r="U100">
         <v>0.2126732333250682</v>
       </c>
       <c r="V100">
-        <v>0.1006964510794085</v>
+        <v>0.09967931520991956</v>
       </c>
       <c r="W100">
-        <v>0.1912577934896508</v>
+        <v>0.1914741110637459</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5299813214705712</v>
+        <v>0.5246279747890503</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2280102562241139</v>
-      </c>
-      <c r="C101">
-        <v>-1030.984652529524</v>
-      </c>
-      <c r="D101">
-        <v>830.2333474704756</v>
-      </c>
-      <c r="E101">
-        <v>1321.118</v>
-      </c>
-      <c r="F101">
-        <v>1938.618</v>
-      </c>
-      <c r="G101">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>1340.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>328.4</v>
-      </c>
-      <c r="K101">
-        <v>112.1</v>
-      </c>
-      <c r="L101">
-        <v>216.3</v>
-      </c>
-      <c r="M101">
-        <v>412.292158242177</v>
-      </c>
-      <c r="N101">
-        <v>-195.9921582421771</v>
-      </c>
-      <c r="O101">
-        <v>-37.23851006601364</v>
-      </c>
-      <c r="P101">
-        <v>-158.7536481761634</v>
-      </c>
-      <c r="Q101">
-        <v>-46.65364817616341</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.845088627100543</v>
-      </c>
-      <c r="T101">
-        <v>64.06146439305526</v>
-      </c>
-      <c r="U101">
-        <v>0.2126732333250682</v>
-      </c>
-      <c r="V101">
-        <v>0.09967931520991956</v>
-      </c>
-      <c r="W101">
-        <v>0.1914741110637459</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5246279747890503</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
